--- a/AKC.xlsx
+++ b/AKC.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="513" documentId="8_{2A84C096-BC25-6B45-83BF-6F0F09ED3276}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F444A99E-ACCF-4FE6-A733-30F6EDF20981}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/55b6a939d4276db6/Escritorio/APP GAV AKC/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="550" documentId="8_{2A84C096-BC25-6B45-83BF-6F0F09ED3276}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{481812EB-DFD4-F44E-A10D-10A62009C09A}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="140" yWindow="660" windowWidth="16560" windowHeight="20200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
@@ -31,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2018" uniqueCount="883">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2020" uniqueCount="884">
   <si>
     <t>Tipo</t>
   </si>
@@ -2680,13 +2685,16 @@
   </si>
   <si>
     <t>https://youtube.com/shorts/M1LZbpW788w?feature=shared</t>
+  </si>
+  <si>
+    <t>Abductor</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2709,6 +2717,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -2724,7 +2738,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -2747,12 +2761,67 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -2760,8 +2829,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="2" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
@@ -2776,6 +2851,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3064,23 +3143,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K418"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="61" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.85546875" customWidth="1"/>
+    <col min="6" max="6" width="7.83203125" customWidth="1"/>
     <col min="7" max="7" width="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="56.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="2.85546875" customWidth="1"/>
+    <col min="8" max="8" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="56.1640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="2.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3115,7 +3194,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>11</v>
       </c>
@@ -3136,7 +3215,7 @@
       <c r="J2" s="4"/>
       <c r="K2" s="4"/>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>11</v>
       </c>
@@ -3157,7 +3236,7 @@
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>11</v>
       </c>
@@ -3178,7 +3257,7 @@
       <c r="J4" s="4"/>
       <c r="K4" s="4"/>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>11</v>
       </c>
@@ -3199,7 +3278,7 @@
       <c r="J5" s="4"/>
       <c r="K5" s="4"/>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>11</v>
       </c>
@@ -3220,7 +3299,7 @@
       <c r="J6" s="4"/>
       <c r="K6" s="4"/>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>11</v>
       </c>
@@ -3241,7 +3320,7 @@
       <c r="J7" s="4"/>
       <c r="K7" s="4"/>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>11</v>
       </c>
@@ -3262,7 +3341,7 @@
       <c r="J8" s="4"/>
       <c r="K8" s="4"/>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
@@ -3283,7 +3362,7 @@
       <c r="J9" s="4"/>
       <c r="K9" s="4"/>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>11</v>
       </c>
@@ -3304,7 +3383,7 @@
       <c r="J10" s="4"/>
       <c r="K10" s="4"/>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>11</v>
       </c>
@@ -3325,7 +3404,7 @@
       <c r="J11" s="4"/>
       <c r="K11" s="4"/>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
         <v>11</v>
       </c>
@@ -3346,7 +3425,7 @@
       <c r="J12" s="4"/>
       <c r="K12" s="4"/>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
         <v>11</v>
       </c>
@@ -3367,7 +3446,7 @@
       <c r="J13" s="4"/>
       <c r="K13" s="4"/>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
         <v>11</v>
       </c>
@@ -3388,7 +3467,7 @@
       <c r="J14" s="4"/>
       <c r="K14" s="4"/>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
         <v>11</v>
       </c>
@@ -3409,7 +3488,7 @@
       <c r="J15" s="4"/>
       <c r="K15" s="4"/>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
         <v>11</v>
       </c>
@@ -3430,7 +3509,7 @@
       <c r="J16" s="4"/>
       <c r="K16" s="4"/>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
         <v>11</v>
       </c>
@@ -3451,7 +3530,7 @@
       <c r="J17" s="4"/>
       <c r="K17" s="4"/>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
         <v>11</v>
       </c>
@@ -3472,7 +3551,7 @@
       <c r="J18" s="4"/>
       <c r="K18" s="4"/>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
         <v>11</v>
       </c>
@@ -3493,7 +3572,7 @@
       <c r="J19" s="4"/>
       <c r="K19" s="4"/>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
         <v>11</v>
       </c>
@@ -3514,7 +3593,7 @@
       <c r="J20" s="4"/>
       <c r="K20" s="4"/>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
         <v>11</v>
       </c>
@@ -3535,7 +3614,7 @@
       <c r="J21" s="4"/>
       <c r="K21" s="4"/>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>11</v>
       </c>
@@ -3556,7 +3635,7 @@
       <c r="J22" s="4"/>
       <c r="K22" s="4"/>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
         <v>11</v>
       </c>
@@ -3577,7 +3656,7 @@
       <c r="J23" s="4"/>
       <c r="K23" s="4"/>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
         <v>11</v>
       </c>
@@ -3598,7 +3677,7 @@
       <c r="J24" s="4"/>
       <c r="K24" s="4"/>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
         <v>11</v>
       </c>
@@ -3619,7 +3698,7 @@
       <c r="J25" s="4"/>
       <c r="K25" s="4"/>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
         <v>11</v>
       </c>
@@ -3640,7 +3719,7 @@
       <c r="J26" s="4"/>
       <c r="K26" s="4"/>
     </row>
-    <row r="27" spans="1:11">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
         <v>11</v>
       </c>
@@ -3661,7 +3740,7 @@
       <c r="J27" s="4"/>
       <c r="K27" s="4"/>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
         <v>11</v>
       </c>
@@ -3682,7 +3761,7 @@
       <c r="J28" s="4"/>
       <c r="K28" s="4"/>
     </row>
-    <row r="29" spans="1:11">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
         <v>11</v>
       </c>
@@ -3703,7 +3782,7 @@
       <c r="J29" s="4"/>
       <c r="K29" s="4"/>
     </row>
-    <row r="30" spans="1:11">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
         <v>11</v>
       </c>
@@ -3724,7 +3803,7 @@
       <c r="J30" s="4"/>
       <c r="K30" s="4"/>
     </row>
-    <row r="31" spans="1:11">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
         <v>11</v>
       </c>
@@ -3745,7 +3824,7 @@
       <c r="J31" s="4"/>
       <c r="K31" s="4"/>
     </row>
-    <row r="32" spans="1:11">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
         <v>11</v>
       </c>
@@ -3766,7 +3845,7 @@
       <c r="J32" s="4"/>
       <c r="K32" s="4"/>
     </row>
-    <row r="33" spans="1:11">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
         <v>11</v>
       </c>
@@ -3787,7 +3866,7 @@
       <c r="J33" s="4"/>
       <c r="K33" s="4"/>
     </row>
-    <row r="34" spans="1:11">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
         <v>11</v>
       </c>
@@ -3808,7 +3887,7 @@
       <c r="J34" s="4"/>
       <c r="K34" s="4"/>
     </row>
-    <row r="35" spans="1:11">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
         <v>11</v>
       </c>
@@ -3829,7 +3908,7 @@
       <c r="J35" s="4"/>
       <c r="K35" s="4"/>
     </row>
-    <row r="36" spans="1:11">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
         <v>11</v>
       </c>
@@ -3850,7 +3929,7 @@
       <c r="J36" s="4"/>
       <c r="K36" s="4"/>
     </row>
-    <row r="37" spans="1:11">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
         <v>11</v>
       </c>
@@ -3871,7 +3950,7 @@
       <c r="J37" s="4"/>
       <c r="K37" s="4"/>
     </row>
-    <row r="38" spans="1:11">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
         <v>11</v>
       </c>
@@ -3892,7 +3971,7 @@
       <c r="J38" s="4"/>
       <c r="K38" s="4"/>
     </row>
-    <row r="39" spans="1:11">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39" s="4" t="s">
         <v>11</v>
       </c>
@@ -3913,7 +3992,7 @@
       <c r="J39" s="4"/>
       <c r="K39" s="4"/>
     </row>
-    <row r="40" spans="1:11">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
         <v>11</v>
       </c>
@@ -3934,7 +4013,7 @@
       <c r="J40" s="4"/>
       <c r="K40" s="4"/>
     </row>
-    <row r="41" spans="1:11">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A41" s="4" t="s">
         <v>11</v>
       </c>
@@ -3955,7 +4034,7 @@
       <c r="J41" s="4"/>
       <c r="K41" s="4"/>
     </row>
-    <row r="42" spans="1:11">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
         <v>11</v>
       </c>
@@ -3976,7 +4055,7 @@
       <c r="J42" s="4"/>
       <c r="K42" s="4"/>
     </row>
-    <row r="43" spans="1:11">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A43" s="4" t="s">
         <v>11</v>
       </c>
@@ -3997,7 +4076,7 @@
       <c r="J43" s="4"/>
       <c r="K43" s="4"/>
     </row>
-    <row r="44" spans="1:11">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" s="4" t="s">
         <v>11</v>
       </c>
@@ -4018,7 +4097,7 @@
       <c r="J44" s="4"/>
       <c r="K44" s="4"/>
     </row>
-    <row r="45" spans="1:11">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A45" s="4" t="s">
         <v>11</v>
       </c>
@@ -4039,7 +4118,7 @@
       <c r="J45" s="4"/>
       <c r="K45" s="4"/>
     </row>
-    <row r="46" spans="1:11">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" s="4" t="s">
         <v>11</v>
       </c>
@@ -4060,7 +4139,7 @@
       <c r="J46" s="4"/>
       <c r="K46" s="4"/>
     </row>
-    <row r="47" spans="1:11">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A47" s="4" t="s">
         <v>11</v>
       </c>
@@ -4081,7 +4160,7 @@
       <c r="J47" s="4"/>
       <c r="K47" s="4"/>
     </row>
-    <row r="48" spans="1:11">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" s="4" t="s">
         <v>11</v>
       </c>
@@ -4102,7 +4181,7 @@
       <c r="J48" s="4"/>
       <c r="K48" s="4"/>
     </row>
-    <row r="49" spans="1:11">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A49" s="4" t="s">
         <v>11</v>
       </c>
@@ -4123,7 +4202,7 @@
       <c r="J49" s="4"/>
       <c r="K49" s="4"/>
     </row>
-    <row r="50" spans="1:11">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
         <v>11</v>
       </c>
@@ -4144,7 +4223,7 @@
       <c r="J50" s="4"/>
       <c r="K50" s="4"/>
     </row>
-    <row r="51" spans="1:11">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51" s="4" t="s">
         <v>11</v>
       </c>
@@ -4165,7 +4244,7 @@
       <c r="J51" s="4"/>
       <c r="K51" s="4"/>
     </row>
-    <row r="52" spans="1:11">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52" s="4" t="s">
         <v>11</v>
       </c>
@@ -4186,7 +4265,7 @@
       <c r="J52" s="4"/>
       <c r="K52" s="4"/>
     </row>
-    <row r="53" spans="1:11">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A53" s="4" t="s">
         <v>11</v>
       </c>
@@ -4207,7 +4286,7 @@
       <c r="J53" s="4"/>
       <c r="K53" s="4"/>
     </row>
-    <row r="54" spans="1:11">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A54" s="4" t="s">
         <v>11</v>
       </c>
@@ -4228,7 +4307,7 @@
       <c r="J54" s="4"/>
       <c r="K54" s="4"/>
     </row>
-    <row r="55" spans="1:11">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A55" s="4" t="s">
         <v>11</v>
       </c>
@@ -4249,7 +4328,7 @@
       <c r="J55" s="4"/>
       <c r="K55" s="4"/>
     </row>
-    <row r="56" spans="1:11">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A56" s="4" t="s">
         <v>11</v>
       </c>
@@ -4270,7 +4349,7 @@
       <c r="J56" s="4"/>
       <c r="K56" s="4"/>
     </row>
-    <row r="57" spans="1:11">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A57" s="4" t="s">
         <v>11</v>
       </c>
@@ -4291,7 +4370,7 @@
       <c r="J57" s="4"/>
       <c r="K57" s="4"/>
     </row>
-    <row r="58" spans="1:11">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A58" s="4" t="s">
         <v>11</v>
       </c>
@@ -4312,7 +4391,7 @@
       <c r="J58" s="4"/>
       <c r="K58" s="4"/>
     </row>
-    <row r="59" spans="1:11">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A59" s="4" t="s">
         <v>11</v>
       </c>
@@ -4333,7 +4412,7 @@
       <c r="J59" s="4"/>
       <c r="K59" s="4"/>
     </row>
-    <row r="60" spans="1:11">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A60" s="4" t="s">
         <v>11</v>
       </c>
@@ -4354,7 +4433,7 @@
       <c r="J60" s="4"/>
       <c r="K60" s="4"/>
     </row>
-    <row r="61" spans="1:11">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A61" s="4" t="s">
         <v>11</v>
       </c>
@@ -4375,7 +4454,7 @@
       <c r="J61" s="4"/>
       <c r="K61" s="4"/>
     </row>
-    <row r="62" spans="1:11">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A62" s="4" t="s">
         <v>11</v>
       </c>
@@ -4396,7 +4475,7 @@
       <c r="J62" s="4"/>
       <c r="K62" s="4"/>
     </row>
-    <row r="63" spans="1:11">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A63" s="4" t="s">
         <v>11</v>
       </c>
@@ -4417,7 +4496,7 @@
       <c r="J63" s="4"/>
       <c r="K63" s="4"/>
     </row>
-    <row r="64" spans="1:11">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A64" s="4" t="s">
         <v>11</v>
       </c>
@@ -4438,7 +4517,7 @@
       <c r="J64" s="4"/>
       <c r="K64" s="4"/>
     </row>
-    <row r="65" spans="1:11">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A65" s="4" t="s">
         <v>11</v>
       </c>
@@ -4459,7 +4538,7 @@
       <c r="J65" s="4"/>
       <c r="K65" s="4"/>
     </row>
-    <row r="66" spans="1:11">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A66" s="4" t="s">
         <v>11</v>
       </c>
@@ -4480,7 +4559,7 @@
       <c r="J66" s="4"/>
       <c r="K66" s="4"/>
     </row>
-    <row r="67" spans="1:11">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A67" s="4" t="s">
         <v>11</v>
       </c>
@@ -4501,7 +4580,7 @@
       <c r="J67" s="4"/>
       <c r="K67" s="4"/>
     </row>
-    <row r="68" spans="1:11">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A68" s="4" t="s">
         <v>11</v>
       </c>
@@ -4522,7 +4601,7 @@
       <c r="J68" s="4"/>
       <c r="K68" s="4"/>
     </row>
-    <row r="69" spans="1:11">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A69" s="4" t="s">
         <v>11</v>
       </c>
@@ -4543,7 +4622,7 @@
       <c r="J69" s="4"/>
       <c r="K69" s="4"/>
     </row>
-    <row r="70" spans="1:11">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A70" s="4" t="s">
         <v>11</v>
       </c>
@@ -4564,7 +4643,7 @@
       <c r="J70" s="4"/>
       <c r="K70" s="4"/>
     </row>
-    <row r="71" spans="1:11">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A71" s="4" t="s">
         <v>11</v>
       </c>
@@ -4585,7 +4664,7 @@
       <c r="J71" s="4"/>
       <c r="K71" s="4"/>
     </row>
-    <row r="72" spans="1:11">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A72" s="4" t="s">
         <v>11</v>
       </c>
@@ -4606,7 +4685,7 @@
       <c r="J72" s="4"/>
       <c r="K72" s="4"/>
     </row>
-    <row r="73" spans="1:11">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A73" s="4" t="s">
         <v>11</v>
       </c>
@@ -4627,7 +4706,7 @@
       <c r="J73" s="4"/>
       <c r="K73" s="4"/>
     </row>
-    <row r="74" spans="1:11">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A74" s="4" t="s">
         <v>11</v>
       </c>
@@ -4648,7 +4727,7 @@
       <c r="J74" s="4"/>
       <c r="K74" s="4"/>
     </row>
-    <row r="75" spans="1:11">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A75" s="4" t="s">
         <v>11</v>
       </c>
@@ -4669,7 +4748,7 @@
       <c r="J75" s="4"/>
       <c r="K75" s="4"/>
     </row>
-    <row r="76" spans="1:11">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A76" s="4" t="s">
         <v>11</v>
       </c>
@@ -4690,7 +4769,7 @@
       <c r="J76" s="4"/>
       <c r="K76" s="4"/>
     </row>
-    <row r="77" spans="1:11">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A77" s="4" t="s">
         <v>11</v>
       </c>
@@ -4711,7 +4790,7 @@
       <c r="J77" s="4"/>
       <c r="K77" s="4"/>
     </row>
-    <row r="78" spans="1:11">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A78" s="4" t="s">
         <v>11</v>
       </c>
@@ -4732,7 +4811,7 @@
       <c r="J78" s="4"/>
       <c r="K78" s="4"/>
     </row>
-    <row r="79" spans="1:11">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A79" s="4" t="s">
         <v>11</v>
       </c>
@@ -4753,7 +4832,7 @@
       <c r="J79" s="4"/>
       <c r="K79" s="4"/>
     </row>
-    <row r="80" spans="1:11">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A80" s="4" t="s">
         <v>11</v>
       </c>
@@ -4774,7 +4853,7 @@
       <c r="J80" s="4"/>
       <c r="K80" s="4"/>
     </row>
-    <row r="81" spans="1:11">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A81" s="4" t="s">
         <v>11</v>
       </c>
@@ -4795,7 +4874,7 @@
       <c r="J81" s="4"/>
       <c r="K81" s="4"/>
     </row>
-    <row r="82" spans="1:11">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A82" s="4" t="s">
         <v>11</v>
       </c>
@@ -4816,7 +4895,7 @@
       <c r="J82" s="4"/>
       <c r="K82" s="4"/>
     </row>
-    <row r="83" spans="1:11">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A83" s="4" t="s">
         <v>11</v>
       </c>
@@ -4837,7 +4916,7 @@
       <c r="J83" s="4"/>
       <c r="K83" s="4"/>
     </row>
-    <row r="84" spans="1:11">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A84" s="4" t="s">
         <v>11</v>
       </c>
@@ -4858,7 +4937,7 @@
       <c r="J84" s="4"/>
       <c r="K84" s="4"/>
     </row>
-    <row r="85" spans="1:11">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A85" s="4" t="s">
         <v>11</v>
       </c>
@@ -4879,7 +4958,7 @@
       <c r="J85" s="4"/>
       <c r="K85" s="4"/>
     </row>
-    <row r="86" spans="1:11">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A86" s="4" t="s">
         <v>11</v>
       </c>
@@ -4900,7 +4979,7 @@
       <c r="J86" s="4"/>
       <c r="K86" s="4"/>
     </row>
-    <row r="87" spans="1:11">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A87" s="4" t="s">
         <v>11</v>
       </c>
@@ -4921,7 +5000,7 @@
       <c r="J87" s="4"/>
       <c r="K87" s="4"/>
     </row>
-    <row r="88" spans="1:11">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A88" s="4" t="s">
         <v>11</v>
       </c>
@@ -4942,7 +5021,7 @@
       <c r="J88" s="4"/>
       <c r="K88" s="4"/>
     </row>
-    <row r="89" spans="1:11">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A89" s="4" t="s">
         <v>11</v>
       </c>
@@ -4963,7 +5042,7 @@
       <c r="J89" s="4"/>
       <c r="K89" s="4"/>
     </row>
-    <row r="90" spans="1:11">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A90" s="4" t="s">
         <v>11</v>
       </c>
@@ -4984,7 +5063,7 @@
       <c r="J90" s="4"/>
       <c r="K90" s="4"/>
     </row>
-    <row r="91" spans="1:11">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A91" s="4" t="s">
         <v>11</v>
       </c>
@@ -5005,7 +5084,7 @@
       <c r="J91" s="4"/>
       <c r="K91" s="4"/>
     </row>
-    <row r="92" spans="1:11">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A92" s="4" t="s">
         <v>11</v>
       </c>
@@ -5026,7 +5105,7 @@
       <c r="J92" s="4"/>
       <c r="K92" s="4"/>
     </row>
-    <row r="93" spans="1:11">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A93" s="4" t="s">
         <v>11</v>
       </c>
@@ -5047,7 +5126,7 @@
       <c r="J93" s="4"/>
       <c r="K93" s="4"/>
     </row>
-    <row r="94" spans="1:11">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A94" s="4" t="s">
         <v>11</v>
       </c>
@@ -5068,7 +5147,7 @@
       <c r="J94" s="4"/>
       <c r="K94" s="4"/>
     </row>
-    <row r="95" spans="1:11">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A95" s="4" t="s">
         <v>11</v>
       </c>
@@ -5089,7 +5168,7 @@
       <c r="J95" s="4"/>
       <c r="K95" s="4"/>
     </row>
-    <row r="96" spans="1:11">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A96" s="4" t="s">
         <v>11</v>
       </c>
@@ -5110,7 +5189,7 @@
       <c r="J96" s="4"/>
       <c r="K96" s="4"/>
     </row>
-    <row r="97" spans="1:11">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A97" s="4" t="s">
         <v>11</v>
       </c>
@@ -5131,7 +5210,7 @@
       <c r="J97" s="4"/>
       <c r="K97" s="4"/>
     </row>
-    <row r="98" spans="1:11">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A98" s="4" t="s">
         <v>11</v>
       </c>
@@ -5152,7 +5231,7 @@
       <c r="J98" s="4"/>
       <c r="K98" s="4"/>
     </row>
-    <row r="99" spans="1:11">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A99" s="4" t="s">
         <v>11</v>
       </c>
@@ -5173,7 +5252,7 @@
       <c r="J99" s="4"/>
       <c r="K99" s="4"/>
     </row>
-    <row r="100" spans="1:11">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A100" s="4" t="s">
         <v>11</v>
       </c>
@@ -5194,7 +5273,7 @@
       <c r="J100" s="4"/>
       <c r="K100" s="4"/>
     </row>
-    <row r="101" spans="1:11">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A101" s="4" t="s">
         <v>11</v>
       </c>
@@ -5215,7 +5294,7 @@
       <c r="J101" s="4"/>
       <c r="K101" s="4"/>
     </row>
-    <row r="102" spans="1:11">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A102" s="4" t="s">
         <v>11</v>
       </c>
@@ -5236,7 +5315,7 @@
       <c r="J102" s="4"/>
       <c r="K102" s="4"/>
     </row>
-    <row r="103" spans="1:11">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A103" s="4" t="s">
         <v>11</v>
       </c>
@@ -5257,7 +5336,7 @@
       <c r="J103" s="4"/>
       <c r="K103" s="4"/>
     </row>
-    <row r="104" spans="1:11">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A104" s="4" t="s">
         <v>11</v>
       </c>
@@ -5278,7 +5357,7 @@
       <c r="J104" s="4"/>
       <c r="K104" s="4"/>
     </row>
-    <row r="105" spans="1:11">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A105" s="4" t="s">
         <v>11</v>
       </c>
@@ -5299,7 +5378,7 @@
       <c r="J105" s="4"/>
       <c r="K105" s="4"/>
     </row>
-    <row r="106" spans="1:11">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A106" s="4" t="s">
         <v>11</v>
       </c>
@@ -5320,7 +5399,7 @@
       <c r="J106" s="4"/>
       <c r="K106" s="4"/>
     </row>
-    <row r="107" spans="1:11">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A107" s="4" t="s">
         <v>11</v>
       </c>
@@ -5341,7 +5420,7 @@
       <c r="J107" s="4"/>
       <c r="K107" s="4"/>
     </row>
-    <row r="108" spans="1:11">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A108" s="4" t="s">
         <v>11</v>
       </c>
@@ -5362,7 +5441,7 @@
       <c r="J108" s="4"/>
       <c r="K108" s="4"/>
     </row>
-    <row r="109" spans="1:11">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A109" s="4" t="s">
         <v>11</v>
       </c>
@@ -5383,7 +5462,7 @@
       <c r="J109" s="4"/>
       <c r="K109" s="4"/>
     </row>
-    <row r="110" spans="1:11">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A110" s="4" t="s">
         <v>11</v>
       </c>
@@ -5404,7 +5483,7 @@
       <c r="J110" s="4"/>
       <c r="K110" s="4"/>
     </row>
-    <row r="111" spans="1:11">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A111" s="4" t="s">
         <v>11</v>
       </c>
@@ -5425,7 +5504,7 @@
       <c r="J111" s="4"/>
       <c r="K111" s="4"/>
     </row>
-    <row r="112" spans="1:11">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A112" s="4" t="s">
         <v>11</v>
       </c>
@@ -5446,7 +5525,7 @@
       <c r="J112" s="4"/>
       <c r="K112" s="4"/>
     </row>
-    <row r="113" spans="1:11">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A113" s="4" t="s">
         <v>11</v>
       </c>
@@ -5467,7 +5546,7 @@
       <c r="J113" s="4"/>
       <c r="K113" s="4"/>
     </row>
-    <row r="114" spans="1:11">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A114" s="4" t="s">
         <v>11</v>
       </c>
@@ -5488,7 +5567,7 @@
       <c r="J114" s="4"/>
       <c r="K114" s="4"/>
     </row>
-    <row r="115" spans="1:11">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A115" s="4" t="s">
         <v>11</v>
       </c>
@@ -5509,7 +5588,7 @@
       <c r="J115" s="4"/>
       <c r="K115" s="4"/>
     </row>
-    <row r="116" spans="1:11">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A116" s="4" t="s">
         <v>11</v>
       </c>
@@ -5530,7 +5609,7 @@
       <c r="J116" s="4"/>
       <c r="K116" s="4"/>
     </row>
-    <row r="117" spans="1:11">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A117" s="4" t="s">
         <v>11</v>
       </c>
@@ -5551,7 +5630,7 @@
       <c r="J117" s="4"/>
       <c r="K117" s="4"/>
     </row>
-    <row r="118" spans="1:11">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A118" s="4" t="s">
         <v>11</v>
       </c>
@@ -5572,7 +5651,7 @@
       <c r="J118" s="4"/>
       <c r="K118" s="4"/>
     </row>
-    <row r="119" spans="1:11">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A119" s="4" t="s">
         <v>11</v>
       </c>
@@ -5593,7 +5672,7 @@
       <c r="J119" s="4"/>
       <c r="K119" s="4"/>
     </row>
-    <row r="120" spans="1:11">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A120" s="4" t="s">
         <v>11</v>
       </c>
@@ -5614,7 +5693,7 @@
       <c r="J120" s="4"/>
       <c r="K120" s="4"/>
     </row>
-    <row r="121" spans="1:11">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A121" s="4" t="s">
         <v>11</v>
       </c>
@@ -5635,7 +5714,7 @@
       <c r="J121" s="4"/>
       <c r="K121" s="4"/>
     </row>
-    <row r="122" spans="1:11">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A122" s="4" t="s">
         <v>11</v>
       </c>
@@ -5656,7 +5735,7 @@
       <c r="J122" s="4"/>
       <c r="K122" s="4"/>
     </row>
-    <row r="123" spans="1:11">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A123" s="4" t="s">
         <v>11</v>
       </c>
@@ -5677,7 +5756,7 @@
       <c r="J123" s="4"/>
       <c r="K123" s="4"/>
     </row>
-    <row r="124" spans="1:11">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A124" s="4" t="s">
         <v>11</v>
       </c>
@@ -5698,7 +5777,7 @@
       <c r="J124" s="4"/>
       <c r="K124" s="4"/>
     </row>
-    <row r="125" spans="1:11">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A125" s="4" t="s">
         <v>11</v>
       </c>
@@ -5719,7 +5798,7 @@
       <c r="J125" s="4"/>
       <c r="K125" s="4"/>
     </row>
-    <row r="126" spans="1:11">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A126" s="4" t="s">
         <v>11</v>
       </c>
@@ -5740,7 +5819,7 @@
       <c r="J126" s="4"/>
       <c r="K126" s="4"/>
     </row>
-    <row r="127" spans="1:11">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A127" s="4" t="s">
         <v>11</v>
       </c>
@@ -5761,7 +5840,7 @@
       <c r="J127" s="4"/>
       <c r="K127" s="4"/>
     </row>
-    <row r="128" spans="1:11">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A128" s="4" t="s">
         <v>11</v>
       </c>
@@ -5782,7 +5861,7 @@
       <c r="J128" s="4"/>
       <c r="K128" s="4"/>
     </row>
-    <row r="129" spans="1:11">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A129" s="4" t="s">
         <v>11</v>
       </c>
@@ -5803,7 +5882,7 @@
       <c r="J129" s="4"/>
       <c r="K129" s="4"/>
     </row>
-    <row r="130" spans="1:11">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A130" s="4" t="s">
         <v>11</v>
       </c>
@@ -5824,7 +5903,7 @@
       <c r="J130" s="4"/>
       <c r="K130" s="4"/>
     </row>
-    <row r="131" spans="1:11">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A131" s="4" t="s">
         <v>11</v>
       </c>
@@ -5845,7 +5924,7 @@
       <c r="J131" s="4"/>
       <c r="K131" s="4"/>
     </row>
-    <row r="132" spans="1:11">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A132" s="4" t="s">
         <v>11</v>
       </c>
@@ -5866,7 +5945,7 @@
       <c r="J132" s="4"/>
       <c r="K132" s="4"/>
     </row>
-    <row r="133" spans="1:11">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A133" s="4" t="s">
         <v>11</v>
       </c>
@@ -5887,7 +5966,7 @@
       <c r="J133" s="4"/>
       <c r="K133" s="4"/>
     </row>
-    <row r="134" spans="1:11">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A134" s="4" t="s">
         <v>11</v>
       </c>
@@ -5908,7 +5987,7 @@
       <c r="J134" s="4"/>
       <c r="K134" s="4"/>
     </row>
-    <row r="135" spans="1:11">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A135" s="4" t="s">
         <v>11</v>
       </c>
@@ -5929,7 +6008,7 @@
       <c r="J135" s="4"/>
       <c r="K135" s="4"/>
     </row>
-    <row r="136" spans="1:11">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A136" s="4" t="s">
         <v>11</v>
       </c>
@@ -5950,7 +6029,7 @@
       <c r="J136" s="4"/>
       <c r="K136" s="4"/>
     </row>
-    <row r="137" spans="1:11">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A137" s="4" t="s">
         <v>288</v>
       </c>
@@ -5965,13 +6044,13 @@
       <c r="F137" s="4"/>
       <c r="G137" s="4"/>
       <c r="H137" s="4"/>
-      <c r="I137" s="4" t="s">
+      <c r="I137" s="11" t="s">
         <v>290</v>
       </c>
       <c r="J137" s="4"/>
       <c r="K137" s="4"/>
     </row>
-    <row r="138" spans="1:11">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A138" s="4" t="s">
         <v>288</v>
       </c>
@@ -5986,13 +6065,13 @@
       <c r="F138" s="4"/>
       <c r="G138" s="4"/>
       <c r="H138" s="4"/>
-      <c r="I138" s="4" t="s">
+      <c r="I138" s="11" t="s">
         <v>292</v>
       </c>
       <c r="J138" s="4"/>
       <c r="K138" s="4"/>
     </row>
-    <row r="139" spans="1:11">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A139" s="4" t="s">
         <v>288</v>
       </c>
@@ -6007,13 +6086,13 @@
       <c r="F139" s="4"/>
       <c r="G139" s="4"/>
       <c r="H139" s="4"/>
-      <c r="I139" s="4" t="s">
+      <c r="I139" s="11" t="s">
         <v>294</v>
       </c>
       <c r="J139" s="4"/>
       <c r="K139" s="4"/>
     </row>
-    <row r="140" spans="1:11">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A140" s="4" t="s">
         <v>288</v>
       </c>
@@ -6034,7 +6113,7 @@
       <c r="J140" s="4"/>
       <c r="K140" s="4"/>
     </row>
-    <row r="141" spans="1:11">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A141" s="4" t="s">
         <v>288</v>
       </c>
@@ -6055,7 +6134,7 @@
       <c r="J141" s="4"/>
       <c r="K141" s="4"/>
     </row>
-    <row r="142" spans="1:11">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A142" s="4" t="s">
         <v>288</v>
       </c>
@@ -6076,7 +6155,7 @@
       <c r="J142" s="4"/>
       <c r="K142" s="4"/>
     </row>
-    <row r="143" spans="1:11">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A143" s="4" t="s">
         <v>288</v>
       </c>
@@ -6091,13 +6170,13 @@
       <c r="F143" s="4"/>
       <c r="G143" s="4"/>
       <c r="H143" s="4"/>
-      <c r="I143" s="4" t="s">
+      <c r="I143" s="11" t="s">
         <v>302</v>
       </c>
       <c r="J143" s="4"/>
       <c r="K143" s="4"/>
     </row>
-    <row r="144" spans="1:11">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A144" s="4" t="s">
         <v>288</v>
       </c>
@@ -6118,7 +6197,7 @@
       <c r="J144" s="4"/>
       <c r="K144" s="4"/>
     </row>
-    <row r="145" spans="1:11">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A145" s="4" t="s">
         <v>288</v>
       </c>
@@ -6139,7 +6218,7 @@
       <c r="J145" s="4"/>
       <c r="K145" s="4"/>
     </row>
-    <row r="146" spans="1:11">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A146" s="4" t="s">
         <v>288</v>
       </c>
@@ -6160,7 +6239,7 @@
       <c r="J146" s="4"/>
       <c r="K146" s="4"/>
     </row>
-    <row r="147" spans="1:11">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A147" s="4" t="s">
         <v>288</v>
       </c>
@@ -6181,7 +6260,7 @@
       <c r="J147" s="4"/>
       <c r="K147" s="4"/>
     </row>
-    <row r="148" spans="1:11">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A148" s="4" t="s">
         <v>288</v>
       </c>
@@ -6202,7 +6281,7 @@
       <c r="J148" s="4"/>
       <c r="K148" s="4"/>
     </row>
-    <row r="149" spans="1:11">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A149" s="4" t="s">
         <v>288</v>
       </c>
@@ -6223,7 +6302,7 @@
       <c r="J149" s="4"/>
       <c r="K149" s="4"/>
     </row>
-    <row r="150" spans="1:11">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A150" s="4" t="s">
         <v>288</v>
       </c>
@@ -6244,7 +6323,7 @@
       <c r="J150" s="4"/>
       <c r="K150" s="4"/>
     </row>
-    <row r="151" spans="1:11">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A151" s="4" t="s">
         <v>288</v>
       </c>
@@ -6265,7 +6344,7 @@
       <c r="J151" s="4"/>
       <c r="K151" s="4"/>
     </row>
-    <row r="152" spans="1:11">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A152" s="4" t="s">
         <v>288</v>
       </c>
@@ -6286,7 +6365,7 @@
       <c r="J152" s="4"/>
       <c r="K152" s="4"/>
     </row>
-    <row r="153" spans="1:11">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A153" s="4" t="s">
         <v>288</v>
       </c>
@@ -6307,7 +6386,7 @@
       <c r="J153" s="4"/>
       <c r="K153" s="4"/>
     </row>
-    <row r="154" spans="1:11">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A154" s="4" t="s">
         <v>288</v>
       </c>
@@ -6328,7 +6407,7 @@
       <c r="J154" s="4"/>
       <c r="K154" s="4"/>
     </row>
-    <row r="155" spans="1:11">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A155" s="4" t="s">
         <v>288</v>
       </c>
@@ -6349,7 +6428,7 @@
       <c r="J155" s="4"/>
       <c r="K155" s="4"/>
     </row>
-    <row r="156" spans="1:11">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A156" s="4" t="s">
         <v>288</v>
       </c>
@@ -6370,7 +6449,7 @@
       <c r="J156" s="4"/>
       <c r="K156" s="4"/>
     </row>
-    <row r="157" spans="1:11">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A157" s="4" t="s">
         <v>288</v>
       </c>
@@ -6391,7 +6470,7 @@
       <c r="J157" s="4"/>
       <c r="K157" s="4"/>
     </row>
-    <row r="158" spans="1:11">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A158" s="4" t="s">
         <v>288</v>
       </c>
@@ -6412,7 +6491,7 @@
       <c r="J158" s="4"/>
       <c r="K158" s="4"/>
     </row>
-    <row r="159" spans="1:11">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A159" s="4" t="s">
         <v>288</v>
       </c>
@@ -6433,7 +6512,7 @@
       <c r="J159" s="4"/>
       <c r="K159" s="4"/>
     </row>
-    <row r="160" spans="1:11">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A160" s="4" t="s">
         <v>288</v>
       </c>
@@ -6454,7 +6533,7 @@
       <c r="J160" s="4"/>
       <c r="K160" s="4"/>
     </row>
-    <row r="161" spans="1:11">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A161" s="4" t="s">
         <v>288</v>
       </c>
@@ -6475,7 +6554,7 @@
       <c r="J161" s="4"/>
       <c r="K161" s="4"/>
     </row>
-    <row r="162" spans="1:11">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A162" s="4" t="s">
         <v>288</v>
       </c>
@@ -6496,7 +6575,7 @@
       <c r="J162" s="4"/>
       <c r="K162" s="4"/>
     </row>
-    <row r="163" spans="1:11">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A163" s="4" t="s">
         <v>288</v>
       </c>
@@ -6517,7 +6596,7 @@
       <c r="J163" s="4"/>
       <c r="K163" s="4"/>
     </row>
-    <row r="164" spans="1:11">
+    <row r="164" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A164" s="4" t="s">
         <v>288</v>
       </c>
@@ -6538,7 +6617,7 @@
       <c r="J164" s="4"/>
       <c r="K164" s="4"/>
     </row>
-    <row r="165" spans="1:11">
+    <row r="165" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A165" s="4" t="s">
         <v>288</v>
       </c>
@@ -6559,7 +6638,7 @@
       <c r="J165" s="4"/>
       <c r="K165" s="4"/>
     </row>
-    <row r="166" spans="1:11">
+    <row r="166" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A166" s="4" t="s">
         <v>288</v>
       </c>
@@ -6580,7 +6659,7 @@
       <c r="J166" s="4"/>
       <c r="K166" s="4"/>
     </row>
-    <row r="167" spans="1:11">
+    <row r="167" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A167" s="4" t="s">
         <v>288</v>
       </c>
@@ -6601,7 +6680,7 @@
       <c r="J167" s="4"/>
       <c r="K167" s="4"/>
     </row>
-    <row r="168" spans="1:11">
+    <row r="168" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A168" s="4" t="s">
         <v>288</v>
       </c>
@@ -6622,7 +6701,7 @@
       <c r="J168" s="4"/>
       <c r="K168" s="4"/>
     </row>
-    <row r="169" spans="1:11">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A169" s="4" t="s">
         <v>288</v>
       </c>
@@ -6643,7 +6722,7 @@
       <c r="J169" s="4"/>
       <c r="K169" s="4"/>
     </row>
-    <row r="170" spans="1:11">
+    <row r="170" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A170" s="4" t="s">
         <v>288</v>
       </c>
@@ -6664,7 +6743,7 @@
       <c r="J170" s="4"/>
       <c r="K170" s="4"/>
     </row>
-    <row r="171" spans="1:11">
+    <row r="171" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A171" s="4" t="s">
         <v>288</v>
       </c>
@@ -6685,7 +6764,7 @@
       <c r="J171" s="4"/>
       <c r="K171" s="4"/>
     </row>
-    <row r="172" spans="1:11">
+    <row r="172" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A172" s="4" t="s">
         <v>288</v>
       </c>
@@ -6706,7 +6785,7 @@
       <c r="J172" s="4"/>
       <c r="K172" s="4"/>
     </row>
-    <row r="173" spans="1:11">
+    <row r="173" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A173" s="4" t="s">
         <v>288</v>
       </c>
@@ -6727,7 +6806,7 @@
       <c r="J173" s="4"/>
       <c r="K173" s="4"/>
     </row>
-    <row r="174" spans="1:11">
+    <row r="174" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A174" s="4" t="s">
         <v>288</v>
       </c>
@@ -6748,7 +6827,7 @@
       <c r="J174" s="4"/>
       <c r="K174" s="4"/>
     </row>
-    <row r="175" spans="1:11">
+    <row r="175" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A175" s="4" t="s">
         <v>288</v>
       </c>
@@ -6769,7 +6848,7 @@
       <c r="J175" s="4"/>
       <c r="K175" s="4"/>
     </row>
-    <row r="176" spans="1:11">
+    <row r="176" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A176" s="4" t="s">
         <v>288</v>
       </c>
@@ -6790,7 +6869,7 @@
       <c r="J176" s="4"/>
       <c r="K176" s="4"/>
     </row>
-    <row r="177" spans="1:11">
+    <row r="177" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A177" s="4" t="s">
         <v>288</v>
       </c>
@@ -6811,7 +6890,7 @@
       <c r="J177" s="4"/>
       <c r="K177" s="4"/>
     </row>
-    <row r="178" spans="1:11">
+    <row r="178" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A178" s="4" t="s">
         <v>288</v>
       </c>
@@ -6832,7 +6911,7 @@
       <c r="J178" s="4"/>
       <c r="K178" s="4"/>
     </row>
-    <row r="179" spans="1:11">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A179" s="4" t="s">
         <v>288</v>
       </c>
@@ -6853,7 +6932,7 @@
       <c r="J179" s="4"/>
       <c r="K179" s="4"/>
     </row>
-    <row r="180" spans="1:11">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A180" s="4" t="s">
         <v>288</v>
       </c>
@@ -6874,7 +6953,7 @@
       <c r="J180" s="4"/>
       <c r="K180" s="4"/>
     </row>
-    <row r="181" spans="1:11">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A181" s="4" t="s">
         <v>288</v>
       </c>
@@ -6895,7 +6974,7 @@
       <c r="J181" s="4"/>
       <c r="K181" s="4"/>
     </row>
-    <row r="182" spans="1:11">
+    <row r="182" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A182" s="4" t="s">
         <v>288</v>
       </c>
@@ -6916,7 +6995,7 @@
       <c r="J182" s="4"/>
       <c r="K182" s="4"/>
     </row>
-    <row r="183" spans="1:11">
+    <row r="183" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A183" s="4" t="s">
         <v>288</v>
       </c>
@@ -6937,7 +7016,7 @@
       <c r="J183" s="4"/>
       <c r="K183" s="4"/>
     </row>
-    <row r="184" spans="1:11">
+    <row r="184" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A184" s="4" t="s">
         <v>288</v>
       </c>
@@ -6958,7 +7037,7 @@
       <c r="J184" s="4"/>
       <c r="K184" s="4"/>
     </row>
-    <row r="185" spans="1:11">
+    <row r="185" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A185" s="4" t="s">
         <v>288</v>
       </c>
@@ -6979,7 +7058,7 @@
       <c r="J185" s="4"/>
       <c r="K185" s="4"/>
     </row>
-    <row r="186" spans="1:11">
+    <row r="186" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A186" s="4" t="s">
         <v>288</v>
       </c>
@@ -7000,7 +7079,7 @@
       <c r="J186" s="4"/>
       <c r="K186" s="4"/>
     </row>
-    <row r="187" spans="1:11">
+    <row r="187" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A187" s="4" t="s">
         <v>288</v>
       </c>
@@ -7021,7 +7100,7 @@
       <c r="J187" s="4"/>
       <c r="K187" s="4"/>
     </row>
-    <row r="188" spans="1:11">
+    <row r="188" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A188" s="4" t="s">
         <v>288</v>
       </c>
@@ -7042,7 +7121,7 @@
       <c r="J188" s="4"/>
       <c r="K188" s="4"/>
     </row>
-    <row r="189" spans="1:11">
+    <row r="189" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A189" s="4" t="s">
         <v>288</v>
       </c>
@@ -7063,7 +7142,7 @@
       <c r="J189" s="4"/>
       <c r="K189" s="4"/>
     </row>
-    <row r="190" spans="1:11">
+    <row r="190" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A190" s="4" t="s">
         <v>288</v>
       </c>
@@ -7084,7 +7163,7 @@
       <c r="J190" s="4"/>
       <c r="K190" s="4"/>
     </row>
-    <row r="191" spans="1:11">
+    <row r="191" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A191" s="4" t="s">
         <v>288</v>
       </c>
@@ -7105,7 +7184,7 @@
       <c r="J191" s="4"/>
       <c r="K191" s="4"/>
     </row>
-    <row r="192" spans="1:11">
+    <row r="192" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A192" s="4" t="s">
         <v>288</v>
       </c>
@@ -7126,7 +7205,7 @@
       <c r="J192" s="4"/>
       <c r="K192" s="4"/>
     </row>
-    <row r="193" spans="1:11">
+    <row r="193" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A193" s="4" t="s">
         <v>288</v>
       </c>
@@ -7147,7 +7226,7 @@
       <c r="J193" s="4"/>
       <c r="K193" s="4"/>
     </row>
-    <row r="194" spans="1:11">
+    <row r="194" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A194" s="4" t="s">
         <v>288</v>
       </c>
@@ -7168,7 +7247,7 @@
       <c r="J194" s="4"/>
       <c r="K194" s="4"/>
     </row>
-    <row r="195" spans="1:11">
+    <row r="195" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A195" s="4" t="s">
         <v>288</v>
       </c>
@@ -7189,7 +7268,7 @@
       <c r="J195" s="4"/>
       <c r="K195" s="4"/>
     </row>
-    <row r="196" spans="1:11">
+    <row r="196" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A196" s="4" t="s">
         <v>288</v>
       </c>
@@ -7210,7 +7289,7 @@
       <c r="J196" s="4"/>
       <c r="K196" s="4"/>
     </row>
-    <row r="197" spans="1:11">
+    <row r="197" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A197" s="4" t="s">
         <v>409</v>
       </c>
@@ -7237,7 +7316,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="198" spans="1:11">
+    <row r="198" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A198" s="4" t="s">
         <v>409</v>
       </c>
@@ -7245,26 +7324,26 @@
         <v>410</v>
       </c>
       <c r="C198" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D198" s="4"/>
       <c r="E198" s="5" t="s">
-        <v>415</v>
+        <v>440</v>
       </c>
       <c r="F198" s="4"/>
       <c r="G198" s="4"/>
       <c r="H198" s="4"/>
       <c r="I198" s="4" t="s">
-        <v>416</v>
+        <v>441</v>
       </c>
       <c r="J198" s="4" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="K198" s="4" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="199" spans="1:11">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="199" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A199" s="4" t="s">
         <v>409</v>
       </c>
@@ -7272,26 +7351,26 @@
         <v>410</v>
       </c>
       <c r="C199" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D199" s="4"/>
       <c r="E199" s="5" t="s">
-        <v>418</v>
+        <v>458</v>
       </c>
       <c r="F199" s="4"/>
       <c r="G199" s="4"/>
       <c r="H199" s="4"/>
       <c r="I199" s="4" t="s">
-        <v>419</v>
+        <v>459</v>
       </c>
       <c r="J199" s="4" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="K199" s="4" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="200" spans="1:11">
+    <row r="200" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A200" s="4" t="s">
         <v>409</v>
       </c>
@@ -7299,179 +7378,179 @@
         <v>410</v>
       </c>
       <c r="C200" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D200" s="4"/>
       <c r="E200" s="5" t="s">
-        <v>421</v>
+        <v>477</v>
       </c>
       <c r="F200" s="4"/>
       <c r="G200" s="4"/>
       <c r="H200" s="4"/>
       <c r="I200" s="4" t="s">
-        <v>422</v>
+        <v>478</v>
       </c>
       <c r="J200" s="4" t="s">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="K200" s="4" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="201" spans="1:11">
+    <row r="201" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A201" s="4" t="s">
         <v>409</v>
       </c>
       <c r="B201" s="4" t="s">
-        <v>410</v>
+        <v>495</v>
       </c>
       <c r="C201" s="4">
         <v>1</v>
       </c>
       <c r="D201" s="4"/>
       <c r="E201" s="5" t="s">
-        <v>424</v>
+        <v>496</v>
       </c>
       <c r="F201" s="4"/>
       <c r="G201" s="4"/>
       <c r="H201" s="4"/>
       <c r="I201" s="4" t="s">
-        <v>425</v>
+        <v>497</v>
       </c>
       <c r="J201" s="4" t="s">
-        <v>426</v>
+        <v>413</v>
       </c>
       <c r="K201" s="4" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="202" spans="1:11">
+    <row r="202" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A202" s="4" t="s">
         <v>409</v>
       </c>
       <c r="B202" s="4" t="s">
-        <v>410</v>
+        <v>495</v>
       </c>
       <c r="C202" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D202" s="4"/>
       <c r="E202" s="5" t="s">
-        <v>428</v>
+        <v>514</v>
       </c>
       <c r="F202" s="4"/>
       <c r="G202" s="4"/>
       <c r="H202" s="4"/>
       <c r="I202" s="4" t="s">
-        <v>429</v>
+        <v>515</v>
       </c>
       <c r="J202" s="4" t="s">
-        <v>430</v>
+        <v>413</v>
       </c>
       <c r="K202" s="4" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="203" spans="1:11">
+    <row r="203" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A203" s="4" t="s">
         <v>409</v>
       </c>
       <c r="B203" s="4" t="s">
-        <v>410</v>
+        <v>495</v>
       </c>
       <c r="C203" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D203" s="4"/>
       <c r="E203" s="5" t="s">
-        <v>431</v>
+        <v>532</v>
       </c>
       <c r="F203" s="4"/>
       <c r="G203" s="4"/>
       <c r="H203" s="4"/>
       <c r="I203" s="4" t="s">
-        <v>432</v>
+        <v>533</v>
       </c>
       <c r="J203" s="4" t="s">
-        <v>433</v>
+        <v>413</v>
       </c>
       <c r="K203" s="4" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="204" spans="1:11">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="204" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A204" s="4" t="s">
         <v>409</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>410</v>
+        <v>495</v>
       </c>
       <c r="C204" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D204" s="4"/>
       <c r="E204" s="5" t="s">
-        <v>434</v>
+        <v>550</v>
       </c>
       <c r="F204" s="4"/>
       <c r="G204" s="4"/>
       <c r="H204" s="4"/>
       <c r="I204" s="4" t="s">
-        <v>435</v>
+        <v>551</v>
       </c>
       <c r="J204" s="4" t="s">
-        <v>436</v>
+        <v>413</v>
       </c>
       <c r="K204" s="4" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="205" spans="1:11">
+    <row r="205" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A205" s="4" t="s">
         <v>409</v>
       </c>
       <c r="B205" s="4" t="s">
-        <v>410</v>
+        <v>568</v>
       </c>
       <c r="C205" s="4">
         <v>1</v>
       </c>
       <c r="D205" s="4"/>
       <c r="E205" s="5" t="s">
-        <v>437</v>
+        <v>572</v>
       </c>
       <c r="F205" s="4"/>
       <c r="G205" s="4"/>
       <c r="H205" s="4"/>
       <c r="I205" s="4" t="s">
-        <v>438</v>
+        <v>573</v>
       </c>
       <c r="J205" s="4" t="s">
-        <v>439</v>
+        <v>413</v>
       </c>
       <c r="K205" s="4" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="206" spans="1:11">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="206" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A206" s="4" t="s">
         <v>409</v>
       </c>
       <c r="B206" s="4" t="s">
-        <v>410</v>
+        <v>568</v>
       </c>
       <c r="C206" s="4">
         <v>2</v>
       </c>
       <c r="D206" s="4"/>
       <c r="E206" s="5" t="s">
-        <v>440</v>
+        <v>588</v>
       </c>
       <c r="F206" s="4"/>
       <c r="G206" s="4"/>
       <c r="H206" s="4"/>
       <c r="I206" s="4" t="s">
-        <v>441</v>
+        <v>589</v>
       </c>
       <c r="J206" s="4" t="s">
         <v>413</v>
@@ -7480,7 +7559,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="207" spans="1:11">
+    <row r="207" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A207" s="4" t="s">
         <v>409</v>
       </c>
@@ -7488,17 +7567,17 @@
         <v>410</v>
       </c>
       <c r="C207" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D207" s="4"/>
       <c r="E207" s="5" t="s">
-        <v>442</v>
+        <v>415</v>
       </c>
       <c r="F207" s="4"/>
       <c r="G207" s="4"/>
       <c r="H207" s="4"/>
       <c r="I207" s="4" t="s">
-        <v>443</v>
+        <v>416</v>
       </c>
       <c r="J207" s="4" t="s">
         <v>417</v>
@@ -7507,7 +7586,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="208" spans="1:11">
+    <row r="208" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A208" s="4" t="s">
         <v>409</v>
       </c>
@@ -7519,22 +7598,22 @@
       </c>
       <c r="D208" s="4"/>
       <c r="E208" s="5" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="F208" s="4"/>
       <c r="G208" s="4"/>
       <c r="H208" s="4"/>
       <c r="I208" s="4" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="J208" s="4" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="K208" s="4" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="209" spans="1:11">
+    <row r="209" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A209" s="4" t="s">
         <v>409</v>
       </c>
@@ -7542,26 +7621,26 @@
         <v>410</v>
       </c>
       <c r="C209" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D209" s="4"/>
       <c r="E209" s="5" t="s">
-        <v>446</v>
+        <v>460</v>
       </c>
       <c r="F209" s="4"/>
       <c r="G209" s="4"/>
       <c r="H209" s="4"/>
       <c r="I209" s="4" t="s">
-        <v>447</v>
+        <v>461</v>
       </c>
       <c r="J209" s="4" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="K209" s="4" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="210" spans="1:11">
+    <row r="210" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A210" s="4" t="s">
         <v>409</v>
       </c>
@@ -7569,179 +7648,179 @@
         <v>410</v>
       </c>
       <c r="C210" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D210" s="4"/>
       <c r="E210" s="5" t="s">
-        <v>448</v>
+        <v>479</v>
       </c>
       <c r="F210" s="4"/>
       <c r="G210" s="4"/>
       <c r="H210" s="4"/>
-      <c r="I210" s="6" t="s">
-        <v>449</v>
+      <c r="I210" s="4" t="s">
+        <v>480</v>
       </c>
       <c r="J210" s="4" t="s">
-        <v>426</v>
+        <v>417</v>
       </c>
       <c r="K210" s="4" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="211" spans="1:11">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="211" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A211" s="4" t="s">
         <v>409</v>
       </c>
       <c r="B211" s="4" t="s">
-        <v>410</v>
+        <v>495</v>
       </c>
       <c r="C211" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D211" s="4"/>
       <c r="E211" s="5" t="s">
-        <v>450</v>
+        <v>498</v>
       </c>
       <c r="F211" s="4"/>
       <c r="G211" s="4"/>
       <c r="H211" s="4"/>
       <c r="I211" s="4" t="s">
-        <v>451</v>
+        <v>499</v>
       </c>
       <c r="J211" s="4" t="s">
-        <v>430</v>
+        <v>417</v>
       </c>
       <c r="K211" s="4" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="212" spans="1:11">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="212" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A212" s="4" t="s">
         <v>409</v>
       </c>
       <c r="B212" s="4" t="s">
-        <v>410</v>
+        <v>495</v>
       </c>
       <c r="C212" s="4">
         <v>2</v>
       </c>
       <c r="D212" s="4"/>
       <c r="E212" s="5" t="s">
-        <v>452</v>
+        <v>516</v>
       </c>
       <c r="F212" s="4"/>
       <c r="G212" s="4"/>
       <c r="H212" s="4"/>
       <c r="I212" s="4" t="s">
-        <v>453</v>
+        <v>517</v>
       </c>
       <c r="J212" s="4" t="s">
-        <v>433</v>
+        <v>417</v>
       </c>
       <c r="K212" s="4" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="213" spans="1:11">
+    <row r="213" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A213" s="4" t="s">
         <v>409</v>
       </c>
       <c r="B213" s="4" t="s">
-        <v>410</v>
+        <v>495</v>
       </c>
       <c r="C213" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D213" s="4"/>
       <c r="E213" s="5" t="s">
-        <v>454</v>
+        <v>534</v>
       </c>
       <c r="F213" s="4"/>
       <c r="G213" s="4"/>
       <c r="H213" s="4"/>
       <c r="I213" s="4" t="s">
-        <v>455</v>
+        <v>535</v>
       </c>
       <c r="J213" s="4" t="s">
-        <v>436</v>
+        <v>417</v>
       </c>
       <c r="K213" s="4" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="214" spans="1:11">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="214" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A214" s="4" t="s">
         <v>409</v>
       </c>
       <c r="B214" s="4" t="s">
-        <v>410</v>
+        <v>495</v>
       </c>
       <c r="C214" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D214" s="4"/>
       <c r="E214" s="5" t="s">
-        <v>456</v>
+        <v>552</v>
       </c>
       <c r="F214" s="4"/>
       <c r="G214" s="4"/>
       <c r="H214" s="4"/>
       <c r="I214" s="4" t="s">
-        <v>457</v>
+        <v>553</v>
       </c>
       <c r="J214" s="4" t="s">
-        <v>439</v>
+        <v>417</v>
       </c>
       <c r="K214" s="4" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="215" spans="1:11">
+    <row r="215" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A215" s="4" t="s">
         <v>409</v>
       </c>
       <c r="B215" s="4" t="s">
-        <v>410</v>
+        <v>568</v>
       </c>
       <c r="C215" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D215" s="4"/>
       <c r="E215" s="5" t="s">
-        <v>458</v>
+        <v>574</v>
       </c>
       <c r="F215" s="4"/>
       <c r="G215" s="4"/>
       <c r="H215" s="4"/>
       <c r="I215" s="4" t="s">
-        <v>459</v>
+        <v>575</v>
       </c>
       <c r="J215" s="4" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="K215" s="4" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="216" spans="1:11">
+    <row r="216" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A216" s="4" t="s">
         <v>409</v>
       </c>
       <c r="B216" s="4" t="s">
-        <v>410</v>
+        <v>568</v>
       </c>
       <c r="C216" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D216" s="4"/>
       <c r="E216" s="5" t="s">
-        <v>460</v>
+        <v>590</v>
       </c>
       <c r="F216" s="4"/>
       <c r="G216" s="4"/>
       <c r="H216" s="4"/>
       <c r="I216" s="4" t="s">
-        <v>461</v>
+        <v>591</v>
       </c>
       <c r="J216" s="4" t="s">
         <v>417</v>
@@ -7750,223 +7829,199 @@
         <v>414</v>
       </c>
     </row>
-    <row r="217" spans="1:11">
+    <row r="217" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A217" s="4" t="s">
         <v>409</v>
       </c>
       <c r="B217" s="4" t="s">
-        <v>410</v>
+        <v>568</v>
       </c>
       <c r="C217" s="4">
         <v>3</v>
       </c>
       <c r="D217" s="4"/>
       <c r="E217" s="5" t="s">
-        <v>462</v>
+        <v>604</v>
       </c>
       <c r="F217" s="4"/>
       <c r="G217" s="4"/>
       <c r="H217" s="4"/>
-      <c r="I217" s="4" t="s">
-        <v>463</v>
+      <c r="I217" s="6" t="s">
+        <v>605</v>
       </c>
       <c r="J217" s="4" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="K217" s="4" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="218" spans="1:11">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="218" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A218" s="4" t="s">
         <v>409</v>
       </c>
       <c r="B218" s="4" t="s">
-        <v>410</v>
+        <v>568</v>
       </c>
       <c r="C218" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D218" s="4"/>
       <c r="E218" s="5" t="s">
-        <v>464</v>
+        <v>620</v>
       </c>
       <c r="F218" s="4"/>
       <c r="G218" s="4"/>
       <c r="H218" s="4"/>
       <c r="I218" s="4" t="s">
-        <v>465</v>
+        <v>621</v>
       </c>
       <c r="J218" s="4" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="K218" s="4" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="219" spans="1:11">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="219" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A219" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="B219" s="4" t="s">
-        <v>410</v>
-      </c>
-      <c r="C219" s="4">
-        <v>3</v>
-      </c>
+      <c r="B219" s="4"/>
+      <c r="C219" s="4"/>
       <c r="D219" s="4"/>
       <c r="E219" s="5" t="s">
-        <v>466</v>
+        <v>634</v>
       </c>
       <c r="F219" s="4"/>
       <c r="G219" s="4"/>
       <c r="H219" s="4"/>
-      <c r="I219" s="6" t="s">
-        <v>467</v>
+      <c r="I219" s="4" t="s">
+        <v>635</v>
       </c>
       <c r="J219" s="4" t="s">
-        <v>426</v>
+        <v>417</v>
       </c>
       <c r="K219" s="4" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="220" spans="1:11">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="220" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A220" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="B220" s="4" t="s">
-        <v>410</v>
-      </c>
-      <c r="C220" s="4">
-        <v>3</v>
-      </c>
+      <c r="B220" s="4"/>
+      <c r="C220" s="4"/>
       <c r="D220" s="4"/>
       <c r="E220" s="5" t="s">
-        <v>468</v>
+        <v>636</v>
       </c>
       <c r="F220" s="4"/>
       <c r="G220" s="4"/>
       <c r="H220" s="4"/>
       <c r="I220" s="4" t="s">
-        <v>469</v>
+        <v>637</v>
       </c>
       <c r="J220" s="4" t="s">
-        <v>430</v>
+        <v>417</v>
       </c>
       <c r="K220" s="4" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="221" spans="1:11">
+    <row r="221" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A221" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="B221" s="4" t="s">
-        <v>410</v>
-      </c>
-      <c r="C221" s="4">
-        <v>3</v>
-      </c>
+      <c r="B221" s="4"/>
+      <c r="C221" s="4"/>
       <c r="D221" s="4"/>
       <c r="E221" s="5" t="s">
-        <v>470</v>
+        <v>638</v>
       </c>
       <c r="F221" s="4"/>
       <c r="G221" s="4"/>
       <c r="H221" s="4"/>
       <c r="I221" s="4" t="s">
-        <v>471</v>
+        <v>639</v>
       </c>
       <c r="J221" s="4" t="s">
-        <v>433</v>
+        <v>417</v>
       </c>
       <c r="K221" s="4" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="222" spans="1:11">
+    <row r="222" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A222" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="B222" s="4" t="s">
-        <v>410</v>
-      </c>
-      <c r="C222" s="4">
-        <v>3</v>
-      </c>
+      <c r="B222" s="4"/>
+      <c r="C222" s="4"/>
       <c r="D222" s="4"/>
       <c r="E222" s="5" t="s">
-        <v>472</v>
+        <v>640</v>
       </c>
       <c r="F222" s="4"/>
       <c r="G222" s="4"/>
       <c r="H222" s="4"/>
       <c r="I222" s="4" t="s">
-        <v>473</v>
+        <v>641</v>
       </c>
       <c r="J222" s="4" t="s">
-        <v>436</v>
+        <v>417</v>
       </c>
       <c r="K222" s="4" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="223" spans="1:11">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="223" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A223" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="B223" s="4" t="s">
-        <v>410</v>
-      </c>
-      <c r="C223" s="4">
-        <v>3</v>
-      </c>
+      <c r="B223" s="4"/>
+      <c r="C223" s="4"/>
       <c r="D223" s="4"/>
       <c r="E223" s="5" t="s">
-        <v>474</v>
+        <v>642</v>
       </c>
       <c r="F223" s="4"/>
       <c r="G223" s="4"/>
       <c r="H223" s="4"/>
       <c r="I223" s="4" t="s">
-        <v>475</v>
+        <v>643</v>
       </c>
       <c r="J223" s="4" t="s">
-        <v>476</v>
+        <v>417</v>
       </c>
       <c r="K223" s="4" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="224" spans="1:11">
+    <row r="224" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A224" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="B224" s="4" t="s">
-        <v>410</v>
-      </c>
-      <c r="C224" s="4">
-        <v>4</v>
-      </c>
+      <c r="B224" s="4"/>
+      <c r="C224" s="4"/>
       <c r="D224" s="4"/>
       <c r="E224" s="5" t="s">
-        <v>477</v>
+        <v>644</v>
       </c>
       <c r="F224" s="4"/>
       <c r="G224" s="4"/>
       <c r="H224" s="4"/>
       <c r="I224" s="4" t="s">
-        <v>478</v>
+        <v>645</v>
       </c>
       <c r="J224" s="4" t="s">
-        <v>413</v>
+        <v>646</v>
       </c>
       <c r="K224" s="4" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="225" spans="1:11">
+    <row r="225" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A225" s="4" t="s">
         <v>409</v>
       </c>
@@ -7974,26 +8029,26 @@
         <v>410</v>
       </c>
       <c r="C225" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D225" s="4"/>
       <c r="E225" s="5" t="s">
-        <v>479</v>
+        <v>418</v>
       </c>
       <c r="F225" s="4"/>
       <c r="G225" s="4"/>
       <c r="H225" s="4"/>
       <c r="I225" s="4" t="s">
-        <v>480</v>
+        <v>419</v>
       </c>
       <c r="J225" s="4" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="K225" s="4" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="226" spans="1:11">
+    <row r="226" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A226" s="4" t="s">
         <v>409</v>
       </c>
@@ -8001,17 +8056,17 @@
         <v>410</v>
       </c>
       <c r="C226" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D226" s="4"/>
       <c r="E226" s="5" t="s">
-        <v>481</v>
+        <v>444</v>
       </c>
       <c r="F226" s="4"/>
       <c r="G226" s="4"/>
       <c r="H226" s="4"/>
       <c r="I226" s="4" t="s">
-        <v>482</v>
+        <v>445</v>
       </c>
       <c r="J226" s="4" t="s">
         <v>420</v>
@@ -8020,7 +8075,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="227" spans="1:11">
+    <row r="227" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A227" s="4" t="s">
         <v>409</v>
       </c>
@@ -8028,26 +8083,26 @@
         <v>410</v>
       </c>
       <c r="C227" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D227" s="4"/>
       <c r="E227" s="5" t="s">
-        <v>483</v>
+        <v>462</v>
       </c>
       <c r="F227" s="4"/>
       <c r="G227" s="4"/>
       <c r="H227" s="4"/>
       <c r="I227" s="4" t="s">
-        <v>484</v>
+        <v>463</v>
       </c>
       <c r="J227" s="4" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="K227" s="4" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="228" spans="1:11">
+    <row r="228" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A228" s="4" t="s">
         <v>409</v>
       </c>
@@ -8059,373 +8114,369 @@
       </c>
       <c r="D228" s="4"/>
       <c r="E228" s="5" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="F228" s="4"/>
       <c r="G228" s="4"/>
       <c r="H228" s="4"/>
       <c r="I228" s="4" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="J228" s="4" t="s">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="K228" s="4" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="229" spans="1:11">
+    <row r="229" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A229" s="4" t="s">
         <v>409</v>
       </c>
       <c r="B229" s="4" t="s">
-        <v>410</v>
+        <v>495</v>
       </c>
       <c r="C229" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D229" s="4"/>
       <c r="E229" s="5" t="s">
-        <v>487</v>
+        <v>500</v>
       </c>
       <c r="F229" s="4"/>
       <c r="G229" s="4"/>
       <c r="H229" s="4"/>
       <c r="I229" s="4" t="s">
-        <v>488</v>
+        <v>501</v>
       </c>
       <c r="J229" s="4" t="s">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="K229" s="4" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="230" spans="1:11">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="230" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A230" s="4" t="s">
         <v>409</v>
       </c>
       <c r="B230" s="4" t="s">
-        <v>410</v>
+        <v>495</v>
       </c>
       <c r="C230" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D230" s="4"/>
       <c r="E230" s="5" t="s">
-        <v>489</v>
+        <v>518</v>
       </c>
       <c r="F230" s="4"/>
       <c r="G230" s="4"/>
       <c r="H230" s="4"/>
       <c r="I230" s="4" t="s">
-        <v>490</v>
+        <v>519</v>
       </c>
       <c r="J230" s="4" t="s">
-        <v>433</v>
+        <v>420</v>
       </c>
       <c r="K230" s="4" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="231" spans="1:11">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="231" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A231" s="4" t="s">
         <v>409</v>
       </c>
       <c r="B231" s="4" t="s">
-        <v>410</v>
+        <v>495</v>
       </c>
       <c r="C231" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D231" s="4"/>
       <c r="E231" s="5" t="s">
-        <v>491</v>
+        <v>536</v>
       </c>
       <c r="F231" s="4"/>
       <c r="G231" s="4"/>
       <c r="H231" s="4"/>
       <c r="I231" s="4" t="s">
-        <v>492</v>
+        <v>537</v>
       </c>
       <c r="J231" s="4" t="s">
-        <v>436</v>
+        <v>420</v>
       </c>
       <c r="K231" s="4" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="232" spans="1:11">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="232" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A232" s="4" t="s">
         <v>409</v>
       </c>
       <c r="B232" s="4" t="s">
-        <v>410</v>
+        <v>495</v>
       </c>
       <c r="C232" s="4">
         <v>4</v>
       </c>
       <c r="D232" s="4"/>
       <c r="E232" s="5" t="s">
-        <v>493</v>
+        <v>554</v>
       </c>
       <c r="F232" s="4"/>
       <c r="G232" s="4"/>
       <c r="H232" s="4"/>
       <c r="I232" s="4" t="s">
-        <v>494</v>
+        <v>555</v>
       </c>
       <c r="J232" s="4" t="s">
-        <v>476</v>
+        <v>420</v>
       </c>
       <c r="K232" s="4" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="233" spans="1:11">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="233" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A233" s="4" t="s">
         <v>409</v>
       </c>
       <c r="B233" s="4" t="s">
-        <v>495</v>
+        <v>568</v>
       </c>
       <c r="C233" s="4">
         <v>1</v>
       </c>
       <c r="D233" s="4"/>
       <c r="E233" s="5" t="s">
-        <v>496</v>
+        <v>576</v>
       </c>
       <c r="F233" s="4"/>
       <c r="G233" s="4"/>
       <c r="H233" s="4"/>
       <c r="I233" s="4" t="s">
-        <v>497</v>
+        <v>577</v>
       </c>
       <c r="J233" s="4" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="K233" s="4" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="234" spans="1:11">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="234" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A234" s="4" t="s">
         <v>409</v>
       </c>
       <c r="B234" s="4" t="s">
-        <v>495</v>
+        <v>568</v>
       </c>
       <c r="C234" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D234" s="4"/>
       <c r="E234" s="5" t="s">
-        <v>498</v>
+        <v>592</v>
       </c>
       <c r="F234" s="4"/>
       <c r="G234" s="4"/>
       <c r="H234" s="4"/>
       <c r="I234" s="4" t="s">
-        <v>499</v>
+        <v>593</v>
       </c>
       <c r="J234" s="4" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="K234" s="4" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="235" spans="1:11">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="235" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A235" s="4" t="s">
         <v>409</v>
       </c>
       <c r="B235" s="4" t="s">
-        <v>495</v>
+        <v>568</v>
       </c>
       <c r="C235" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D235" s="4"/>
       <c r="E235" s="5" t="s">
-        <v>500</v>
+        <v>606</v>
       </c>
       <c r="F235" s="4"/>
       <c r="G235" s="4"/>
       <c r="H235" s="4"/>
       <c r="I235" s="4" t="s">
-        <v>501</v>
+        <v>607</v>
       </c>
       <c r="J235" s="4" t="s">
         <v>420</v>
       </c>
       <c r="K235" s="4" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="236" spans="1:11">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="236" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A236" s="4" t="s">
         <v>409</v>
       </c>
       <c r="B236" s="4" t="s">
-        <v>495</v>
+        <v>568</v>
       </c>
       <c r="C236" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D236" s="4"/>
       <c r="E236" s="5" t="s">
-        <v>502</v>
+        <v>622</v>
       </c>
       <c r="F236" s="4"/>
       <c r="G236" s="4"/>
       <c r="H236" s="4"/>
       <c r="I236" s="4" t="s">
-        <v>503</v>
+        <v>623</v>
       </c>
       <c r="J236" s="4" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="K236" s="4" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="237" spans="1:11">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="237" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A237" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="B237" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="C237" s="4">
-        <v>1</v>
-      </c>
+      <c r="B237" s="4"/>
+      <c r="C237" s="4"/>
       <c r="D237" s="4"/>
       <c r="E237" s="5" t="s">
-        <v>504</v>
+        <v>647</v>
       </c>
       <c r="F237" s="4"/>
       <c r="G237" s="4"/>
       <c r="H237" s="4"/>
       <c r="I237" s="4" t="s">
-        <v>505</v>
+        <v>648</v>
       </c>
       <c r="J237" s="4" t="s">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="K237" s="4" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="238" spans="1:11">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="238" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A238" s="4" t="s">
         <v>409</v>
       </c>
       <c r="B238" s="4" t="s">
-        <v>495</v>
+        <v>410</v>
       </c>
       <c r="C238" s="4">
         <v>1</v>
       </c>
       <c r="D238" s="4"/>
       <c r="E238" s="5" t="s">
-        <v>506</v>
+        <v>421</v>
       </c>
       <c r="F238" s="4"/>
       <c r="G238" s="4"/>
       <c r="H238" s="4"/>
       <c r="I238" s="4" t="s">
-        <v>507</v>
+        <v>422</v>
       </c>
       <c r="J238" s="4" t="s">
-        <v>430</v>
+        <v>423</v>
       </c>
       <c r="K238" s="4" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="239" spans="1:11">
+    <row r="239" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A239" s="4" t="s">
         <v>409</v>
       </c>
       <c r="B239" s="4" t="s">
-        <v>495</v>
+        <v>410</v>
       </c>
       <c r="C239" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D239" s="4"/>
       <c r="E239" s="5" t="s">
-        <v>508</v>
+        <v>446</v>
       </c>
       <c r="F239" s="4"/>
       <c r="G239" s="4"/>
       <c r="H239" s="4"/>
       <c r="I239" s="4" t="s">
-        <v>509</v>
+        <v>447</v>
       </c>
       <c r="J239" s="4" t="s">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="K239" s="4" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="240" spans="1:11">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="240" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A240" s="4" t="s">
         <v>409</v>
       </c>
       <c r="B240" s="4" t="s">
-        <v>495</v>
+        <v>410</v>
       </c>
       <c r="C240" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D240" s="4"/>
       <c r="E240" s="5" t="s">
-        <v>510</v>
+        <v>464</v>
       </c>
       <c r="F240" s="4"/>
       <c r="G240" s="4"/>
       <c r="H240" s="4"/>
-      <c r="I240" s="6" t="s">
-        <v>511</v>
+      <c r="I240" s="4" t="s">
+        <v>465</v>
       </c>
       <c r="J240" s="4" t="s">
-        <v>436</v>
+        <v>423</v>
       </c>
       <c r="K240" s="4" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="241" spans="1:11">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="241" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A241" s="4" t="s">
         <v>409</v>
       </c>
       <c r="B241" s="4" t="s">
-        <v>495</v>
+        <v>410</v>
       </c>
       <c r="C241" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D241" s="4"/>
       <c r="E241" s="5" t="s">
-        <v>512</v>
+        <v>483</v>
       </c>
       <c r="F241" s="4"/>
       <c r="G241" s="4"/>
       <c r="H241" s="4"/>
       <c r="I241" s="4" t="s">
-        <v>513</v>
+        <v>484</v>
       </c>
       <c r="J241" s="4" t="s">
-        <v>476</v>
+        <v>423</v>
       </c>
       <c r="K241" s="4" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="242" spans="1:11">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="242" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A242" s="4" t="s">
         <v>409</v>
       </c>
@@ -8433,26 +8484,26 @@
         <v>495</v>
       </c>
       <c r="C242" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D242" s="4"/>
       <c r="E242" s="5" t="s">
-        <v>514</v>
+        <v>502</v>
       </c>
       <c r="F242" s="4"/>
       <c r="G242" s="4"/>
       <c r="H242" s="4"/>
       <c r="I242" s="4" t="s">
-        <v>515</v>
+        <v>503</v>
       </c>
       <c r="J242" s="4" t="s">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c r="K242" s="4" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="243" spans="1:11">
+    <row r="243" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A243" s="4" t="s">
         <v>409</v>
       </c>
@@ -8464,22 +8515,22 @@
       </c>
       <c r="D243" s="4"/>
       <c r="E243" s="5" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="F243" s="4"/>
       <c r="G243" s="4"/>
       <c r="H243" s="4"/>
       <c r="I243" s="4" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="J243" s="4" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="K243" s="4" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="244" spans="1:11">
+    <row r="244" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A244" s="4" t="s">
         <v>409</v>
       </c>
@@ -8487,26 +8538,26 @@
         <v>495</v>
       </c>
       <c r="C244" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D244" s="4"/>
       <c r="E244" s="5" t="s">
-        <v>518</v>
+        <v>538</v>
       </c>
       <c r="F244" s="4"/>
       <c r="G244" s="4"/>
       <c r="H244" s="4"/>
       <c r="I244" s="4" t="s">
-        <v>519</v>
+        <v>539</v>
       </c>
       <c r="J244" s="4" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="K244" s="4" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="245" spans="1:11">
+    <row r="245" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A245" s="4" t="s">
         <v>409</v>
       </c>
@@ -8514,17 +8565,17 @@
         <v>495</v>
       </c>
       <c r="C245" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D245" s="4"/>
       <c r="E245" s="5" t="s">
-        <v>520</v>
+        <v>556</v>
       </c>
       <c r="F245" s="4"/>
       <c r="G245" s="4"/>
       <c r="H245" s="4"/>
       <c r="I245" s="4" t="s">
-        <v>521</v>
+        <v>557</v>
       </c>
       <c r="J245" s="4" t="s">
         <v>423</v>
@@ -8533,511 +8584,479 @@
         <v>414</v>
       </c>
     </row>
-    <row r="246" spans="1:11">
+    <row r="246" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A246" s="4" t="s">
         <v>409</v>
       </c>
       <c r="B246" s="4" t="s">
-        <v>495</v>
+        <v>568</v>
       </c>
       <c r="C246" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D246" s="4"/>
       <c r="E246" s="5" t="s">
-        <v>522</v>
+        <v>578</v>
       </c>
       <c r="F246" s="4"/>
       <c r="G246" s="4"/>
       <c r="H246" s="4"/>
       <c r="I246" s="4" t="s">
-        <v>523</v>
+        <v>579</v>
       </c>
       <c r="J246" s="4" t="s">
-        <v>430</v>
+        <v>423</v>
       </c>
       <c r="K246" s="4" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="247" spans="1:11">
+    <row r="247" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A247" s="4" t="s">
         <v>409</v>
       </c>
       <c r="B247" s="4" t="s">
-        <v>495</v>
+        <v>568</v>
       </c>
       <c r="C247" s="4">
         <v>2</v>
       </c>
       <c r="D247" s="4"/>
       <c r="E247" s="5" t="s">
-        <v>524</v>
+        <v>594</v>
       </c>
       <c r="F247" s="4"/>
       <c r="G247" s="4"/>
       <c r="H247" s="4"/>
       <c r="I247" s="4" t="s">
-        <v>525</v>
+        <v>595</v>
       </c>
       <c r="J247" s="4" t="s">
-        <v>430</v>
+        <v>423</v>
       </c>
       <c r="K247" s="4" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="248" spans="1:11">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="248" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A248" s="4" t="s">
         <v>409</v>
       </c>
       <c r="B248" s="4" t="s">
-        <v>495</v>
+        <v>568</v>
       </c>
       <c r="C248" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D248" s="4"/>
       <c r="E248" s="5" t="s">
-        <v>526</v>
+        <v>608</v>
       </c>
       <c r="F248" s="4"/>
       <c r="G248" s="4"/>
       <c r="H248" s="4"/>
       <c r="I248" s="4" t="s">
-        <v>527</v>
+        <v>609</v>
       </c>
       <c r="J248" s="4" t="s">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="K248" s="4" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="249" spans="1:11">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="249" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A249" s="4" t="s">
         <v>409</v>
       </c>
       <c r="B249" s="4" t="s">
-        <v>495</v>
+        <v>568</v>
       </c>
       <c r="C249" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D249" s="4"/>
       <c r="E249" s="5" t="s">
-        <v>528</v>
+        <v>624</v>
       </c>
       <c r="F249" s="4"/>
       <c r="G249" s="4"/>
       <c r="H249" s="4"/>
       <c r="I249" s="4" t="s">
-        <v>529</v>
+        <v>625</v>
       </c>
       <c r="J249" s="4" t="s">
-        <v>436</v>
+        <v>423</v>
       </c>
       <c r="K249" s="4" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="250" spans="1:11">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="250" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A250" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="B250" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="C250" s="4">
-        <v>2</v>
-      </c>
+      <c r="B250" s="4"/>
+      <c r="C250" s="4"/>
       <c r="D250" s="4"/>
       <c r="E250" s="5" t="s">
-        <v>530</v>
+        <v>649</v>
       </c>
       <c r="F250" s="4"/>
       <c r="G250" s="4"/>
       <c r="H250" s="4"/>
       <c r="I250" s="4" t="s">
-        <v>531</v>
+        <v>650</v>
       </c>
       <c r="J250" s="4" t="s">
-        <v>476</v>
+        <v>423</v>
       </c>
       <c r="K250" s="4" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="251" spans="1:11">
+    <row r="251" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A251" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="B251" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="C251" s="4">
-        <v>3</v>
-      </c>
+      <c r="B251" s="4"/>
+      <c r="C251" s="4"/>
       <c r="D251" s="4"/>
       <c r="E251" s="5" t="s">
-        <v>532</v>
+        <v>651</v>
       </c>
       <c r="F251" s="4"/>
       <c r="G251" s="4"/>
       <c r="H251" s="4"/>
       <c r="I251" s="4" t="s">
-        <v>533</v>
+        <v>652</v>
       </c>
       <c r="J251" s="4" t="s">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c r="K251" s="4" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="252" spans="1:11">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="252" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A252" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="B252" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="C252" s="4">
-        <v>3</v>
-      </c>
+      <c r="B252" s="4"/>
+      <c r="C252" s="4"/>
       <c r="D252" s="4"/>
       <c r="E252" s="5" t="s">
-        <v>534</v>
+        <v>653</v>
       </c>
       <c r="F252" s="4"/>
       <c r="G252" s="4"/>
       <c r="H252" s="4"/>
       <c r="I252" s="4" t="s">
-        <v>535</v>
+        <v>654</v>
       </c>
       <c r="J252" s="4" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="K252" s="4" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="253" spans="1:11">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="253" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A253" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="B253" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="C253" s="4">
-        <v>3</v>
-      </c>
+      <c r="B253" s="4"/>
+      <c r="C253" s="4"/>
       <c r="D253" s="4"/>
       <c r="E253" s="5" t="s">
-        <v>536</v>
+        <v>655</v>
       </c>
       <c r="F253" s="4"/>
       <c r="G253" s="4"/>
       <c r="H253" s="4"/>
       <c r="I253" s="4" t="s">
-        <v>537</v>
+        <v>656</v>
       </c>
       <c r="J253" s="4" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="K253" s="4" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="254" spans="1:11">
+    <row r="254" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A254" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="B254" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="C254" s="4">
-        <v>3</v>
-      </c>
+      <c r="B254" s="4"/>
+      <c r="C254" s="4"/>
       <c r="D254" s="4"/>
       <c r="E254" s="5" t="s">
-        <v>538</v>
+        <v>657</v>
       </c>
       <c r="F254" s="4"/>
       <c r="G254" s="4"/>
       <c r="H254" s="4"/>
       <c r="I254" s="4" t="s">
-        <v>539</v>
+        <v>658</v>
       </c>
       <c r="J254" s="4" t="s">
         <v>423</v>
       </c>
       <c r="K254" s="4" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="255" spans="1:11">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="255" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A255" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="B255" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="C255" s="4">
-        <v>3</v>
-      </c>
+      <c r="B255" s="4"/>
+      <c r="C255" s="4"/>
       <c r="D255" s="4"/>
       <c r="E255" s="5" t="s">
-        <v>540</v>
+        <v>659</v>
       </c>
       <c r="F255" s="4"/>
       <c r="G255" s="4"/>
       <c r="H255" s="4"/>
       <c r="I255" s="4" t="s">
-        <v>541</v>
+        <v>660</v>
       </c>
       <c r="J255" s="4" t="s">
-        <v>430</v>
+        <v>423</v>
       </c>
       <c r="K255" s="4" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="256" spans="1:11">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="256" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A256" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="B256" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="C256" s="4">
-        <v>3</v>
-      </c>
+      <c r="B256" s="4"/>
+      <c r="C256" s="4"/>
       <c r="D256" s="4"/>
       <c r="E256" s="5" t="s">
-        <v>542</v>
+        <v>661</v>
       </c>
       <c r="F256" s="4"/>
       <c r="G256" s="4"/>
       <c r="H256" s="4"/>
       <c r="I256" s="4" t="s">
-        <v>543</v>
+        <v>662</v>
       </c>
       <c r="J256" s="4" t="s">
-        <v>430</v>
+        <v>423</v>
       </c>
       <c r="K256" s="4" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="257" spans="1:11">
+    <row r="257" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A257" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="B257" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="C257" s="4">
-        <v>3</v>
-      </c>
+      <c r="B257" s="4"/>
+      <c r="C257" s="4"/>
       <c r="D257" s="4"/>
       <c r="E257" s="5" t="s">
-        <v>544</v>
+        <v>663</v>
       </c>
       <c r="F257" s="4"/>
       <c r="G257" s="4"/>
       <c r="H257" s="4"/>
       <c r="I257" s="4" t="s">
-        <v>545</v>
+        <v>664</v>
       </c>
       <c r="J257" s="4" t="s">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="K257" s="4" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="258" spans="1:11">
+    <row r="258" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A258" s="4" t="s">
         <v>409</v>
       </c>
       <c r="B258" s="4" t="s">
-        <v>495</v>
+        <v>410</v>
       </c>
       <c r="C258" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D258" s="4"/>
       <c r="E258" s="5" t="s">
-        <v>546</v>
+        <v>424</v>
       </c>
       <c r="F258" s="4"/>
       <c r="G258" s="4"/>
       <c r="H258" s="4"/>
       <c r="I258" s="4" t="s">
-        <v>547</v>
+        <v>425</v>
       </c>
       <c r="J258" s="4" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="K258" s="4" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="259" spans="1:11">
+    <row r="259" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A259" s="4" t="s">
         <v>409</v>
       </c>
       <c r="B259" s="4" t="s">
-        <v>495</v>
+        <v>410</v>
       </c>
       <c r="C259" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D259" s="4"/>
       <c r="E259" s="5" t="s">
-        <v>548</v>
+        <v>448</v>
       </c>
       <c r="F259" s="4"/>
       <c r="G259" s="4"/>
       <c r="H259" s="4"/>
-      <c r="I259" s="4" t="s">
-        <v>549</v>
+      <c r="I259" s="6" t="s">
+        <v>449</v>
       </c>
       <c r="J259" s="4" t="s">
-        <v>476</v>
+        <v>426</v>
       </c>
       <c r="K259" s="4" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="260" spans="1:11">
+    <row r="260" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A260" s="4" t="s">
         <v>409</v>
       </c>
       <c r="B260" s="4" t="s">
-        <v>495</v>
+        <v>410</v>
       </c>
       <c r="C260" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D260" s="4"/>
       <c r="E260" s="5" t="s">
-        <v>550</v>
+        <v>466</v>
       </c>
       <c r="F260" s="4"/>
       <c r="G260" s="4"/>
       <c r="H260" s="4"/>
-      <c r="I260" s="4" t="s">
-        <v>551</v>
+      <c r="I260" s="6" t="s">
+        <v>467</v>
       </c>
       <c r="J260" s="4" t="s">
-        <v>413</v>
+        <v>426</v>
       </c>
       <c r="K260" s="4" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="261" spans="1:11">
+    <row r="261" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A261" s="4" t="s">
         <v>409</v>
       </c>
       <c r="B261" s="4" t="s">
-        <v>495</v>
+        <v>410</v>
       </c>
       <c r="C261" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D261" s="4"/>
       <c r="E261" s="5" t="s">
-        <v>552</v>
+        <v>428</v>
       </c>
       <c r="F261" s="4"/>
       <c r="G261" s="4"/>
       <c r="H261" s="4"/>
       <c r="I261" s="4" t="s">
-        <v>553</v>
+        <v>429</v>
       </c>
       <c r="J261" s="4" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="K261" s="4" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="262" spans="1:11">
+    <row r="262" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A262" s="4" t="s">
         <v>409</v>
       </c>
       <c r="B262" s="4" t="s">
-        <v>495</v>
+        <v>410</v>
       </c>
       <c r="C262" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D262" s="4"/>
       <c r="E262" s="5" t="s">
-        <v>554</v>
+        <v>450</v>
       </c>
       <c r="F262" s="4"/>
       <c r="G262" s="4"/>
       <c r="H262" s="4"/>
       <c r="I262" s="4" t="s">
-        <v>555</v>
+        <v>451</v>
       </c>
       <c r="J262" s="4" t="s">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="K262" s="4" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="263" spans="1:11">
+    <row r="263" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A263" s="4" t="s">
         <v>409</v>
       </c>
       <c r="B263" s="4" t="s">
-        <v>495</v>
+        <v>410</v>
       </c>
       <c r="C263" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D263" s="4"/>
       <c r="E263" s="5" t="s">
-        <v>556</v>
+        <v>468</v>
       </c>
       <c r="F263" s="4"/>
       <c r="G263" s="4"/>
       <c r="H263" s="4"/>
       <c r="I263" s="4" t="s">
-        <v>557</v>
+        <v>469</v>
       </c>
       <c r="J263" s="4" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="K263" s="4" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="264" spans="1:11">
+    <row r="264" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A264" s="4" t="s">
         <v>409</v>
       </c>
       <c r="B264" s="4" t="s">
-        <v>495</v>
+        <v>410</v>
       </c>
       <c r="C264" s="4">
         <v>4</v>
       </c>
       <c r="D264" s="4"/>
       <c r="E264" s="5" t="s">
-        <v>558</v>
+        <v>485</v>
       </c>
       <c r="F264" s="4"/>
       <c r="G264" s="4"/>
       <c r="H264" s="4"/>
       <c r="I264" s="4" t="s">
-        <v>559</v>
+        <v>486</v>
       </c>
       <c r="J264" s="4" t="s">
         <v>430</v>
@@ -9046,25 +9065,25 @@
         <v>414</v>
       </c>
     </row>
-    <row r="265" spans="1:11">
+    <row r="265" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A265" s="4" t="s">
         <v>409</v>
       </c>
       <c r="B265" s="4" t="s">
-        <v>495</v>
+        <v>410</v>
       </c>
       <c r="C265" s="4">
         <v>4</v>
       </c>
       <c r="D265" s="4"/>
       <c r="E265" s="5" t="s">
-        <v>560</v>
+        <v>487</v>
       </c>
       <c r="F265" s="4"/>
       <c r="G265" s="4"/>
       <c r="H265" s="4"/>
-      <c r="I265" s="6" t="s">
-        <v>561</v>
+      <c r="I265" s="4" t="s">
+        <v>488</v>
       </c>
       <c r="J265" s="4" t="s">
         <v>430</v>
@@ -9073,7 +9092,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="266" spans="1:11">
+    <row r="266" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A266" s="4" t="s">
         <v>409</v>
       </c>
@@ -9081,26 +9100,26 @@
         <v>495</v>
       </c>
       <c r="C266" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D266" s="4"/>
       <c r="E266" s="5" t="s">
-        <v>562</v>
+        <v>504</v>
       </c>
       <c r="F266" s="4"/>
       <c r="G266" s="4"/>
       <c r="H266" s="4"/>
       <c r="I266" s="4" t="s">
-        <v>563</v>
+        <v>505</v>
       </c>
       <c r="J266" s="4" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="K266" s="4" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="267" spans="1:11">
+    <row r="267" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A267" s="4" t="s">
         <v>409</v>
       </c>
@@ -9108,26 +9127,26 @@
         <v>495</v>
       </c>
       <c r="C267" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D267" s="4"/>
       <c r="E267" s="5" t="s">
-        <v>564</v>
+        <v>506</v>
       </c>
       <c r="F267" s="4"/>
       <c r="G267" s="4"/>
       <c r="H267" s="4"/>
-      <c r="I267" s="6" t="s">
-        <v>565</v>
+      <c r="I267" s="4" t="s">
+        <v>507</v>
       </c>
       <c r="J267" s="4" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="K267" s="4" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="268" spans="1:11">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="268" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A268" s="4" t="s">
         <v>409</v>
       </c>
@@ -9135,161 +9154,161 @@
         <v>495</v>
       </c>
       <c r="C268" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D268" s="4"/>
       <c r="E268" s="5" t="s">
-        <v>566</v>
+        <v>522</v>
       </c>
       <c r="F268" s="4"/>
       <c r="G268" s="4"/>
       <c r="H268" s="4"/>
       <c r="I268" s="4" t="s">
-        <v>567</v>
+        <v>523</v>
       </c>
       <c r="J268" s="4" t="s">
-        <v>476</v>
+        <v>430</v>
       </c>
       <c r="K268" s="4" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="269" spans="1:11">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="269" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A269" s="4" t="s">
         <v>409</v>
       </c>
       <c r="B269" s="4" t="s">
-        <v>568</v>
+        <v>495</v>
       </c>
       <c r="C269" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D269" s="4"/>
       <c r="E269" s="5" t="s">
-        <v>569</v>
+        <v>524</v>
       </c>
       <c r="F269" s="4"/>
       <c r="G269" s="4"/>
       <c r="H269" s="4"/>
       <c r="I269" s="4" t="s">
-        <v>570</v>
+        <v>525</v>
       </c>
       <c r="J269" s="4" t="s">
-        <v>571</v>
+        <v>430</v>
       </c>
       <c r="K269" s="4" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="270" spans="1:11">
+    <row r="270" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A270" s="4" t="s">
         <v>409</v>
       </c>
       <c r="B270" s="4" t="s">
-        <v>568</v>
+        <v>495</v>
       </c>
       <c r="C270" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D270" s="4"/>
       <c r="E270" s="5" t="s">
-        <v>572</v>
+        <v>540</v>
       </c>
       <c r="F270" s="4"/>
       <c r="G270" s="4"/>
       <c r="H270" s="4"/>
       <c r="I270" s="4" t="s">
-        <v>573</v>
+        <v>541</v>
       </c>
       <c r="J270" s="4" t="s">
-        <v>413</v>
+        <v>430</v>
       </c>
       <c r="K270" s="4" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="271" spans="1:11">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="271" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A271" s="4" t="s">
         <v>409</v>
       </c>
       <c r="B271" s="4" t="s">
-        <v>568</v>
+        <v>495</v>
       </c>
       <c r="C271" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D271" s="4"/>
       <c r="E271" s="5" t="s">
-        <v>574</v>
+        <v>542</v>
       </c>
       <c r="F271" s="4"/>
       <c r="G271" s="4"/>
       <c r="H271" s="4"/>
       <c r="I271" s="4" t="s">
-        <v>575</v>
+        <v>543</v>
       </c>
       <c r="J271" s="4" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="K271" s="4" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="272" spans="1:11">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="272" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A272" s="4" t="s">
         <v>409</v>
       </c>
       <c r="B272" s="4" t="s">
-        <v>568</v>
+        <v>495</v>
       </c>
       <c r="C272" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D272" s="4"/>
       <c r="E272" s="5" t="s">
-        <v>576</v>
+        <v>558</v>
       </c>
       <c r="F272" s="4"/>
       <c r="G272" s="4"/>
       <c r="H272" s="4"/>
       <c r="I272" s="4" t="s">
-        <v>577</v>
+        <v>559</v>
       </c>
       <c r="J272" s="4" t="s">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="K272" s="4" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="273" spans="1:11">
+    <row r="273" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A273" s="4" t="s">
         <v>409</v>
       </c>
       <c r="B273" s="4" t="s">
-        <v>568</v>
+        <v>495</v>
       </c>
       <c r="C273" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D273" s="4"/>
       <c r="E273" s="5" t="s">
-        <v>578</v>
+        <v>560</v>
       </c>
       <c r="F273" s="4"/>
       <c r="G273" s="4"/>
       <c r="H273" s="4"/>
-      <c r="I273" s="4" t="s">
-        <v>579</v>
+      <c r="I273" s="6" t="s">
+        <v>561</v>
       </c>
       <c r="J273" s="4" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="K273" s="4" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="274" spans="1:11">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="274" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A274" s="4" t="s">
         <v>409</v>
       </c>
@@ -9316,7 +9335,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="275" spans="1:11">
+    <row r="275" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A275" s="4" t="s">
         <v>409</v>
       </c>
@@ -9343,7 +9362,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="276" spans="1:11">
+    <row r="276" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A276" s="4" t="s">
         <v>409</v>
       </c>
@@ -9351,26 +9370,26 @@
         <v>568</v>
       </c>
       <c r="C276" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D276" s="4"/>
       <c r="E276" s="5" t="s">
-        <v>584</v>
+        <v>596</v>
       </c>
       <c r="F276" s="4"/>
       <c r="G276" s="4"/>
       <c r="H276" s="4"/>
       <c r="I276" s="4" t="s">
-        <v>585</v>
+        <v>597</v>
       </c>
       <c r="J276" s="4" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="K276" s="4" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="277" spans="1:11">
+    <row r="277" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A277" s="4" t="s">
         <v>409</v>
       </c>
@@ -9378,26 +9397,26 @@
         <v>568</v>
       </c>
       <c r="C277" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D277" s="4"/>
       <c r="E277" s="5" t="s">
-        <v>586</v>
+        <v>610</v>
       </c>
       <c r="F277" s="4"/>
       <c r="G277" s="4"/>
       <c r="H277" s="4"/>
       <c r="I277" s="4" t="s">
-        <v>587</v>
+        <v>611</v>
       </c>
       <c r="J277" s="4" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="K277" s="4" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="278" spans="1:11">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="278" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A278" s="4" t="s">
         <v>409</v>
       </c>
@@ -9405,26 +9424,26 @@
         <v>568</v>
       </c>
       <c r="C278" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D278" s="4"/>
       <c r="E278" s="5" t="s">
-        <v>588</v>
+        <v>626</v>
       </c>
       <c r="F278" s="4"/>
       <c r="G278" s="4"/>
       <c r="H278" s="4"/>
       <c r="I278" s="4" t="s">
-        <v>589</v>
+        <v>627</v>
       </c>
       <c r="J278" s="4" t="s">
-        <v>413</v>
+        <v>430</v>
       </c>
       <c r="K278" s="4" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="279" spans="1:11">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="279" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A279" s="4" t="s">
         <v>409</v>
       </c>
@@ -9432,26 +9451,26 @@
         <v>568</v>
       </c>
       <c r="C279" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D279" s="4"/>
       <c r="E279" s="5" t="s">
-        <v>590</v>
+        <v>569</v>
       </c>
       <c r="F279" s="4"/>
       <c r="G279" s="4"/>
       <c r="H279" s="4"/>
       <c r="I279" s="4" t="s">
-        <v>591</v>
+        <v>570</v>
       </c>
       <c r="J279" s="4" t="s">
-        <v>417</v>
+        <v>571</v>
       </c>
       <c r="K279" s="4" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="280" spans="1:11">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="280" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A280" s="4" t="s">
         <v>409</v>
       </c>
@@ -9463,22 +9482,22 @@
       </c>
       <c r="D280" s="4"/>
       <c r="E280" s="5" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="F280" s="4"/>
       <c r="G280" s="4"/>
       <c r="H280" s="4"/>
       <c r="I280" s="4" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="J280" s="4" t="s">
-        <v>420</v>
+        <v>571</v>
       </c>
       <c r="K280" s="4" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="281" spans="1:11">
+    <row r="281" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A281" s="4" t="s">
         <v>409</v>
       </c>
@@ -9486,26 +9505,26 @@
         <v>568</v>
       </c>
       <c r="C281" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D281" s="4"/>
       <c r="E281" s="5" t="s">
-        <v>594</v>
+        <v>612</v>
       </c>
       <c r="F281" s="4"/>
       <c r="G281" s="4"/>
       <c r="H281" s="4"/>
       <c r="I281" s="4" t="s">
-        <v>595</v>
+        <v>613</v>
       </c>
       <c r="J281" s="4" t="s">
-        <v>423</v>
+        <v>571</v>
       </c>
       <c r="K281" s="4" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="282" spans="1:11">
+    <row r="282" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A282" s="4" t="s">
         <v>409</v>
       </c>
@@ -9513,476 +9532,468 @@
         <v>568</v>
       </c>
       <c r="C282" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D282" s="4"/>
       <c r="E282" s="5" t="s">
-        <v>596</v>
+        <v>628</v>
       </c>
       <c r="F282" s="4"/>
       <c r="G282" s="4"/>
       <c r="H282" s="4"/>
       <c r="I282" s="4" t="s">
-        <v>597</v>
+        <v>629</v>
       </c>
       <c r="J282" s="4" t="s">
-        <v>430</v>
+        <v>571</v>
       </c>
       <c r="K282" s="4" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="283" spans="1:11">
+    <row r="283" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A283" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="B283" s="4" t="s">
-        <v>568</v>
-      </c>
-      <c r="C283" s="4">
-        <v>2</v>
-      </c>
+      <c r="B283" s="4"/>
+      <c r="C283" s="4"/>
       <c r="D283" s="4"/>
       <c r="E283" s="5" t="s">
-        <v>598</v>
+        <v>665</v>
       </c>
       <c r="F283" s="4"/>
       <c r="G283" s="4"/>
       <c r="H283" s="4"/>
       <c r="I283" s="4" t="s">
-        <v>599</v>
+        <v>666</v>
       </c>
       <c r="J283" s="4" t="s">
         <v>571</v>
       </c>
       <c r="K283" s="4" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="284" spans="1:11">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="284" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A284" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="B284" s="4" t="s">
-        <v>568</v>
-      </c>
-      <c r="C284" s="4">
-        <v>2</v>
-      </c>
+      <c r="B284" s="4"/>
+      <c r="C284" s="4"/>
       <c r="D284" s="4"/>
       <c r="E284" s="5" t="s">
-        <v>600</v>
+        <v>667</v>
       </c>
       <c r="F284" s="4"/>
       <c r="G284" s="4"/>
       <c r="H284" s="4"/>
       <c r="I284" s="4" t="s">
-        <v>601</v>
+        <v>668</v>
       </c>
       <c r="J284" s="4" t="s">
-        <v>436</v>
+        <v>571</v>
       </c>
       <c r="K284" s="4" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="285" spans="1:11">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="285" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A285" s="4" t="s">
         <v>409</v>
       </c>
       <c r="B285" s="4" t="s">
-        <v>568</v>
+        <v>410</v>
       </c>
       <c r="C285" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D285" s="4"/>
       <c r="E285" s="5" t="s">
-        <v>602</v>
+        <v>431</v>
       </c>
       <c r="F285" s="4"/>
       <c r="G285" s="4"/>
       <c r="H285" s="4"/>
       <c r="I285" s="4" t="s">
-        <v>603</v>
+        <v>432</v>
       </c>
       <c r="J285" s="4" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="K285" s="4" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="286" spans="1:11">
+    <row r="286" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A286" s="4" t="s">
         <v>409</v>
       </c>
       <c r="B286" s="4" t="s">
-        <v>568</v>
+        <v>410</v>
       </c>
       <c r="C286" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D286" s="4"/>
       <c r="E286" s="5" t="s">
-        <v>604</v>
+        <v>452</v>
       </c>
       <c r="F286" s="4"/>
       <c r="G286" s="4"/>
       <c r="H286" s="4"/>
-      <c r="I286" s="6" t="s">
-        <v>605</v>
+      <c r="I286" s="4" t="s">
+        <v>453</v>
       </c>
       <c r="J286" s="4" t="s">
-        <v>417</v>
+        <v>433</v>
       </c>
       <c r="K286" s="4" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="287" spans="1:11">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="287" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A287" s="4" t="s">
         <v>409</v>
       </c>
       <c r="B287" s="4" t="s">
-        <v>568</v>
+        <v>410</v>
       </c>
       <c r="C287" s="4">
         <v>3</v>
       </c>
       <c r="D287" s="4"/>
       <c r="E287" s="5" t="s">
-        <v>606</v>
+        <v>470</v>
       </c>
       <c r="F287" s="4"/>
       <c r="G287" s="4"/>
       <c r="H287" s="4"/>
       <c r="I287" s="4" t="s">
-        <v>607</v>
+        <v>471</v>
       </c>
       <c r="J287" s="4" t="s">
-        <v>420</v>
+        <v>433</v>
       </c>
       <c r="K287" s="4" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="288" spans="1:11">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="288" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A288" s="4" t="s">
         <v>409</v>
       </c>
       <c r="B288" s="4" t="s">
-        <v>568</v>
+        <v>410</v>
       </c>
       <c r="C288" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D288" s="4"/>
       <c r="E288" s="5" t="s">
-        <v>608</v>
+        <v>489</v>
       </c>
       <c r="F288" s="4"/>
       <c r="G288" s="4"/>
       <c r="H288" s="4"/>
       <c r="I288" s="4" t="s">
-        <v>609</v>
+        <v>490</v>
       </c>
       <c r="J288" s="4" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="K288" s="4" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="289" spans="1:11">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="289" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A289" s="4" t="s">
         <v>409</v>
       </c>
       <c r="B289" s="4" t="s">
-        <v>568</v>
+        <v>495</v>
       </c>
       <c r="C289" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D289" s="4"/>
       <c r="E289" s="5" t="s">
-        <v>610</v>
+        <v>508</v>
       </c>
       <c r="F289" s="4"/>
       <c r="G289" s="4"/>
       <c r="H289" s="4"/>
       <c r="I289" s="4" t="s">
-        <v>611</v>
+        <v>509</v>
       </c>
       <c r="J289" s="4" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="K289" s="4" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="290" spans="1:11">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="290" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A290" s="4" t="s">
         <v>409</v>
       </c>
       <c r="B290" s="4" t="s">
-        <v>568</v>
+        <v>495</v>
       </c>
       <c r="C290" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D290" s="4"/>
       <c r="E290" s="5" t="s">
-        <v>612</v>
+        <v>526</v>
       </c>
       <c r="F290" s="4"/>
       <c r="G290" s="4"/>
       <c r="H290" s="4"/>
       <c r="I290" s="4" t="s">
-        <v>613</v>
+        <v>527</v>
       </c>
       <c r="J290" s="4" t="s">
-        <v>571</v>
+        <v>433</v>
       </c>
       <c r="K290" s="4" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="291" spans="1:11">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="291" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A291" s="4" t="s">
         <v>409</v>
       </c>
       <c r="B291" s="4" t="s">
-        <v>568</v>
+        <v>495</v>
       </c>
       <c r="C291" s="4">
         <v>3</v>
       </c>
       <c r="D291" s="4"/>
       <c r="E291" s="5" t="s">
-        <v>614</v>
+        <v>544</v>
       </c>
       <c r="F291" s="4"/>
       <c r="G291" s="4"/>
       <c r="H291" s="4"/>
       <c r="I291" s="4" t="s">
-        <v>615</v>
+        <v>545</v>
       </c>
       <c r="J291" s="4" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="K291" s="4" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="292" spans="1:11">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="292" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A292" s="4" t="s">
         <v>409</v>
       </c>
       <c r="B292" s="4" t="s">
-        <v>568</v>
+        <v>410</v>
       </c>
       <c r="C292" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D292" s="4"/>
       <c r="E292" s="5" t="s">
-        <v>616</v>
+        <v>434</v>
       </c>
       <c r="F292" s="4"/>
       <c r="G292" s="4"/>
       <c r="H292" s="4"/>
       <c r="I292" s="4" t="s">
-        <v>617</v>
+        <v>435</v>
       </c>
       <c r="J292" s="4" t="s">
         <v>436</v>
       </c>
       <c r="K292" s="4" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="293" spans="1:11">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="293" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A293" s="4" t="s">
         <v>409</v>
       </c>
       <c r="B293" s="4" t="s">
-        <v>568</v>
+        <v>410</v>
       </c>
       <c r="C293" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D293" s="4"/>
       <c r="E293" s="5" t="s">
-        <v>618</v>
+        <v>454</v>
       </c>
       <c r="F293" s="4"/>
       <c r="G293" s="4"/>
       <c r="H293" s="4"/>
       <c r="I293" s="4" t="s">
-        <v>619</v>
+        <v>455</v>
       </c>
       <c r="J293" s="4" t="s">
-        <v>476</v>
+        <v>436</v>
       </c>
       <c r="K293" s="4" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="294" spans="1:11">
+    <row r="294" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A294" s="4" t="s">
         <v>409</v>
       </c>
       <c r="B294" s="4" t="s">
-        <v>568</v>
+        <v>410</v>
       </c>
       <c r="C294" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D294" s="4"/>
       <c r="E294" s="5" t="s">
-        <v>620</v>
+        <v>472</v>
       </c>
       <c r="F294" s="4"/>
       <c r="G294" s="4"/>
       <c r="H294" s="4"/>
       <c r="I294" s="4" t="s">
-        <v>621</v>
+        <v>473</v>
       </c>
       <c r="J294" s="4" t="s">
-        <v>417</v>
+        <v>436</v>
       </c>
       <c r="K294" s="4" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="295" spans="1:11">
+    <row r="295" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A295" s="4" t="s">
         <v>409</v>
       </c>
       <c r="B295" s="4" t="s">
-        <v>568</v>
+        <v>410</v>
       </c>
       <c r="C295" s="4">
         <v>4</v>
       </c>
       <c r="D295" s="4"/>
       <c r="E295" s="5" t="s">
-        <v>622</v>
+        <v>491</v>
       </c>
       <c r="F295" s="4"/>
       <c r="G295" s="4"/>
       <c r="H295" s="4"/>
       <c r="I295" s="4" t="s">
-        <v>623</v>
+        <v>492</v>
       </c>
       <c r="J295" s="4" t="s">
-        <v>420</v>
+        <v>436</v>
       </c>
       <c r="K295" s="4" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="296" spans="1:11">
+    <row r="296" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A296" s="4" t="s">
         <v>409</v>
       </c>
       <c r="B296" s="4" t="s">
-        <v>568</v>
+        <v>495</v>
       </c>
       <c r="C296" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D296" s="4"/>
       <c r="E296" s="5" t="s">
-        <v>624</v>
+        <v>510</v>
       </c>
       <c r="F296" s="4"/>
       <c r="G296" s="4"/>
       <c r="H296" s="4"/>
-      <c r="I296" s="4" t="s">
-        <v>625</v>
+      <c r="I296" s="6" t="s">
+        <v>511</v>
       </c>
       <c r="J296" s="4" t="s">
-        <v>423</v>
+        <v>436</v>
       </c>
       <c r="K296" s="4" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="297" spans="1:11">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="297" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A297" s="4" t="s">
         <v>409</v>
       </c>
       <c r="B297" s="4" t="s">
-        <v>568</v>
+        <v>495</v>
       </c>
       <c r="C297" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D297" s="4"/>
       <c r="E297" s="5" t="s">
-        <v>626</v>
+        <v>528</v>
       </c>
       <c r="F297" s="4"/>
       <c r="G297" s="4"/>
       <c r="H297" s="4"/>
       <c r="I297" s="4" t="s">
-        <v>627</v>
+        <v>529</v>
       </c>
       <c r="J297" s="4" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="K297" s="4" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="298" spans="1:11">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="298" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A298" s="4" t="s">
         <v>409</v>
       </c>
       <c r="B298" s="4" t="s">
-        <v>568</v>
+        <v>495</v>
       </c>
       <c r="C298" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D298" s="4"/>
       <c r="E298" s="5" t="s">
-        <v>628</v>
+        <v>546</v>
       </c>
       <c r="F298" s="4"/>
       <c r="G298" s="4"/>
       <c r="H298" s="4"/>
       <c r="I298" s="4" t="s">
-        <v>629</v>
+        <v>547</v>
       </c>
       <c r="J298" s="4" t="s">
-        <v>571</v>
+        <v>436</v>
       </c>
       <c r="K298" s="4" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="299" spans="1:11">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="299" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A299" s="4" t="s">
         <v>409</v>
       </c>
       <c r="B299" s="4" t="s">
-        <v>568</v>
+        <v>495</v>
       </c>
       <c r="C299" s="4">
         <v>4</v>
       </c>
       <c r="D299" s="4"/>
       <c r="E299" s="5" t="s">
-        <v>630</v>
+        <v>562</v>
       </c>
       <c r="F299" s="4"/>
       <c r="G299" s="4"/>
       <c r="H299" s="4"/>
       <c r="I299" s="4" t="s">
-        <v>631</v>
+        <v>563</v>
       </c>
       <c r="J299" s="4" t="s">
         <v>436</v>
@@ -9991,218 +10002,250 @@
         <v>414</v>
       </c>
     </row>
-    <row r="300" spans="1:11">
+    <row r="300" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A300" s="4" t="s">
         <v>409</v>
       </c>
       <c r="B300" s="4" t="s">
-        <v>568</v>
+        <v>495</v>
       </c>
       <c r="C300" s="4">
         <v>4</v>
       </c>
       <c r="D300" s="4"/>
       <c r="E300" s="5" t="s">
-        <v>632</v>
+        <v>564</v>
       </c>
       <c r="F300" s="4"/>
       <c r="G300" s="4"/>
       <c r="H300" s="4"/>
-      <c r="I300" s="4" t="s">
-        <v>633</v>
+      <c r="I300" s="6" t="s">
+        <v>565</v>
       </c>
       <c r="J300" s="4" t="s">
         <v>436</v>
       </c>
       <c r="K300" s="4" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="301" spans="1:11">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="301" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A301" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="B301" s="4"/>
-      <c r="C301" s="4"/>
+      <c r="B301" s="4" t="s">
+        <v>568</v>
+      </c>
+      <c r="C301" s="4">
+        <v>1</v>
+      </c>
       <c r="D301" s="4"/>
       <c r="E301" s="5" t="s">
-        <v>634</v>
+        <v>584</v>
       </c>
       <c r="F301" s="4"/>
       <c r="G301" s="4"/>
       <c r="H301" s="4"/>
       <c r="I301" s="4" t="s">
-        <v>635</v>
+        <v>585</v>
       </c>
       <c r="J301" s="4" t="s">
-        <v>417</v>
+        <v>436</v>
       </c>
       <c r="K301" s="4" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="302" spans="1:11">
+    <row r="302" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A302" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="B302" s="4"/>
-      <c r="C302" s="4"/>
+      <c r="B302" s="4" t="s">
+        <v>568</v>
+      </c>
+      <c r="C302" s="4">
+        <v>1</v>
+      </c>
       <c r="D302" s="4"/>
       <c r="E302" s="5" t="s">
-        <v>636</v>
+        <v>586</v>
       </c>
       <c r="F302" s="4"/>
       <c r="G302" s="4"/>
       <c r="H302" s="4"/>
       <c r="I302" s="4" t="s">
-        <v>637</v>
+        <v>587</v>
       </c>
       <c r="J302" s="4" t="s">
-        <v>417</v>
+        <v>436</v>
       </c>
       <c r="K302" s="4" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="303" spans="1:11">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="303" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A303" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="B303" s="4"/>
-      <c r="C303" s="4"/>
+      <c r="B303" s="4" t="s">
+        <v>568</v>
+      </c>
+      <c r="C303" s="4">
+        <v>2</v>
+      </c>
       <c r="D303" s="4"/>
       <c r="E303" s="5" t="s">
-        <v>638</v>
+        <v>600</v>
       </c>
       <c r="F303" s="4"/>
       <c r="G303" s="4"/>
       <c r="H303" s="4"/>
       <c r="I303" s="4" t="s">
-        <v>639</v>
+        <v>601</v>
       </c>
       <c r="J303" s="4" t="s">
-        <v>417</v>
+        <v>436</v>
       </c>
       <c r="K303" s="4" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="304" spans="1:11">
+    <row r="304" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A304" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="B304" s="4"/>
-      <c r="C304" s="4"/>
+      <c r="B304" s="4" t="s">
+        <v>568</v>
+      </c>
+      <c r="C304" s="4">
+        <v>2</v>
+      </c>
       <c r="D304" s="4"/>
       <c r="E304" s="5" t="s">
-        <v>640</v>
+        <v>602</v>
       </c>
       <c r="F304" s="4"/>
       <c r="G304" s="4"/>
       <c r="H304" s="4"/>
       <c r="I304" s="4" t="s">
-        <v>641</v>
+        <v>603</v>
       </c>
       <c r="J304" s="4" t="s">
-        <v>417</v>
+        <v>436</v>
       </c>
       <c r="K304" s="4" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="305" spans="1:11">
+    <row r="305" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A305" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="B305" s="4"/>
-      <c r="C305" s="4"/>
+      <c r="B305" s="4" t="s">
+        <v>568</v>
+      </c>
+      <c r="C305" s="4">
+        <v>3</v>
+      </c>
       <c r="D305" s="4"/>
       <c r="E305" s="5" t="s">
-        <v>642</v>
+        <v>614</v>
       </c>
       <c r="F305" s="4"/>
       <c r="G305" s="4"/>
       <c r="H305" s="4"/>
       <c r="I305" s="4" t="s">
-        <v>643</v>
+        <v>615</v>
       </c>
       <c r="J305" s="4" t="s">
-        <v>417</v>
+        <v>436</v>
       </c>
       <c r="K305" s="4" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="306" spans="1:11">
+    <row r="306" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A306" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="B306" s="4"/>
-      <c r="C306" s="4"/>
+      <c r="B306" s="4" t="s">
+        <v>568</v>
+      </c>
+      <c r="C306" s="4">
+        <v>3</v>
+      </c>
       <c r="D306" s="4"/>
       <c r="E306" s="5" t="s">
-        <v>644</v>
+        <v>616</v>
       </c>
       <c r="F306" s="4"/>
       <c r="G306" s="4"/>
       <c r="H306" s="4"/>
       <c r="I306" s="4" t="s">
-        <v>645</v>
+        <v>617</v>
       </c>
       <c r="J306" s="4" t="s">
-        <v>646</v>
+        <v>436</v>
       </c>
       <c r="K306" s="4" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="307" spans="1:11">
+    <row r="307" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A307" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="B307" s="4"/>
-      <c r="C307" s="4"/>
+      <c r="B307" s="4" t="s">
+        <v>568</v>
+      </c>
+      <c r="C307" s="4">
+        <v>4</v>
+      </c>
       <c r="D307" s="4"/>
       <c r="E307" s="5" t="s">
-        <v>647</v>
+        <v>630</v>
       </c>
       <c r="F307" s="4"/>
       <c r="G307" s="4"/>
       <c r="H307" s="4"/>
       <c r="I307" s="4" t="s">
-        <v>648</v>
+        <v>631</v>
       </c>
       <c r="J307" s="4" t="s">
-        <v>420</v>
+        <v>436</v>
       </c>
       <c r="K307" s="4" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="308" spans="1:11">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="308" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A308" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="B308" s="4"/>
-      <c r="C308" s="4"/>
+      <c r="B308" s="4" t="s">
+        <v>568</v>
+      </c>
+      <c r="C308" s="4">
+        <v>4</v>
+      </c>
       <c r="D308" s="4"/>
       <c r="E308" s="5" t="s">
-        <v>649</v>
+        <v>632</v>
       </c>
       <c r="F308" s="4"/>
       <c r="G308" s="4"/>
       <c r="H308" s="4"/>
       <c r="I308" s="4" t="s">
-        <v>650</v>
+        <v>633</v>
       </c>
       <c r="J308" s="4" t="s">
-        <v>423</v>
+        <v>436</v>
       </c>
       <c r="K308" s="4" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="309" spans="1:11">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="309" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A309" s="4" t="s">
         <v>409</v>
       </c>
@@ -10210,22 +10253,22 @@
       <c r="C309" s="4"/>
       <c r="D309" s="4"/>
       <c r="E309" s="5" t="s">
-        <v>651</v>
+        <v>669</v>
       </c>
       <c r="F309" s="4"/>
       <c r="G309" s="4"/>
       <c r="H309" s="4"/>
       <c r="I309" s="4" t="s">
-        <v>652</v>
+        <v>670</v>
       </c>
       <c r="J309" s="4" t="s">
-        <v>423</v>
+        <v>436</v>
       </c>
       <c r="K309" s="4" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="310" spans="1:11">
+    <row r="310" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A310" s="4" t="s">
         <v>409</v>
       </c>
@@ -10233,22 +10276,22 @@
       <c r="C310" s="4"/>
       <c r="D310" s="4"/>
       <c r="E310" s="5" t="s">
-        <v>653</v>
+        <v>671</v>
       </c>
       <c r="F310" s="4"/>
       <c r="G310" s="4"/>
       <c r="H310" s="4"/>
       <c r="I310" s="4" t="s">
-        <v>654</v>
+        <v>672</v>
       </c>
       <c r="J310" s="4" t="s">
-        <v>423</v>
+        <v>436</v>
       </c>
       <c r="K310" s="4" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="311" spans="1:11">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="311" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A311" s="4" t="s">
         <v>409</v>
       </c>
@@ -10256,22 +10299,22 @@
       <c r="C311" s="4"/>
       <c r="D311" s="4"/>
       <c r="E311" s="5" t="s">
-        <v>655</v>
+        <v>673</v>
       </c>
       <c r="F311" s="4"/>
       <c r="G311" s="4"/>
       <c r="H311" s="4"/>
       <c r="I311" s="4" t="s">
-        <v>656</v>
+        <v>674</v>
       </c>
       <c r="J311" s="4" t="s">
-        <v>423</v>
+        <v>436</v>
       </c>
       <c r="K311" s="4" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="312" spans="1:11">
+    <row r="312" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A312" s="4" t="s">
         <v>409</v>
       </c>
@@ -10279,22 +10322,22 @@
       <c r="C312" s="4"/>
       <c r="D312" s="4"/>
       <c r="E312" s="5" t="s">
-        <v>657</v>
+        <v>675</v>
       </c>
       <c r="F312" s="4"/>
       <c r="G312" s="4"/>
       <c r="H312" s="4"/>
       <c r="I312" s="4" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="J312" s="4" t="s">
-        <v>423</v>
+        <v>436</v>
       </c>
       <c r="K312" s="4" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="313" spans="1:11">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="313" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A313" s="4" t="s">
         <v>409</v>
       </c>
@@ -10302,22 +10345,22 @@
       <c r="C313" s="4"/>
       <c r="D313" s="4"/>
       <c r="E313" s="5" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
       <c r="F313" s="4"/>
       <c r="G313" s="4"/>
       <c r="H313" s="4"/>
       <c r="I313" s="4" t="s">
-        <v>660</v>
+        <v>678</v>
       </c>
       <c r="J313" s="4" t="s">
-        <v>423</v>
+        <v>436</v>
       </c>
       <c r="K313" s="4" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="314" spans="1:11">
+    <row r="314" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A314" s="4" t="s">
         <v>409</v>
       </c>
@@ -10325,22 +10368,22 @@
       <c r="C314" s="4"/>
       <c r="D314" s="4"/>
       <c r="E314" s="5" t="s">
-        <v>661</v>
+        <v>679</v>
       </c>
       <c r="F314" s="4"/>
       <c r="G314" s="4"/>
       <c r="H314" s="4"/>
       <c r="I314" s="4" t="s">
-        <v>662</v>
+        <v>680</v>
       </c>
       <c r="J314" s="4" t="s">
-        <v>423</v>
+        <v>436</v>
       </c>
       <c r="K314" s="4" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="315" spans="1:11">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="315" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A315" s="4" t="s">
         <v>409</v>
       </c>
@@ -10348,22 +10391,22 @@
       <c r="C315" s="4"/>
       <c r="D315" s="4"/>
       <c r="E315" s="5" t="s">
-        <v>663</v>
+        <v>681</v>
       </c>
       <c r="F315" s="4"/>
       <c r="G315" s="4"/>
       <c r="H315" s="4"/>
       <c r="I315" s="4" t="s">
-        <v>664</v>
+        <v>682</v>
       </c>
       <c r="J315" s="4" t="s">
-        <v>423</v>
+        <v>436</v>
       </c>
       <c r="K315" s="4" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="316" spans="1:11">
+    <row r="316" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A316" s="4" t="s">
         <v>409</v>
       </c>
@@ -10371,22 +10414,22 @@
       <c r="C316" s="4"/>
       <c r="D316" s="4"/>
       <c r="E316" s="5" t="s">
-        <v>665</v>
+        <v>683</v>
       </c>
       <c r="F316" s="4"/>
       <c r="G316" s="4"/>
       <c r="H316" s="4"/>
       <c r="I316" s="4" t="s">
-        <v>666</v>
+        <v>684</v>
       </c>
       <c r="J316" s="4" t="s">
-        <v>571</v>
+        <v>436</v>
       </c>
       <c r="K316" s="4" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="317" spans="1:11">
+    <row r="317" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A317" s="4" t="s">
         <v>409</v>
       </c>
@@ -10394,22 +10437,22 @@
       <c r="C317" s="4"/>
       <c r="D317" s="4"/>
       <c r="E317" s="5" t="s">
-        <v>667</v>
+        <v>685</v>
       </c>
       <c r="F317" s="4"/>
       <c r="G317" s="4"/>
       <c r="H317" s="4"/>
       <c r="I317" s="4" t="s">
-        <v>668</v>
+        <v>686</v>
       </c>
       <c r="J317" s="4" t="s">
-        <v>571</v>
+        <v>436</v>
       </c>
       <c r="K317" s="4" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="318" spans="1:11">
+    <row r="318" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A318" s="4" t="s">
         <v>409</v>
       </c>
@@ -10417,22 +10460,22 @@
       <c r="C318" s="4"/>
       <c r="D318" s="4"/>
       <c r="E318" s="5" t="s">
-        <v>669</v>
+        <v>687</v>
       </c>
       <c r="F318" s="4"/>
       <c r="G318" s="4"/>
       <c r="H318" s="4"/>
       <c r="I318" s="4" t="s">
-        <v>670</v>
+        <v>688</v>
       </c>
       <c r="J318" s="4" t="s">
         <v>436</v>
       </c>
       <c r="K318" s="4" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="319" spans="1:11">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="319" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A319" s="4" t="s">
         <v>409</v>
       </c>
@@ -10440,22 +10483,22 @@
       <c r="C319" s="4"/>
       <c r="D319" s="4"/>
       <c r="E319" s="5" t="s">
-        <v>671</v>
+        <v>689</v>
       </c>
       <c r="F319" s="4"/>
       <c r="G319" s="4"/>
       <c r="H319" s="4"/>
       <c r="I319" s="4" t="s">
-        <v>672</v>
+        <v>690</v>
       </c>
       <c r="J319" s="4" t="s">
         <v>436</v>
       </c>
       <c r="K319" s="4" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="320" spans="1:11">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="320" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A320" s="4" t="s">
         <v>409</v>
       </c>
@@ -10463,13 +10506,13 @@
       <c r="C320" s="4"/>
       <c r="D320" s="4"/>
       <c r="E320" s="5" t="s">
-        <v>673</v>
+        <v>691</v>
       </c>
       <c r="F320" s="4"/>
       <c r="G320" s="4"/>
       <c r="H320" s="4"/>
       <c r="I320" s="4" t="s">
-        <v>674</v>
+        <v>692</v>
       </c>
       <c r="J320" s="4" t="s">
         <v>436</v>
@@ -10478,7 +10521,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="321" spans="1:11">
+    <row r="321" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A321" s="4" t="s">
         <v>409</v>
       </c>
@@ -10486,13 +10529,13 @@
       <c r="C321" s="4"/>
       <c r="D321" s="4"/>
       <c r="E321" s="5" t="s">
-        <v>675</v>
+        <v>693</v>
       </c>
       <c r="F321" s="4"/>
       <c r="G321" s="4"/>
       <c r="H321" s="4"/>
       <c r="I321" s="4" t="s">
-        <v>676</v>
+        <v>694</v>
       </c>
       <c r="J321" s="4" t="s">
         <v>436</v>
@@ -10501,214 +10544,250 @@
         <v>414</v>
       </c>
     </row>
-    <row r="322" spans="1:11">
+    <row r="322" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A322" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="B322" s="4"/>
-      <c r="C322" s="4"/>
+      <c r="B322" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="C322" s="4">
+        <v>1</v>
+      </c>
       <c r="D322" s="4"/>
       <c r="E322" s="5" t="s">
-        <v>677</v>
+        <v>437</v>
       </c>
       <c r="F322" s="4"/>
       <c r="G322" s="4"/>
       <c r="H322" s="4"/>
       <c r="I322" s="4" t="s">
-        <v>678</v>
+        <v>438</v>
       </c>
       <c r="J322" s="4" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="K322" s="4" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="323" spans="1:11">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="323" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A323" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="B323" s="4"/>
-      <c r="C323" s="4"/>
+      <c r="B323" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="C323" s="4">
+        <v>2</v>
+      </c>
       <c r="D323" s="4"/>
       <c r="E323" s="5" t="s">
-        <v>679</v>
+        <v>456</v>
       </c>
       <c r="F323" s="4"/>
       <c r="G323" s="4"/>
       <c r="H323" s="4"/>
       <c r="I323" s="4" t="s">
-        <v>680</v>
+        <v>457</v>
       </c>
       <c r="J323" s="4" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="K323" s="4" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="324" spans="1:11">
+    <row r="324" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A324" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="B324" s="4"/>
-      <c r="C324" s="4"/>
+      <c r="B324" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="C324" s="4">
+        <v>3</v>
+      </c>
       <c r="D324" s="4"/>
       <c r="E324" s="5" t="s">
-        <v>681</v>
+        <v>474</v>
       </c>
       <c r="F324" s="4"/>
       <c r="G324" s="4"/>
       <c r="H324" s="4"/>
       <c r="I324" s="4" t="s">
-        <v>682</v>
+        <v>475</v>
       </c>
       <c r="J324" s="4" t="s">
-        <v>436</v>
+        <v>476</v>
       </c>
       <c r="K324" s="4" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="325" spans="1:11">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="325" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A325" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="B325" s="4"/>
-      <c r="C325" s="4"/>
+      <c r="B325" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="C325" s="4">
+        <v>4</v>
+      </c>
       <c r="D325" s="4"/>
       <c r="E325" s="5" t="s">
-        <v>683</v>
+        <v>493</v>
       </c>
       <c r="F325" s="4"/>
       <c r="G325" s="4"/>
       <c r="H325" s="4"/>
       <c r="I325" s="4" t="s">
-        <v>684</v>
+        <v>494</v>
       </c>
       <c r="J325" s="4" t="s">
-        <v>436</v>
+        <v>476</v>
       </c>
       <c r="K325" s="4" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="326" spans="1:11">
+    <row r="326" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A326" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="B326" s="4"/>
-      <c r="C326" s="4"/>
+      <c r="B326" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="C326" s="4">
+        <v>1</v>
+      </c>
       <c r="D326" s="4"/>
       <c r="E326" s="5" t="s">
-        <v>685</v>
+        <v>512</v>
       </c>
       <c r="F326" s="4"/>
       <c r="G326" s="4"/>
       <c r="H326" s="4"/>
       <c r="I326" s="4" t="s">
-        <v>686</v>
+        <v>513</v>
       </c>
       <c r="J326" s="4" t="s">
-        <v>436</v>
+        <v>476</v>
       </c>
       <c r="K326" s="4" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="327" spans="1:11">
+    <row r="327" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A327" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="B327" s="4"/>
-      <c r="C327" s="4"/>
+      <c r="B327" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="C327" s="4">
+        <v>2</v>
+      </c>
       <c r="D327" s="4"/>
       <c r="E327" s="5" t="s">
-        <v>687</v>
+        <v>530</v>
       </c>
       <c r="F327" s="4"/>
       <c r="G327" s="4"/>
       <c r="H327" s="4"/>
       <c r="I327" s="4" t="s">
-        <v>688</v>
+        <v>531</v>
       </c>
       <c r="J327" s="4" t="s">
-        <v>436</v>
+        <v>476</v>
       </c>
       <c r="K327" s="4" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="328" spans="1:11">
+    <row r="328" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A328" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="B328" s="4"/>
-      <c r="C328" s="4"/>
+      <c r="B328" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="C328" s="4">
+        <v>3</v>
+      </c>
       <c r="D328" s="4"/>
       <c r="E328" s="5" t="s">
-        <v>689</v>
+        <v>548</v>
       </c>
       <c r="F328" s="4"/>
       <c r="G328" s="4"/>
       <c r="H328" s="4"/>
       <c r="I328" s="4" t="s">
-        <v>690</v>
+        <v>549</v>
       </c>
       <c r="J328" s="4" t="s">
-        <v>436</v>
+        <v>476</v>
       </c>
       <c r="K328" s="4" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="329" spans="1:11">
+    <row r="329" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A329" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="B329" s="4"/>
-      <c r="C329" s="4"/>
+      <c r="B329" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="C329" s="4">
+        <v>4</v>
+      </c>
       <c r="D329" s="4"/>
       <c r="E329" s="5" t="s">
-        <v>691</v>
+        <v>566</v>
       </c>
       <c r="F329" s="4"/>
       <c r="G329" s="4"/>
       <c r="H329" s="4"/>
       <c r="I329" s="4" t="s">
-        <v>692</v>
+        <v>567</v>
       </c>
       <c r="J329" s="4" t="s">
-        <v>436</v>
+        <v>476</v>
       </c>
       <c r="K329" s="4" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="330" spans="1:11">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="330" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A330" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="B330" s="4"/>
-      <c r="C330" s="4"/>
+      <c r="B330" s="4" t="s">
+        <v>568</v>
+      </c>
+      <c r="C330" s="4">
+        <v>3</v>
+      </c>
       <c r="D330" s="4"/>
       <c r="E330" s="5" t="s">
-        <v>693</v>
+        <v>618</v>
       </c>
       <c r="F330" s="4"/>
       <c r="G330" s="4"/>
       <c r="H330" s="4"/>
       <c r="I330" s="4" t="s">
-        <v>694</v>
+        <v>619</v>
       </c>
       <c r="J330" s="4" t="s">
-        <v>436</v>
+        <v>476</v>
       </c>
       <c r="K330" s="4" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="331" spans="1:11">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="331" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A331" s="4" t="s">
         <v>695</v>
       </c>
@@ -10731,7 +10810,7 @@
       <c r="J331" s="4"/>
       <c r="K331" s="4"/>
     </row>
-    <row r="332" spans="1:11">
+    <row r="332" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A332" s="4" t="s">
         <v>695</v>
       </c>
@@ -10754,7 +10833,7 @@
       <c r="J332" s="4"/>
       <c r="K332" s="4"/>
     </row>
-    <row r="333" spans="1:11">
+    <row r="333" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A333" s="4" t="s">
         <v>695</v>
       </c>
@@ -10777,7 +10856,7 @@
       <c r="J333" s="4"/>
       <c r="K333" s="4"/>
     </row>
-    <row r="334" spans="1:11">
+    <row r="334" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A334" s="4" t="s">
         <v>695</v>
       </c>
@@ -10800,7 +10879,7 @@
       <c r="J334" s="4"/>
       <c r="K334" s="4"/>
     </row>
-    <row r="335" spans="1:11">
+    <row r="335" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A335" s="4" t="s">
         <v>695</v>
       </c>
@@ -10823,7 +10902,7 @@
       <c r="J335" s="4"/>
       <c r="K335" s="4"/>
     </row>
-    <row r="336" spans="1:11">
+    <row r="336" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A336" s="4" t="s">
         <v>695</v>
       </c>
@@ -10846,7 +10925,7 @@
       <c r="J336" s="4"/>
       <c r="K336" s="4"/>
     </row>
-    <row r="337" spans="1:11">
+    <row r="337" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A337" s="4" t="s">
         <v>695</v>
       </c>
@@ -10869,7 +10948,7 @@
       <c r="J337" s="4"/>
       <c r="K337" s="4"/>
     </row>
-    <row r="338" spans="1:11">
+    <row r="338" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A338" s="4" t="s">
         <v>695</v>
       </c>
@@ -10892,7 +10971,7 @@
       <c r="J338" s="4"/>
       <c r="K338" s="4"/>
     </row>
-    <row r="339" spans="1:11">
+    <row r="339" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A339" s="4" t="s">
         <v>695</v>
       </c>
@@ -10915,7 +10994,7 @@
       <c r="J339" s="4"/>
       <c r="K339" s="4"/>
     </row>
-    <row r="340" spans="1:11">
+    <row r="340" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A340" s="4" t="s">
         <v>695</v>
       </c>
@@ -10938,7 +11017,7 @@
       <c r="J340" s="4"/>
       <c r="K340" s="4"/>
     </row>
-    <row r="341" spans="1:11">
+    <row r="341" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A341" s="4" t="s">
         <v>695</v>
       </c>
@@ -10961,7 +11040,7 @@
       <c r="J341" s="4"/>
       <c r="K341" s="4"/>
     </row>
-    <row r="342" spans="1:11">
+    <row r="342" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A342" s="4" t="s">
         <v>695</v>
       </c>
@@ -10984,7 +11063,7 @@
       <c r="J342" s="4"/>
       <c r="K342" s="4"/>
     </row>
-    <row r="343" spans="1:11">
+    <row r="343" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A343" s="4" t="s">
         <v>695</v>
       </c>
@@ -11007,7 +11086,7 @@
       <c r="J343" s="4"/>
       <c r="K343" s="4"/>
     </row>
-    <row r="344" spans="1:11">
+    <row r="344" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A344" s="4" t="s">
         <v>695</v>
       </c>
@@ -11030,7 +11109,7 @@
       <c r="J344" s="4"/>
       <c r="K344" s="4"/>
     </row>
-    <row r="345" spans="1:11">
+    <row r="345" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A345" s="4" t="s">
         <v>695</v>
       </c>
@@ -11053,7 +11132,7 @@
       <c r="J345" s="4"/>
       <c r="K345" s="4"/>
     </row>
-    <row r="346" spans="1:11">
+    <row r="346" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A346" s="4" t="s">
         <v>695</v>
       </c>
@@ -11076,7 +11155,7 @@
       <c r="J346" s="4"/>
       <c r="K346" s="4"/>
     </row>
-    <row r="347" spans="1:11">
+    <row r="347" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A347" s="4" t="s">
         <v>695</v>
       </c>
@@ -11099,7 +11178,7 @@
       <c r="J347" s="4"/>
       <c r="K347" s="4"/>
     </row>
-    <row r="348" spans="1:11">
+    <row r="348" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A348" s="4" t="s">
         <v>695</v>
       </c>
@@ -11122,7 +11201,7 @@
       <c r="J348" s="4"/>
       <c r="K348" s="4"/>
     </row>
-    <row r="349" spans="1:11">
+    <row r="349" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A349" s="4" t="s">
         <v>695</v>
       </c>
@@ -11145,7 +11224,7 @@
       <c r="J349" s="4"/>
       <c r="K349" s="4"/>
     </row>
-    <row r="350" spans="1:11">
+    <row r="350" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A350" s="4" t="s">
         <v>695</v>
       </c>
@@ -11168,7 +11247,7 @@
       <c r="J350" s="4"/>
       <c r="K350" s="4"/>
     </row>
-    <row r="351" spans="1:11">
+    <row r="351" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A351" s="4" t="s">
         <v>695</v>
       </c>
@@ -11191,7 +11270,7 @@
       <c r="J351" s="4"/>
       <c r="K351" s="4"/>
     </row>
-    <row r="352" spans="1:11">
+    <row r="352" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A352" s="4" t="s">
         <v>695</v>
       </c>
@@ -11214,7 +11293,7 @@
       <c r="J352" s="4"/>
       <c r="K352" s="4"/>
     </row>
-    <row r="353" spans="1:11">
+    <row r="353" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A353" s="4" t="s">
         <v>695</v>
       </c>
@@ -11237,16 +11316,12 @@
       <c r="J353" s="4"/>
       <c r="K353" s="4"/>
     </row>
-    <row r="354" spans="1:11">
+    <row r="354" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A354" s="4" t="s">
         <v>746</v>
       </c>
-      <c r="B354" s="4" t="s">
-        <v>696</v>
-      </c>
-      <c r="C354" s="4">
-        <v>1</v>
-      </c>
+      <c r="B354" s="10"/>
+      <c r="C354" s="10"/>
       <c r="D354" s="4"/>
       <c r="E354" s="5" t="s">
         <v>747</v>
@@ -11268,19 +11343,19 @@
       </c>
       <c r="K354" s="4"/>
     </row>
-    <row r="355" spans="1:11">
-      <c r="A355" s="4" t="s">
+    <row r="355" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A355" s="8" t="s">
         <v>746</v>
       </c>
-      <c r="B355" s="4" t="s">
+      <c r="B355" s="7" t="s">
         <v>696</v>
       </c>
-      <c r="C355" s="4">
+      <c r="C355" s="7">
         <v>1</v>
       </c>
-      <c r="D355" s="4"/>
+      <c r="D355" s="9"/>
       <c r="E355" s="5" t="s">
-        <v>751</v>
+        <v>772</v>
       </c>
       <c r="F355" s="4">
         <v>1</v>
@@ -11292,26 +11367,26 @@
         <v>748</v>
       </c>
       <c r="I355" s="4" t="s">
-        <v>752</v>
+        <v>773</v>
       </c>
       <c r="J355" s="4" t="s">
-        <v>646</v>
+        <v>750</v>
       </c>
       <c r="K355" s="4"/>
     </row>
-    <row r="356" spans="1:11">
-      <c r="A356" s="4" t="s">
+    <row r="356" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A356" s="8" t="s">
         <v>746</v>
       </c>
-      <c r="B356" s="4" t="s">
+      <c r="B356" s="7" t="s">
         <v>696</v>
       </c>
-      <c r="C356" s="4">
-        <v>1</v>
-      </c>
-      <c r="D356" s="4"/>
+      <c r="C356" s="7">
+        <v>2</v>
+      </c>
+      <c r="D356" s="9"/>
       <c r="E356" s="5" t="s">
-        <v>753</v>
+        <v>793</v>
       </c>
       <c r="F356" s="4">
         <v>1</v>
@@ -11323,26 +11398,26 @@
         <v>748</v>
       </c>
       <c r="I356" s="4" t="s">
-        <v>754</v>
+        <v>794</v>
       </c>
       <c r="J356" s="4" t="s">
-        <v>420</v>
+        <v>750</v>
       </c>
       <c r="K356" s="4"/>
     </row>
-    <row r="357" spans="1:11">
-      <c r="A357" s="4" t="s">
+    <row r="357" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A357" s="8" t="s">
         <v>746</v>
       </c>
-      <c r="B357" s="4" t="s">
+      <c r="B357" s="7" t="s">
         <v>696</v>
       </c>
-      <c r="C357" s="4">
-        <v>1</v>
-      </c>
-      <c r="D357" s="4"/>
+      <c r="C357" s="7">
+        <v>3</v>
+      </c>
+      <c r="D357" s="9"/>
       <c r="E357" s="5" t="s">
-        <v>755</v>
+        <v>813</v>
       </c>
       <c r="F357" s="4">
         <v>1</v>
@@ -11354,26 +11429,26 @@
         <v>748</v>
       </c>
       <c r="I357" s="4" t="s">
-        <v>756</v>
+        <v>814</v>
       </c>
       <c r="J357" s="4" t="s">
-        <v>430</v>
+        <v>750</v>
       </c>
       <c r="K357" s="4"/>
     </row>
-    <row r="358" spans="1:11">
-      <c r="A358" s="4" t="s">
+    <row r="358" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A358" s="8" t="s">
         <v>746</v>
       </c>
-      <c r="B358" s="4" t="s">
+      <c r="B358" s="7" t="s">
         <v>696</v>
       </c>
-      <c r="C358" s="4">
-        <v>1</v>
-      </c>
-      <c r="D358" s="4"/>
+      <c r="C358" s="7">
+        <v>4</v>
+      </c>
+      <c r="D358" s="9"/>
       <c r="E358" s="5" t="s">
-        <v>757</v>
+        <v>751</v>
       </c>
       <c r="F358" s="4">
         <v>1</v>
@@ -11385,26 +11460,22 @@
         <v>748</v>
       </c>
       <c r="I358" s="4" t="s">
-        <v>758</v>
+        <v>752</v>
       </c>
       <c r="J358" s="4" t="s">
-        <v>430</v>
+        <v>646</v>
       </c>
       <c r="K358" s="4"/>
     </row>
-    <row r="359" spans="1:11">
-      <c r="A359" s="4" t="s">
+    <row r="359" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A359" s="8" t="s">
         <v>746</v>
       </c>
-      <c r="B359" s="4" t="s">
-        <v>696</v>
-      </c>
-      <c r="C359" s="4">
-        <v>1</v>
-      </c>
-      <c r="D359" s="4"/>
+      <c r="B359" s="7"/>
+      <c r="C359" s="7"/>
+      <c r="D359" s="9"/>
       <c r="E359" s="5" t="s">
-        <v>759</v>
+        <v>753</v>
       </c>
       <c r="F359" s="4">
         <v>1</v>
@@ -11416,26 +11487,22 @@
         <v>748</v>
       </c>
       <c r="I359" s="4" t="s">
-        <v>760</v>
+        <v>754</v>
       </c>
       <c r="J359" s="4" t="s">
-        <v>761</v>
+        <v>420</v>
       </c>
       <c r="K359" s="4"/>
     </row>
-    <row r="360" spans="1:11">
-      <c r="A360" s="4" t="s">
+    <row r="360" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A360" s="8" t="s">
         <v>746</v>
       </c>
-      <c r="B360" s="4" t="s">
-        <v>696</v>
-      </c>
-      <c r="C360" s="4">
-        <v>1</v>
-      </c>
-      <c r="D360" s="4"/>
+      <c r="B360" s="7"/>
+      <c r="C360" s="7"/>
+      <c r="D360" s="9"/>
       <c r="E360" s="5" t="s">
-        <v>762</v>
+        <v>774</v>
       </c>
       <c r="F360" s="4">
         <v>1</v>
@@ -11447,26 +11514,22 @@
         <v>748</v>
       </c>
       <c r="I360" s="4" t="s">
-        <v>763</v>
+        <v>775</v>
       </c>
       <c r="J360" s="4" t="s">
-        <v>436</v>
+        <v>420</v>
       </c>
       <c r="K360" s="4"/>
     </row>
-    <row r="361" spans="1:11">
-      <c r="A361" s="4" t="s">
+    <row r="361" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A361" s="8" t="s">
         <v>746</v>
       </c>
-      <c r="B361" s="4" t="s">
-        <v>696</v>
-      </c>
-      <c r="C361" s="4">
-        <v>1</v>
-      </c>
-      <c r="D361" s="4"/>
+      <c r="B361" s="7"/>
+      <c r="C361" s="7"/>
+      <c r="D361" s="9"/>
       <c r="E361" s="5" t="s">
-        <v>764</v>
+        <v>776</v>
       </c>
       <c r="F361" s="4">
         <v>1</v>
@@ -11478,26 +11541,22 @@
         <v>748</v>
       </c>
       <c r="I361" s="4" t="s">
-        <v>765</v>
+        <v>777</v>
       </c>
       <c r="J361" s="4" t="s">
-        <v>766</v>
+        <v>420</v>
       </c>
       <c r="K361" s="4"/>
     </row>
-    <row r="362" spans="1:11">
-      <c r="A362" s="4" t="s">
+    <row r="362" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A362" s="8" t="s">
         <v>746</v>
       </c>
-      <c r="B362" s="4" t="s">
-        <v>696</v>
-      </c>
-      <c r="C362" s="4">
-        <v>1</v>
-      </c>
-      <c r="D362" s="4"/>
+      <c r="B362" s="7"/>
+      <c r="C362" s="7"/>
+      <c r="D362" s="9"/>
       <c r="E362" s="5" t="s">
-        <v>767</v>
+        <v>795</v>
       </c>
       <c r="F362" s="4">
         <v>1</v>
@@ -11509,26 +11568,22 @@
         <v>748</v>
       </c>
       <c r="I362" s="4" t="s">
-        <v>768</v>
+        <v>796</v>
       </c>
       <c r="J362" s="4" t="s">
-        <v>769</v>
+        <v>420</v>
       </c>
       <c r="K362" s="4"/>
     </row>
-    <row r="363" spans="1:11">
-      <c r="A363" s="4" t="s">
+    <row r="363" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A363" s="8" t="s">
         <v>746</v>
       </c>
-      <c r="B363" s="4" t="s">
-        <v>696</v>
-      </c>
-      <c r="C363" s="4">
-        <v>1</v>
-      </c>
-      <c r="D363" s="4"/>
+      <c r="B363" s="7"/>
+      <c r="C363" s="7"/>
+      <c r="D363" s="9"/>
       <c r="E363" s="5" t="s">
-        <v>770</v>
+        <v>797</v>
       </c>
       <c r="F363" s="4">
         <v>1</v>
@@ -11540,26 +11595,26 @@
         <v>748</v>
       </c>
       <c r="I363" s="4" t="s">
-        <v>771</v>
+        <v>798</v>
       </c>
       <c r="J363" s="4" t="s">
-        <v>769</v>
+        <v>420</v>
       </c>
       <c r="K363" s="4"/>
     </row>
-    <row r="364" spans="1:11">
-      <c r="A364" s="4" t="s">
+    <row r="364" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A364" s="8" t="s">
         <v>746</v>
       </c>
-      <c r="B364" s="4" t="s">
+      <c r="B364" s="7" t="s">
         <v>696</v>
       </c>
-      <c r="C364" s="4">
-        <v>2</v>
-      </c>
-      <c r="D364" s="4"/>
+      <c r="C364" s="7">
+        <v>1</v>
+      </c>
+      <c r="D364" s="9"/>
       <c r="E364" s="5" t="s">
-        <v>772</v>
+        <v>815</v>
       </c>
       <c r="F364" s="4">
         <v>1</v>
@@ -11571,26 +11626,26 @@
         <v>748</v>
       </c>
       <c r="I364" s="4" t="s">
-        <v>773</v>
+        <v>816</v>
       </c>
       <c r="J364" s="4" t="s">
-        <v>750</v>
+        <v>420</v>
       </c>
       <c r="K364" s="4"/>
     </row>
-    <row r="365" spans="1:11">
-      <c r="A365" s="4" t="s">
+    <row r="365" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A365" s="8" t="s">
         <v>746</v>
       </c>
-      <c r="B365" s="4" t="s">
+      <c r="B365" s="7" t="s">
         <v>696</v>
       </c>
-      <c r="C365" s="4">
+      <c r="C365" s="7">
         <v>2</v>
       </c>
-      <c r="D365" s="4"/>
+      <c r="D365" s="9"/>
       <c r="E365" s="5" t="s">
-        <v>774</v>
+        <v>817</v>
       </c>
       <c r="F365" s="4">
         <v>1</v>
@@ -11602,88 +11657,72 @@
         <v>748</v>
       </c>
       <c r="I365" s="4" t="s">
-        <v>775</v>
+        <v>818</v>
       </c>
       <c r="J365" s="4" t="s">
         <v>420</v>
       </c>
       <c r="K365" s="4"/>
     </row>
-    <row r="366" spans="1:11">
-      <c r="A366" s="4" t="s">
+    <row r="366" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A366" s="8" t="s">
         <v>746</v>
       </c>
-      <c r="B366" s="4" t="s">
+      <c r="B366" s="7" t="s">
         <v>696</v>
       </c>
-      <c r="C366" s="4">
-        <v>2</v>
-      </c>
-      <c r="D366" s="4"/>
+      <c r="C366" s="7">
+        <v>3</v>
+      </c>
+      <c r="D366" s="9"/>
       <c r="E366" s="5" t="s">
-        <v>776</v>
-      </c>
-      <c r="F366" s="4">
-        <v>1</v>
-      </c>
-      <c r="G366" s="4">
-        <v>12</v>
-      </c>
-      <c r="H366" s="4" t="s">
-        <v>748</v>
-      </c>
+        <v>833</v>
+      </c>
+      <c r="F366" s="4"/>
+      <c r="G366" s="4"/>
+      <c r="H366" s="4"/>
       <c r="I366" s="4" t="s">
-        <v>777</v>
+        <v>834</v>
       </c>
       <c r="J366" s="4" t="s">
         <v>420</v>
       </c>
       <c r="K366" s="4"/>
     </row>
-    <row r="367" spans="1:11">
-      <c r="A367" s="4" t="s">
+    <row r="367" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A367" s="8" t="s">
         <v>746</v>
       </c>
-      <c r="B367" s="4" t="s">
+      <c r="B367" s="7" t="s">
         <v>696</v>
       </c>
-      <c r="C367" s="4">
-        <v>2</v>
-      </c>
-      <c r="D367" s="4"/>
+      <c r="C367" s="7">
+        <v>4</v>
+      </c>
+      <c r="D367" s="9"/>
       <c r="E367" s="5" t="s">
-        <v>778</v>
-      </c>
-      <c r="F367" s="4">
-        <v>1</v>
-      </c>
-      <c r="G367" s="4">
-        <v>12</v>
-      </c>
-      <c r="H367" s="4" t="s">
-        <v>748</v>
-      </c>
+        <v>835</v>
+      </c>
+      <c r="F367" s="4"/>
+      <c r="G367" s="4"/>
+      <c r="H367" s="4"/>
       <c r="I367" s="4" t="s">
-        <v>779</v>
+        <v>836</v>
       </c>
       <c r="J367" s="4" t="s">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="K367" s="4"/>
     </row>
-    <row r="368" spans="1:11">
-      <c r="A368" s="4" t="s">
+    <row r="368" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A368" s="8" t="s">
         <v>746</v>
       </c>
-      <c r="B368" s="4" t="s">
-        <v>696</v>
-      </c>
-      <c r="C368" s="4">
-        <v>2</v>
-      </c>
-      <c r="D368" s="4"/>
+      <c r="B368" s="7"/>
+      <c r="C368" s="7"/>
+      <c r="D368" s="9"/>
       <c r="E368" s="5" t="s">
-        <v>780</v>
+        <v>755</v>
       </c>
       <c r="F368" s="4">
         <v>1</v>
@@ -11695,26 +11734,22 @@
         <v>748</v>
       </c>
       <c r="I368" s="4" t="s">
-        <v>781</v>
+        <v>756</v>
       </c>
       <c r="J368" s="4" t="s">
         <v>430</v>
       </c>
       <c r="K368" s="4"/>
     </row>
-    <row r="369" spans="1:11">
-      <c r="A369" s="4" t="s">
+    <row r="369" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A369" s="8" t="s">
         <v>746</v>
       </c>
-      <c r="B369" s="4" t="s">
-        <v>696</v>
-      </c>
-      <c r="C369" s="4">
-        <v>2</v>
-      </c>
-      <c r="D369" s="4"/>
+      <c r="B369" s="7"/>
+      <c r="C369" s="7"/>
+      <c r="D369" s="9"/>
       <c r="E369" s="5" t="s">
-        <v>782</v>
+        <v>757</v>
       </c>
       <c r="F369" s="4">
         <v>1</v>
@@ -11726,26 +11761,22 @@
         <v>748</v>
       </c>
       <c r="I369" s="4" t="s">
-        <v>783</v>
+        <v>758</v>
       </c>
       <c r="J369" s="4" t="s">
-        <v>784</v>
+        <v>430</v>
       </c>
       <c r="K369" s="4"/>
     </row>
-    <row r="370" spans="1:11">
-      <c r="A370" s="4" t="s">
+    <row r="370" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A370" s="8" t="s">
         <v>746</v>
       </c>
-      <c r="B370" s="4" t="s">
-        <v>696</v>
-      </c>
-      <c r="C370" s="4">
-        <v>2</v>
-      </c>
-      <c r="D370" s="4"/>
+      <c r="B370" s="7"/>
+      <c r="C370" s="7"/>
+      <c r="D370" s="9"/>
       <c r="E370" s="5" t="s">
-        <v>785</v>
+        <v>778</v>
       </c>
       <c r="F370" s="4">
         <v>1</v>
@@ -11757,26 +11788,22 @@
         <v>748</v>
       </c>
       <c r="I370" s="4" t="s">
-        <v>786</v>
+        <v>779</v>
       </c>
       <c r="J370" s="4" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="K370" s="4"/>
     </row>
-    <row r="371" spans="1:11">
-      <c r="A371" s="4" t="s">
+    <row r="371" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A371" s="8" t="s">
         <v>746</v>
       </c>
-      <c r="B371" s="4" t="s">
-        <v>696</v>
-      </c>
-      <c r="C371" s="4">
-        <v>2</v>
-      </c>
-      <c r="D371" s="4"/>
+      <c r="B371" s="7"/>
+      <c r="C371" s="7"/>
+      <c r="D371" s="9"/>
       <c r="E371" s="5" t="s">
-        <v>787</v>
+        <v>780</v>
       </c>
       <c r="F371" s="4">
         <v>1</v>
@@ -11788,26 +11815,22 @@
         <v>748</v>
       </c>
       <c r="I371" s="4" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="J371" s="4" t="s">
-        <v>766</v>
+        <v>430</v>
       </c>
       <c r="K371" s="4"/>
     </row>
-    <row r="372" spans="1:11">
-      <c r="A372" s="4" t="s">
+    <row r="372" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A372" s="8" t="s">
         <v>746</v>
       </c>
-      <c r="B372" s="4" t="s">
-        <v>696</v>
-      </c>
-      <c r="C372" s="4">
-        <v>2</v>
-      </c>
-      <c r="D372" s="4"/>
+      <c r="B372" s="7"/>
+      <c r="C372" s="7"/>
+      <c r="D372" s="9"/>
       <c r="E372" s="5" t="s">
-        <v>789</v>
+        <v>799</v>
       </c>
       <c r="F372" s="4">
         <v>1</v>
@@ -11819,26 +11842,22 @@
         <v>748</v>
       </c>
       <c r="I372" s="4" t="s">
-        <v>790</v>
+        <v>800</v>
       </c>
       <c r="J372" s="4" t="s">
-        <v>769</v>
+        <v>430</v>
       </c>
       <c r="K372" s="4"/>
     </row>
-    <row r="373" spans="1:11">
-      <c r="A373" s="4" t="s">
+    <row r="373" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A373" s="8" t="s">
         <v>746</v>
       </c>
-      <c r="B373" s="4" t="s">
-        <v>696</v>
-      </c>
-      <c r="C373" s="4">
-        <v>2</v>
-      </c>
-      <c r="D373" s="4"/>
+      <c r="B373" s="7"/>
+      <c r="C373" s="7"/>
+      <c r="D373" s="9"/>
       <c r="E373" s="5" t="s">
-        <v>791</v>
+        <v>801</v>
       </c>
       <c r="F373" s="4">
         <v>1</v>
@@ -11850,26 +11869,22 @@
         <v>748</v>
       </c>
       <c r="I373" s="4" t="s">
-        <v>792</v>
+        <v>802</v>
       </c>
       <c r="J373" s="4" t="s">
-        <v>769</v>
+        <v>430</v>
       </c>
       <c r="K373" s="4"/>
     </row>
-    <row r="374" spans="1:11">
-      <c r="A374" s="4" t="s">
+    <row r="374" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A374" s="8" t="s">
         <v>746</v>
       </c>
-      <c r="B374" s="4" t="s">
-        <v>696</v>
-      </c>
-      <c r="C374" s="4">
-        <v>3</v>
-      </c>
-      <c r="D374" s="4"/>
+      <c r="B374" s="7"/>
+      <c r="C374" s="7"/>
+      <c r="D374" s="9"/>
       <c r="E374" s="5" t="s">
-        <v>793</v>
+        <v>819</v>
       </c>
       <c r="F374" s="4">
         <v>1</v>
@@ -11881,26 +11896,22 @@
         <v>748</v>
       </c>
       <c r="I374" s="4" t="s">
-        <v>794</v>
+        <v>820</v>
       </c>
       <c r="J374" s="4" t="s">
-        <v>750</v>
+        <v>430</v>
       </c>
       <c r="K374" s="4"/>
     </row>
-    <row r="375" spans="1:11">
-      <c r="A375" s="4" t="s">
+    <row r="375" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A375" s="8" t="s">
         <v>746</v>
       </c>
-      <c r="B375" s="4" t="s">
-        <v>696</v>
-      </c>
-      <c r="C375" s="4">
-        <v>3</v>
-      </c>
-      <c r="D375" s="4"/>
+      <c r="B375" s="7"/>
+      <c r="C375" s="7"/>
+      <c r="D375" s="9"/>
       <c r="E375" s="5" t="s">
-        <v>795</v>
+        <v>821</v>
       </c>
       <c r="F375" s="4">
         <v>1</v>
@@ -11912,553 +11923,431 @@
         <v>748</v>
       </c>
       <c r="I375" s="4" t="s">
-        <v>796</v>
+        <v>822</v>
       </c>
       <c r="J375" s="4" t="s">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="K375" s="4"/>
     </row>
-    <row r="376" spans="1:11">
-      <c r="A376" s="4" t="s">
+    <row r="376" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A376" s="8" t="s">
         <v>746</v>
       </c>
-      <c r="B376" s="4" t="s">
+      <c r="B376" s="7" t="s">
         <v>696</v>
       </c>
-      <c r="C376" s="4">
-        <v>3</v>
-      </c>
-      <c r="D376" s="4"/>
+      <c r="C376" s="7">
+        <v>1</v>
+      </c>
+      <c r="D376" s="9"/>
       <c r="E376" s="5" t="s">
-        <v>797</v>
-      </c>
-      <c r="F376" s="4">
-        <v>1</v>
-      </c>
-      <c r="G376" s="4">
-        <v>12</v>
-      </c>
-      <c r="H376" s="4" t="s">
-        <v>748</v>
-      </c>
+        <v>837</v>
+      </c>
+      <c r="F376" s="4"/>
+      <c r="G376" s="4"/>
+      <c r="H376" s="4"/>
       <c r="I376" s="4" t="s">
-        <v>798</v>
+        <v>838</v>
       </c>
       <c r="J376" s="4" t="s">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="K376" s="4"/>
     </row>
-    <row r="377" spans="1:11">
-      <c r="A377" s="4" t="s">
+    <row r="377" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A377" s="8" t="s">
         <v>746</v>
       </c>
-      <c r="B377" s="4" t="s">
+      <c r="B377" s="7" t="s">
         <v>696</v>
       </c>
-      <c r="C377" s="4">
-        <v>3</v>
-      </c>
-      <c r="D377" s="4"/>
+      <c r="C377" s="7">
+        <v>2</v>
+      </c>
+      <c r="D377" s="9"/>
       <c r="E377" s="5" t="s">
-        <v>799</v>
-      </c>
-      <c r="F377" s="4">
-        <v>1</v>
-      </c>
-      <c r="G377" s="4">
-        <v>12</v>
-      </c>
-      <c r="H377" s="4" t="s">
-        <v>748</v>
-      </c>
+        <v>839</v>
+      </c>
+      <c r="F377" s="4"/>
+      <c r="G377" s="4"/>
+      <c r="H377" s="4"/>
       <c r="I377" s="4" t="s">
-        <v>800</v>
+        <v>840</v>
       </c>
       <c r="J377" s="4" t="s">
         <v>430</v>
       </c>
       <c r="K377" s="4"/>
     </row>
-    <row r="378" spans="1:11">
-      <c r="A378" s="4" t="s">
+    <row r="378" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A378" s="8" t="s">
         <v>746</v>
       </c>
-      <c r="B378" s="4" t="s">
+      <c r="B378" s="7" t="s">
         <v>696</v>
       </c>
-      <c r="C378" s="4">
+      <c r="C378" s="7">
         <v>3</v>
       </c>
-      <c r="D378" s="4"/>
+      <c r="D378" s="9"/>
       <c r="E378" s="5" t="s">
-        <v>801</v>
-      </c>
-      <c r="F378" s="4">
-        <v>1</v>
-      </c>
-      <c r="G378" s="4">
-        <v>12</v>
-      </c>
-      <c r="H378" s="4" t="s">
-        <v>748</v>
-      </c>
+        <v>841</v>
+      </c>
+      <c r="F378" s="4"/>
+      <c r="G378" s="4"/>
+      <c r="H378" s="4"/>
       <c r="I378" s="4" t="s">
-        <v>802</v>
+        <v>842</v>
       </c>
       <c r="J378" s="4" t="s">
         <v>430</v>
       </c>
       <c r="K378" s="4"/>
     </row>
-    <row r="379" spans="1:11">
-      <c r="A379" s="4" t="s">
+    <row r="379" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A379" s="8" t="s">
         <v>746</v>
       </c>
-      <c r="B379" s="4" t="s">
+      <c r="B379" s="7" t="s">
         <v>696</v>
       </c>
-      <c r="C379" s="4">
+      <c r="C379" s="7">
+        <v>4</v>
+      </c>
+      <c r="D379" s="9"/>
+      <c r="E379" s="5" t="s">
+        <v>843</v>
+      </c>
+      <c r="F379" s="4"/>
+      <c r="G379" s="4"/>
+      <c r="H379" s="4"/>
+      <c r="I379" s="4" t="s">
+        <v>844</v>
+      </c>
+      <c r="J379" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="K379" s="4"/>
+    </row>
+    <row r="380" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A380" s="8" t="s">
+        <v>746</v>
+      </c>
+      <c r="B380" s="7" t="s">
+        <v>696</v>
+      </c>
+      <c r="C380" s="7">
+        <v>1</v>
+      </c>
+      <c r="D380" s="9"/>
+      <c r="E380" s="5" t="s">
+        <v>845</v>
+      </c>
+      <c r="F380" s="4"/>
+      <c r="G380" s="4"/>
+      <c r="H380" s="4"/>
+      <c r="I380" s="4" t="s">
+        <v>846</v>
+      </c>
+      <c r="J380" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="K380" s="4"/>
+    </row>
+    <row r="381" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A381" s="8" t="s">
+        <v>746</v>
+      </c>
+      <c r="B381" s="7" t="s">
+        <v>696</v>
+      </c>
+      <c r="C381" s="7">
+        <v>2</v>
+      </c>
+      <c r="D381" s="9"/>
+      <c r="E381" s="5" t="s">
+        <v>847</v>
+      </c>
+      <c r="F381" s="4"/>
+      <c r="G381" s="4"/>
+      <c r="H381" s="4"/>
+      <c r="I381" s="4" t="s">
+        <v>848</v>
+      </c>
+      <c r="J381" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="K381" s="4"/>
+    </row>
+    <row r="382" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A382" s="8" t="s">
+        <v>746</v>
+      </c>
+      <c r="B382" s="7" t="s">
+        <v>696</v>
+      </c>
+      <c r="C382" s="7">
         <v>3</v>
       </c>
-      <c r="D379" s="4"/>
-      <c r="E379" s="5" t="s">
-        <v>803</v>
-      </c>
-      <c r="F379" s="4">
+      <c r="D382" s="9"/>
+      <c r="E382" s="5" t="s">
+        <v>849</v>
+      </c>
+      <c r="F382" s="4"/>
+      <c r="G382" s="4"/>
+      <c r="H382" s="4"/>
+      <c r="I382" s="4" t="s">
+        <v>850</v>
+      </c>
+      <c r="J382" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="K382" s="4"/>
+    </row>
+    <row r="383" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A383" s="8" t="s">
+        <v>746</v>
+      </c>
+      <c r="B383" s="7" t="s">
+        <v>696</v>
+      </c>
+      <c r="C383" s="7">
+        <v>4</v>
+      </c>
+      <c r="D383" s="9"/>
+      <c r="E383" s="5" t="s">
+        <v>851</v>
+      </c>
+      <c r="F383" s="4"/>
+      <c r="G383" s="4"/>
+      <c r="H383" s="4"/>
+      <c r="I383" s="4" t="s">
+        <v>852</v>
+      </c>
+      <c r="J383" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="K383" s="4"/>
+    </row>
+    <row r="384" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A384" s="8" t="s">
+        <v>746</v>
+      </c>
+      <c r="B384" s="7"/>
+      <c r="C384" s="7"/>
+      <c r="D384" s="9"/>
+      <c r="E384" s="5" t="s">
+        <v>853</v>
+      </c>
+      <c r="F384" s="4"/>
+      <c r="G384" s="4"/>
+      <c r="H384" s="4"/>
+      <c r="I384" s="4" t="s">
+        <v>854</v>
+      </c>
+      <c r="J384" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="K384" s="4"/>
+    </row>
+    <row r="385" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A385" s="8" t="s">
+        <v>746</v>
+      </c>
+      <c r="B385" s="7"/>
+      <c r="C385" s="7"/>
+      <c r="D385" s="9"/>
+      <c r="E385" s="5" t="s">
+        <v>855</v>
+      </c>
+      <c r="F385" s="4"/>
+      <c r="G385" s="4"/>
+      <c r="H385" s="4"/>
+      <c r="I385" s="4" t="s">
+        <v>856</v>
+      </c>
+      <c r="J385" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="K385" s="4"/>
+    </row>
+    <row r="386" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A386" s="8" t="s">
+        <v>746</v>
+      </c>
+      <c r="B386" s="7" t="s">
+        <v>696</v>
+      </c>
+      <c r="C386" s="7">
         <v>1</v>
       </c>
-      <c r="G379" s="4">
-        <v>12</v>
-      </c>
-      <c r="H379" s="4" t="s">
-        <v>748</v>
-      </c>
-      <c r="I379" s="4" t="s">
-        <v>804</v>
-      </c>
-      <c r="J379" s="4" t="s">
-        <v>784</v>
-      </c>
-      <c r="K379" s="4"/>
-    </row>
-    <row r="380" spans="1:11">
-      <c r="A380" s="4" t="s">
+      <c r="D386" s="9"/>
+      <c r="E386" s="5" t="s">
+        <v>857</v>
+      </c>
+      <c r="F386" s="4"/>
+      <c r="G386" s="4"/>
+      <c r="H386" s="4"/>
+      <c r="I386" s="4" t="s">
+        <v>858</v>
+      </c>
+      <c r="J386" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="K386" s="4"/>
+    </row>
+    <row r="387" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A387" s="8" t="s">
         <v>746</v>
       </c>
-      <c r="B380" s="4" t="s">
+      <c r="B387" s="7" t="s">
         <v>696</v>
       </c>
-      <c r="C380" s="4">
-        <v>3</v>
-      </c>
-      <c r="D380" s="4"/>
-      <c r="E380" s="5" t="s">
-        <v>805</v>
-      </c>
-      <c r="F380" s="4">
-        <v>1</v>
-      </c>
-      <c r="G380" s="4">
-        <v>12</v>
-      </c>
-      <c r="H380" s="4" t="s">
-        <v>748</v>
-      </c>
-      <c r="I380" s="4" t="s">
-        <v>806</v>
-      </c>
-      <c r="J380" s="4" t="s">
-        <v>436</v>
-      </c>
-      <c r="K380" s="4"/>
-    </row>
-    <row r="381" spans="1:11">
-      <c r="A381" s="4" t="s">
-        <v>746</v>
-      </c>
-      <c r="B381" s="4" t="s">
-        <v>696</v>
-      </c>
-      <c r="C381" s="4">
-        <v>3</v>
-      </c>
-      <c r="D381" s="4"/>
-      <c r="E381" s="5" t="s">
-        <v>807</v>
-      </c>
-      <c r="F381" s="4">
-        <v>1</v>
-      </c>
-      <c r="G381" s="4">
-        <v>12</v>
-      </c>
-      <c r="H381" s="4" t="s">
-        <v>748</v>
-      </c>
-      <c r="I381" s="4" t="s">
-        <v>808</v>
-      </c>
-      <c r="J381" s="4" t="s">
-        <v>766</v>
-      </c>
-      <c r="K381" s="4"/>
-    </row>
-    <row r="382" spans="1:11">
-      <c r="A382" s="4" t="s">
-        <v>746</v>
-      </c>
-      <c r="B382" s="4" t="s">
-        <v>696</v>
-      </c>
-      <c r="C382" s="4">
-        <v>3</v>
-      </c>
-      <c r="D382" s="4"/>
-      <c r="E382" s="5" t="s">
-        <v>809</v>
-      </c>
-      <c r="F382" s="4">
-        <v>1</v>
-      </c>
-      <c r="G382" s="4">
-        <v>12</v>
-      </c>
-      <c r="H382" s="4" t="s">
-        <v>748</v>
-      </c>
-      <c r="I382" s="4" t="s">
-        <v>810</v>
-      </c>
-      <c r="J382" s="4" t="s">
-        <v>769</v>
-      </c>
-      <c r="K382" s="4"/>
-    </row>
-    <row r="383" spans="1:11">
-      <c r="A383" s="4" t="s">
-        <v>746</v>
-      </c>
-      <c r="B383" s="4" t="s">
-        <v>696</v>
-      </c>
-      <c r="C383" s="4">
-        <v>3</v>
-      </c>
-      <c r="D383" s="4"/>
-      <c r="E383" s="5" t="s">
-        <v>811</v>
-      </c>
-      <c r="F383" s="4">
-        <v>1</v>
-      </c>
-      <c r="G383" s="4">
-        <v>12</v>
-      </c>
-      <c r="H383" s="4" t="s">
-        <v>748</v>
-      </c>
-      <c r="I383" s="4" t="s">
-        <v>812</v>
-      </c>
-      <c r="J383" s="4" t="s">
-        <v>769</v>
-      </c>
-      <c r="K383" s="4"/>
-    </row>
-    <row r="384" spans="1:11">
-      <c r="A384" s="4" t="s">
-        <v>746</v>
-      </c>
-      <c r="B384" s="4" t="s">
-        <v>696</v>
-      </c>
-      <c r="C384" s="4">
-        <v>4</v>
-      </c>
-      <c r="D384" s="4"/>
-      <c r="E384" s="5" t="s">
-        <v>813</v>
-      </c>
-      <c r="F384" s="4">
-        <v>1</v>
-      </c>
-      <c r="G384" s="4">
-        <v>12</v>
-      </c>
-      <c r="H384" s="4" t="s">
-        <v>748</v>
-      </c>
-      <c r="I384" s="4" t="s">
-        <v>814</v>
-      </c>
-      <c r="J384" s="4" t="s">
-        <v>750</v>
-      </c>
-      <c r="K384" s="4"/>
-    </row>
-    <row r="385" spans="1:11">
-      <c r="A385" s="4" t="s">
-        <v>746</v>
-      </c>
-      <c r="B385" s="4" t="s">
-        <v>696</v>
-      </c>
-      <c r="C385" s="4">
-        <v>4</v>
-      </c>
-      <c r="D385" s="4"/>
-      <c r="E385" s="5" t="s">
-        <v>815</v>
-      </c>
-      <c r="F385" s="4">
-        <v>1</v>
-      </c>
-      <c r="G385" s="4">
-        <v>12</v>
-      </c>
-      <c r="H385" s="4" t="s">
-        <v>748</v>
-      </c>
-      <c r="I385" s="4" t="s">
-        <v>816</v>
-      </c>
-      <c r="J385" s="4" t="s">
-        <v>420</v>
-      </c>
-      <c r="K385" s="4"/>
-    </row>
-    <row r="386" spans="1:11">
-      <c r="A386" s="4" t="s">
-        <v>746</v>
-      </c>
-      <c r="B386" s="4" t="s">
-        <v>696</v>
-      </c>
-      <c r="C386" s="4">
-        <v>4</v>
-      </c>
-      <c r="D386" s="4"/>
-      <c r="E386" s="5" t="s">
-        <v>817</v>
-      </c>
-      <c r="F386" s="4">
-        <v>1</v>
-      </c>
-      <c r="G386" s="4">
-        <v>12</v>
-      </c>
-      <c r="H386" s="4" t="s">
-        <v>748</v>
-      </c>
-      <c r="I386" s="4" t="s">
-        <v>818</v>
-      </c>
-      <c r="J386" s="4" t="s">
-        <v>420</v>
-      </c>
-      <c r="K386" s="4"/>
-    </row>
-    <row r="387" spans="1:11">
-      <c r="A387" s="4" t="s">
-        <v>746</v>
-      </c>
-      <c r="B387" s="4" t="s">
-        <v>696</v>
-      </c>
-      <c r="C387" s="4">
-        <v>4</v>
-      </c>
-      <c r="D387" s="4"/>
+      <c r="C387" s="7">
+        <v>2</v>
+      </c>
+      <c r="D387" s="9"/>
       <c r="E387" s="5" t="s">
-        <v>819</v>
-      </c>
-      <c r="F387" s="4">
-        <v>1</v>
-      </c>
-      <c r="G387" s="4">
-        <v>12</v>
-      </c>
-      <c r="H387" s="4" t="s">
-        <v>748</v>
-      </c>
+        <v>859</v>
+      </c>
+      <c r="F387" s="4"/>
+      <c r="G387" s="4"/>
+      <c r="H387" s="4"/>
       <c r="I387" s="4" t="s">
-        <v>820</v>
+        <v>860</v>
       </c>
       <c r="J387" s="4" t="s">
         <v>430</v>
       </c>
       <c r="K387" s="4"/>
     </row>
-    <row r="388" spans="1:11">
-      <c r="A388" s="4" t="s">
+    <row r="388" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A388" s="8" t="s">
         <v>746</v>
       </c>
-      <c r="B388" s="4" t="s">
+      <c r="B388" s="7" t="s">
         <v>696</v>
       </c>
-      <c r="C388" s="4">
-        <v>4</v>
-      </c>
-      <c r="D388" s="4"/>
+      <c r="C388" s="7">
+        <v>3</v>
+      </c>
+      <c r="D388" s="9"/>
       <c r="E388" s="5" t="s">
-        <v>821</v>
-      </c>
-      <c r="F388" s="4">
-        <v>1</v>
-      </c>
-      <c r="G388" s="4">
-        <v>12</v>
-      </c>
-      <c r="H388" s="4" t="s">
-        <v>748</v>
-      </c>
+        <v>861</v>
+      </c>
+      <c r="F388" s="4"/>
+      <c r="G388" s="4"/>
+      <c r="H388" s="4"/>
       <c r="I388" s="4" t="s">
-        <v>822</v>
+        <v>862</v>
       </c>
       <c r="J388" s="4" t="s">
         <v>430</v>
       </c>
       <c r="K388" s="4"/>
     </row>
-    <row r="389" spans="1:11">
-      <c r="A389" s="4" t="s">
+    <row r="389" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A389" s="8" t="s">
         <v>746</v>
       </c>
-      <c r="B389" s="4" t="s">
+      <c r="B389" s="7" t="s">
         <v>696</v>
       </c>
-      <c r="C389" s="4">
+      <c r="C389" s="7">
         <v>4</v>
       </c>
-      <c r="D389" s="4"/>
+      <c r="D389" s="9"/>
       <c r="E389" s="5" t="s">
-        <v>823</v>
-      </c>
-      <c r="F389" s="4">
+        <v>863</v>
+      </c>
+      <c r="F389" s="4"/>
+      <c r="G389" s="4"/>
+      <c r="H389" s="4"/>
+      <c r="I389" s="4" t="s">
+        <v>864</v>
+      </c>
+      <c r="J389" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="K389" s="4"/>
+    </row>
+    <row r="390" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A390" s="8" t="s">
+        <v>746</v>
+      </c>
+      <c r="B390" s="7"/>
+      <c r="C390" s="7"/>
+      <c r="D390" s="9"/>
+      <c r="E390" s="5" t="s">
+        <v>865</v>
+      </c>
+      <c r="F390" s="4"/>
+      <c r="G390" s="4"/>
+      <c r="H390" s="4"/>
+      <c r="I390" s="4" t="s">
+        <v>866</v>
+      </c>
+      <c r="J390" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="K390" s="4"/>
+    </row>
+    <row r="391" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A391" s="8" t="s">
+        <v>746</v>
+      </c>
+      <c r="B391" s="7"/>
+      <c r="C391" s="7"/>
+      <c r="D391" s="9"/>
+      <c r="E391" s="5" t="s">
+        <v>867</v>
+      </c>
+      <c r="F391" s="4"/>
+      <c r="G391" s="4"/>
+      <c r="H391" s="4"/>
+      <c r="I391" s="4" t="s">
+        <v>868</v>
+      </c>
+      <c r="J391" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="K391" s="4"/>
+    </row>
+    <row r="392" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A392" s="8" t="s">
+        <v>746</v>
+      </c>
+      <c r="B392" s="7"/>
+      <c r="C392" s="7"/>
+      <c r="D392" s="9"/>
+      <c r="E392" s="5" t="s">
+        <v>869</v>
+      </c>
+      <c r="F392" s="4"/>
+      <c r="G392" s="4"/>
+      <c r="H392" s="4"/>
+      <c r="I392" s="4" t="s">
+        <v>870</v>
+      </c>
+      <c r="J392" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="K392" s="4"/>
+    </row>
+    <row r="393" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A393" s="8" t="s">
+        <v>746</v>
+      </c>
+      <c r="B393" s="7" t="s">
+        <v>696</v>
+      </c>
+      <c r="C393" s="7">
         <v>1</v>
       </c>
-      <c r="G389" s="4">
-        <v>12</v>
-      </c>
-      <c r="H389" s="4" t="s">
-        <v>748</v>
-      </c>
-      <c r="I389" s="4" t="s">
-        <v>824</v>
-      </c>
-      <c r="J389" s="4" t="s">
-        <v>784</v>
-      </c>
-      <c r="K389" s="4"/>
-    </row>
-    <row r="390" spans="1:11">
-      <c r="A390" s="4" t="s">
-        <v>746</v>
-      </c>
-      <c r="B390" s="4" t="s">
-        <v>696</v>
-      </c>
-      <c r="C390" s="4">
-        <v>4</v>
-      </c>
-      <c r="D390" s="4"/>
-      <c r="E390" s="5" t="s">
-        <v>825</v>
-      </c>
-      <c r="F390" s="4">
-        <v>1</v>
-      </c>
-      <c r="G390" s="4">
-        <v>12</v>
-      </c>
-      <c r="H390" s="4" t="s">
-        <v>748</v>
-      </c>
-      <c r="I390" s="4" t="s">
-        <v>826</v>
-      </c>
-      <c r="J390" s="4" t="s">
-        <v>766</v>
-      </c>
-      <c r="K390" s="4"/>
-    </row>
-    <row r="391" spans="1:11">
-      <c r="A391" s="4" t="s">
-        <v>746</v>
-      </c>
-      <c r="B391" s="4" t="s">
-        <v>696</v>
-      </c>
-      <c r="C391" s="4">
-        <v>4</v>
-      </c>
-      <c r="D391" s="4"/>
-      <c r="E391" s="5" t="s">
-        <v>827</v>
-      </c>
-      <c r="F391" s="4">
-        <v>1</v>
-      </c>
-      <c r="G391" s="4">
-        <v>12</v>
-      </c>
-      <c r="H391" s="4" t="s">
-        <v>748</v>
-      </c>
-      <c r="I391" s="4" t="s">
-        <v>828</v>
-      </c>
-      <c r="J391" s="4" t="s">
-        <v>769</v>
-      </c>
-      <c r="K391" s="4"/>
-    </row>
-    <row r="392" spans="1:11">
-      <c r="A392" s="4" t="s">
-        <v>746</v>
-      </c>
-      <c r="B392" s="4" t="s">
-        <v>696</v>
-      </c>
-      <c r="C392" s="4">
-        <v>4</v>
-      </c>
-      <c r="D392" s="4"/>
-      <c r="E392" s="5" t="s">
-        <v>829</v>
-      </c>
-      <c r="F392" s="4">
-        <v>1</v>
-      </c>
-      <c r="G392" s="4">
-        <v>12</v>
-      </c>
-      <c r="H392" s="4" t="s">
-        <v>748</v>
-      </c>
-      <c r="I392" s="4" t="s">
-        <v>830</v>
-      </c>
-      <c r="J392" s="4" t="s">
-        <v>769</v>
-      </c>
-      <c r="K392" s="4"/>
-    </row>
-    <row r="393" spans="1:11">
-      <c r="A393" s="4" t="s">
-        <v>746</v>
-      </c>
-      <c r="B393" s="4" t="s">
-        <v>696</v>
-      </c>
-      <c r="C393" s="4">
-        <v>4</v>
-      </c>
-      <c r="D393" s="4"/>
+      <c r="D393" s="9"/>
       <c r="E393" s="5" t="s">
-        <v>831</v>
+        <v>759</v>
       </c>
       <c r="F393" s="4">
         <v>1</v>
@@ -12470,461 +12359,639 @@
         <v>748</v>
       </c>
       <c r="I393" s="4" t="s">
-        <v>832</v>
+        <v>760</v>
       </c>
       <c r="J393" s="4" t="s">
-        <v>769</v>
+        <v>761</v>
       </c>
       <c r="K393" s="4"/>
     </row>
-    <row r="394" spans="1:11">
-      <c r="A394" s="4" t="s">
+    <row r="394" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A394" s="8" t="s">
         <v>746</v>
       </c>
-      <c r="B394" s="4"/>
-      <c r="C394" s="4"/>
-      <c r="D394" s="4"/>
+      <c r="B394" s="7" t="s">
+        <v>696</v>
+      </c>
+      <c r="C394" s="7">
+        <v>2</v>
+      </c>
+      <c r="D394" s="9"/>
       <c r="E394" s="5" t="s">
-        <v>833</v>
-      </c>
-      <c r="F394" s="4"/>
-      <c r="G394" s="4"/>
-      <c r="H394" s="4"/>
+        <v>782</v>
+      </c>
+      <c r="F394" s="4">
+        <v>1</v>
+      </c>
+      <c r="G394" s="4">
+        <v>12</v>
+      </c>
+      <c r="H394" s="4" t="s">
+        <v>748</v>
+      </c>
       <c r="I394" s="4" t="s">
-        <v>834</v>
+        <v>783</v>
       </c>
       <c r="J394" s="4" t="s">
-        <v>420</v>
+        <v>784</v>
       </c>
       <c r="K394" s="4"/>
     </row>
-    <row r="395" spans="1:11">
-      <c r="A395" s="4" t="s">
+    <row r="395" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A395" s="8" t="s">
         <v>746</v>
       </c>
-      <c r="B395" s="4"/>
-      <c r="C395" s="4"/>
-      <c r="D395" s="4"/>
+      <c r="B395" s="7" t="s">
+        <v>696</v>
+      </c>
+      <c r="C395" s="7">
+        <v>3</v>
+      </c>
+      <c r="D395" s="9"/>
       <c r="E395" s="5" t="s">
-        <v>835</v>
-      </c>
-      <c r="F395" s="4"/>
-      <c r="G395" s="4"/>
-      <c r="H395" s="4"/>
+        <v>803</v>
+      </c>
+      <c r="F395" s="4">
+        <v>1</v>
+      </c>
+      <c r="G395" s="4">
+        <v>12</v>
+      </c>
+      <c r="H395" s="4" t="s">
+        <v>748</v>
+      </c>
       <c r="I395" s="4" t="s">
-        <v>836</v>
+        <v>804</v>
       </c>
       <c r="J395" s="4" t="s">
-        <v>420</v>
+        <v>784</v>
       </c>
       <c r="K395" s="4"/>
     </row>
-    <row r="396" spans="1:11">
-      <c r="A396" s="4" t="s">
+    <row r="396" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A396" s="8" t="s">
         <v>746</v>
       </c>
-      <c r="B396" s="4"/>
-      <c r="C396" s="4"/>
-      <c r="D396" s="4"/>
+      <c r="B396" s="7" t="s">
+        <v>696</v>
+      </c>
+      <c r="C396" s="7">
+        <v>4</v>
+      </c>
+      <c r="D396" s="9"/>
       <c r="E396" s="5" t="s">
-        <v>837</v>
-      </c>
-      <c r="F396" s="4"/>
-      <c r="G396" s="4"/>
-      <c r="H396" s="4"/>
+        <v>823</v>
+      </c>
+      <c r="F396" s="4">
+        <v>1</v>
+      </c>
+      <c r="G396" s="4">
+        <v>12</v>
+      </c>
+      <c r="H396" s="4" t="s">
+        <v>748</v>
+      </c>
       <c r="I396" s="4" t="s">
-        <v>838</v>
+        <v>824</v>
       </c>
       <c r="J396" s="4" t="s">
-        <v>430</v>
+        <v>784</v>
       </c>
       <c r="K396" s="4"/>
     </row>
-    <row r="397" spans="1:11">
-      <c r="A397" s="4" t="s">
+    <row r="397" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A397" s="8" t="s">
         <v>746</v>
       </c>
-      <c r="B397" s="4"/>
-      <c r="C397" s="4"/>
-      <c r="D397" s="4"/>
+      <c r="B397" s="7" t="s">
+        <v>696</v>
+      </c>
+      <c r="C397" s="7">
+        <v>1</v>
+      </c>
+      <c r="D397" s="9"/>
       <c r="E397" s="5" t="s">
-        <v>839</v>
+        <v>871</v>
       </c>
       <c r="F397" s="4"/>
       <c r="G397" s="4"/>
       <c r="H397" s="4"/>
       <c r="I397" s="4" t="s">
-        <v>840</v>
+        <v>872</v>
       </c>
       <c r="J397" s="4" t="s">
-        <v>430</v>
+        <v>784</v>
       </c>
       <c r="K397" s="4"/>
     </row>
-    <row r="398" spans="1:11">
-      <c r="A398" s="4" t="s">
+    <row r="398" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A398" s="8" t="s">
         <v>746</v>
       </c>
-      <c r="B398" s="4"/>
-      <c r="C398" s="4"/>
-      <c r="D398" s="4"/>
+      <c r="B398" s="7" t="s">
+        <v>696</v>
+      </c>
+      <c r="C398" s="7">
+        <v>2</v>
+      </c>
+      <c r="D398" s="9"/>
       <c r="E398" s="5" t="s">
-        <v>841</v>
+        <v>873</v>
       </c>
       <c r="F398" s="4"/>
       <c r="G398" s="4"/>
       <c r="H398" s="4"/>
       <c r="I398" s="4" t="s">
-        <v>842</v>
+        <v>874</v>
       </c>
       <c r="J398" s="4" t="s">
-        <v>430</v>
+        <v>784</v>
       </c>
       <c r="K398" s="4"/>
     </row>
-    <row r="399" spans="1:11">
-      <c r="A399" s="4" t="s">
+    <row r="399" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A399" s="8" t="s">
         <v>746</v>
       </c>
-      <c r="B399" s="4"/>
-      <c r="C399" s="4"/>
-      <c r="D399" s="4"/>
+      <c r="B399" s="7" t="s">
+        <v>696</v>
+      </c>
+      <c r="C399" s="7">
+        <v>3</v>
+      </c>
+      <c r="D399" s="9"/>
       <c r="E399" s="5" t="s">
-        <v>843</v>
-      </c>
-      <c r="F399" s="4"/>
-      <c r="G399" s="4"/>
-      <c r="H399" s="4"/>
+        <v>762</v>
+      </c>
+      <c r="F399" s="4">
+        <v>1</v>
+      </c>
+      <c r="G399" s="4">
+        <v>12</v>
+      </c>
+      <c r="H399" s="4" t="s">
+        <v>748</v>
+      </c>
       <c r="I399" s="4" t="s">
-        <v>844</v>
+        <v>763</v>
       </c>
       <c r="J399" s="4" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="K399" s="4"/>
     </row>
-    <row r="400" spans="1:11">
-      <c r="A400" s="4" t="s">
+    <row r="400" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A400" s="8" t="s">
         <v>746</v>
       </c>
-      <c r="B400" s="4"/>
-      <c r="C400" s="4"/>
-      <c r="D400" s="4"/>
+      <c r="B400" s="7" t="s">
+        <v>696</v>
+      </c>
+      <c r="C400" s="7">
+        <v>4</v>
+      </c>
+      <c r="D400" s="9"/>
       <c r="E400" s="5" t="s">
-        <v>845</v>
-      </c>
-      <c r="F400" s="4"/>
-      <c r="G400" s="4"/>
-      <c r="H400" s="4"/>
+        <v>785</v>
+      </c>
+      <c r="F400" s="4">
+        <v>1</v>
+      </c>
+      <c r="G400" s="4">
+        <v>12</v>
+      </c>
+      <c r="H400" s="4" t="s">
+        <v>748</v>
+      </c>
       <c r="I400" s="4" t="s">
-        <v>846</v>
+        <v>786</v>
       </c>
       <c r="J400" s="4" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="K400" s="4"/>
     </row>
-    <row r="401" spans="1:11">
-      <c r="A401" s="4" t="s">
+    <row r="401" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A401" s="8" t="s">
         <v>746</v>
       </c>
-      <c r="B401" s="4"/>
-      <c r="C401" s="4"/>
-      <c r="D401" s="4"/>
+      <c r="B401" s="7"/>
+      <c r="C401" s="7"/>
+      <c r="D401" s="9"/>
       <c r="E401" s="5" t="s">
-        <v>847</v>
-      </c>
-      <c r="F401" s="4"/>
-      <c r="G401" s="4"/>
-      <c r="H401" s="4"/>
+        <v>805</v>
+      </c>
+      <c r="F401" s="4">
+        <v>1</v>
+      </c>
+      <c r="G401" s="4">
+        <v>12</v>
+      </c>
+      <c r="H401" s="4" t="s">
+        <v>748</v>
+      </c>
       <c r="I401" s="4" t="s">
-        <v>848</v>
+        <v>806</v>
       </c>
       <c r="J401" s="4" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="K401" s="4"/>
     </row>
-    <row r="402" spans="1:11">
-      <c r="A402" s="4" t="s">
+    <row r="402" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A402" s="8" t="s">
         <v>746</v>
       </c>
-      <c r="B402" s="4"/>
-      <c r="C402" s="4"/>
-      <c r="D402" s="4"/>
+      <c r="B402" s="7" t="s">
+        <v>696</v>
+      </c>
+      <c r="C402" s="7">
+        <v>1</v>
+      </c>
+      <c r="D402" s="9"/>
       <c r="E402" s="5" t="s">
-        <v>849</v>
-      </c>
-      <c r="F402" s="4"/>
-      <c r="G402" s="4"/>
-      <c r="H402" s="4"/>
+        <v>764</v>
+      </c>
+      <c r="F402" s="4">
+        <v>1</v>
+      </c>
+      <c r="G402" s="4">
+        <v>12</v>
+      </c>
+      <c r="H402" s="4" t="s">
+        <v>748</v>
+      </c>
       <c r="I402" s="4" t="s">
-        <v>850</v>
+        <v>765</v>
       </c>
       <c r="J402" s="4" t="s">
-        <v>430</v>
+        <v>766</v>
       </c>
       <c r="K402" s="4"/>
     </row>
-    <row r="403" spans="1:11">
-      <c r="A403" s="4" t="s">
+    <row r="403" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A403" s="8" t="s">
         <v>746</v>
       </c>
-      <c r="B403" s="4"/>
-      <c r="C403" s="4"/>
-      <c r="D403" s="4"/>
+      <c r="B403" s="7" t="s">
+        <v>696</v>
+      </c>
+      <c r="C403" s="7">
+        <v>2</v>
+      </c>
+      <c r="D403" s="9"/>
       <c r="E403" s="5" t="s">
-        <v>851</v>
-      </c>
-      <c r="F403" s="4"/>
-      <c r="G403" s="4"/>
-      <c r="H403" s="4"/>
+        <v>787</v>
+      </c>
+      <c r="F403" s="4">
+        <v>1</v>
+      </c>
+      <c r="G403" s="4">
+        <v>12</v>
+      </c>
+      <c r="H403" s="4" t="s">
+        <v>748</v>
+      </c>
       <c r="I403" s="4" t="s">
-        <v>852</v>
+        <v>788</v>
       </c>
       <c r="J403" s="4" t="s">
-        <v>430</v>
+        <v>766</v>
       </c>
       <c r="K403" s="4"/>
     </row>
-    <row r="404" spans="1:11">
-      <c r="A404" s="4" t="s">
+    <row r="404" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A404" s="8" t="s">
         <v>746</v>
       </c>
-      <c r="B404" s="4"/>
-      <c r="C404" s="4"/>
-      <c r="D404" s="4"/>
+      <c r="B404" s="7" t="s">
+        <v>696</v>
+      </c>
+      <c r="C404" s="7">
+        <v>3</v>
+      </c>
+      <c r="D404" s="9"/>
       <c r="E404" s="5" t="s">
-        <v>853</v>
-      </c>
-      <c r="F404" s="4"/>
-      <c r="G404" s="4"/>
-      <c r="H404" s="4"/>
+        <v>807</v>
+      </c>
+      <c r="F404" s="4">
+        <v>1</v>
+      </c>
+      <c r="G404" s="4">
+        <v>12</v>
+      </c>
+      <c r="H404" s="4" t="s">
+        <v>748</v>
+      </c>
       <c r="I404" s="4" t="s">
-        <v>854</v>
+        <v>808</v>
       </c>
       <c r="J404" s="4" t="s">
-        <v>430</v>
+        <v>766</v>
       </c>
       <c r="K404" s="4"/>
     </row>
-    <row r="405" spans="1:11">
-      <c r="A405" s="4" t="s">
+    <row r="405" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A405" s="8" t="s">
         <v>746</v>
       </c>
-      <c r="B405" s="4"/>
-      <c r="C405" s="4"/>
-      <c r="D405" s="4"/>
+      <c r="B405" s="7" t="s">
+        <v>696</v>
+      </c>
+      <c r="C405" s="7">
+        <v>4</v>
+      </c>
+      <c r="D405" s="9"/>
       <c r="E405" s="5" t="s">
-        <v>855</v>
-      </c>
-      <c r="F405" s="4"/>
-      <c r="G405" s="4"/>
-      <c r="H405" s="4"/>
+        <v>825</v>
+      </c>
+      <c r="F405" s="4">
+        <v>1</v>
+      </c>
+      <c r="G405" s="4">
+        <v>12</v>
+      </c>
+      <c r="H405" s="4" t="s">
+        <v>748</v>
+      </c>
       <c r="I405" s="4" t="s">
-        <v>856</v>
+        <v>826</v>
       </c>
       <c r="J405" s="4" t="s">
-        <v>430</v>
+        <v>766</v>
       </c>
       <c r="K405" s="4"/>
     </row>
-    <row r="406" spans="1:11">
-      <c r="A406" s="4" t="s">
+    <row r="406" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A406" s="8" t="s">
         <v>746</v>
       </c>
-      <c r="B406" s="4"/>
-      <c r="C406" s="4"/>
-      <c r="D406" s="4"/>
+      <c r="B406" s="7"/>
+      <c r="C406" s="7"/>
+      <c r="D406" s="9"/>
       <c r="E406" s="5" t="s">
-        <v>857</v>
-      </c>
-      <c r="F406" s="4"/>
-      <c r="G406" s="4"/>
-      <c r="H406" s="4"/>
+        <v>767</v>
+      </c>
+      <c r="F406" s="4">
+        <v>1</v>
+      </c>
+      <c r="G406" s="4">
+        <v>12</v>
+      </c>
+      <c r="H406" s="4" t="s">
+        <v>748</v>
+      </c>
       <c r="I406" s="4" t="s">
-        <v>858</v>
+        <v>768</v>
       </c>
       <c r="J406" s="4" t="s">
-        <v>430</v>
+        <v>769</v>
       </c>
       <c r="K406" s="4"/>
     </row>
-    <row r="407" spans="1:11">
-      <c r="A407" s="4" t="s">
+    <row r="407" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A407" s="8" t="s">
         <v>746</v>
       </c>
-      <c r="B407" s="4"/>
-      <c r="C407" s="4"/>
-      <c r="D407" s="4"/>
+      <c r="B407" s="7"/>
+      <c r="C407" s="7"/>
+      <c r="D407" s="9"/>
       <c r="E407" s="5" t="s">
-        <v>859</v>
-      </c>
-      <c r="F407" s="4"/>
-      <c r="G407" s="4"/>
-      <c r="H407" s="4"/>
+        <v>770</v>
+      </c>
+      <c r="F407" s="4">
+        <v>1</v>
+      </c>
+      <c r="G407" s="4">
+        <v>12</v>
+      </c>
+      <c r="H407" s="4" t="s">
+        <v>748</v>
+      </c>
       <c r="I407" s="4" t="s">
-        <v>860</v>
+        <v>771</v>
       </c>
       <c r="J407" s="4" t="s">
-        <v>430</v>
+        <v>769</v>
       </c>
       <c r="K407" s="4"/>
     </row>
-    <row r="408" spans="1:11">
-      <c r="A408" s="4" t="s">
+    <row r="408" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A408" s="8" t="s">
         <v>746</v>
       </c>
-      <c r="B408" s="4"/>
-      <c r="C408" s="4"/>
-      <c r="D408" s="4"/>
+      <c r="B408" s="7"/>
+      <c r="C408" s="7"/>
+      <c r="D408" s="9"/>
       <c r="E408" s="5" t="s">
-        <v>861</v>
-      </c>
-      <c r="F408" s="4"/>
-      <c r="G408" s="4"/>
-      <c r="H408" s="4"/>
+        <v>789</v>
+      </c>
+      <c r="F408" s="4">
+        <v>1</v>
+      </c>
+      <c r="G408" s="4">
+        <v>12</v>
+      </c>
+      <c r="H408" s="4" t="s">
+        <v>748</v>
+      </c>
       <c r="I408" s="4" t="s">
-        <v>862</v>
+        <v>790</v>
       </c>
       <c r="J408" s="4" t="s">
-        <v>430</v>
+        <v>769</v>
       </c>
       <c r="K408" s="4"/>
     </row>
-    <row r="409" spans="1:11">
-      <c r="A409" s="4" t="s">
+    <row r="409" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A409" s="8" t="s">
         <v>746</v>
       </c>
-      <c r="B409" s="4"/>
-      <c r="C409" s="4"/>
-      <c r="D409" s="4"/>
+      <c r="B409" s="7"/>
+      <c r="C409" s="7"/>
+      <c r="D409" s="9"/>
       <c r="E409" s="5" t="s">
-        <v>863</v>
-      </c>
-      <c r="F409" s="4"/>
-      <c r="G409" s="4"/>
-      <c r="H409" s="4"/>
+        <v>791</v>
+      </c>
+      <c r="F409" s="4">
+        <v>1</v>
+      </c>
+      <c r="G409" s="4">
+        <v>12</v>
+      </c>
+      <c r="H409" s="4" t="s">
+        <v>748</v>
+      </c>
       <c r="I409" s="4" t="s">
-        <v>864</v>
+        <v>792</v>
       </c>
       <c r="J409" s="4" t="s">
-        <v>430</v>
+        <v>769</v>
       </c>
       <c r="K409" s="4"/>
     </row>
-    <row r="410" spans="1:11">
-      <c r="A410" s="4" t="s">
+    <row r="410" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A410" s="8" t="s">
         <v>746</v>
       </c>
-      <c r="B410" s="4"/>
-      <c r="C410" s="4"/>
-      <c r="D410" s="4"/>
+      <c r="B410" s="7" t="s">
+        <v>696</v>
+      </c>
+      <c r="C410" s="7">
+        <v>1</v>
+      </c>
+      <c r="D410" s="9"/>
       <c r="E410" s="5" t="s">
-        <v>865</v>
-      </c>
-      <c r="F410" s="4"/>
-      <c r="G410" s="4"/>
-      <c r="H410" s="4"/>
+        <v>809</v>
+      </c>
+      <c r="F410" s="4">
+        <v>1</v>
+      </c>
+      <c r="G410" s="4">
+        <v>12</v>
+      </c>
+      <c r="H410" s="4" t="s">
+        <v>748</v>
+      </c>
       <c r="I410" s="4" t="s">
-        <v>866</v>
+        <v>810</v>
       </c>
       <c r="J410" s="4" t="s">
-        <v>430</v>
+        <v>769</v>
       </c>
       <c r="K410" s="4"/>
     </row>
-    <row r="411" spans="1:11">
-      <c r="A411" s="4" t="s">
+    <row r="411" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A411" s="8" t="s">
         <v>746</v>
       </c>
-      <c r="B411" s="4"/>
-      <c r="C411" s="4"/>
-      <c r="D411" s="4"/>
+      <c r="B411" s="7" t="s">
+        <v>696</v>
+      </c>
+      <c r="C411" s="7">
+        <v>2</v>
+      </c>
+      <c r="D411" s="9"/>
       <c r="E411" s="5" t="s">
-        <v>867</v>
-      </c>
-      <c r="F411" s="4"/>
-      <c r="G411" s="4"/>
-      <c r="H411" s="4"/>
+        <v>811</v>
+      </c>
+      <c r="F411" s="4">
+        <v>1</v>
+      </c>
+      <c r="G411" s="4">
+        <v>12</v>
+      </c>
+      <c r="H411" s="4" t="s">
+        <v>748</v>
+      </c>
       <c r="I411" s="4" t="s">
-        <v>868</v>
+        <v>812</v>
       </c>
       <c r="J411" s="4" t="s">
-        <v>430</v>
+        <v>769</v>
       </c>
       <c r="K411" s="4"/>
     </row>
-    <row r="412" spans="1:11">
-      <c r="A412" s="4" t="s">
+    <row r="412" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A412" s="8" t="s">
         <v>746</v>
       </c>
-      <c r="B412" s="4"/>
-      <c r="C412" s="4"/>
-      <c r="D412" s="4"/>
+      <c r="B412" s="7" t="s">
+        <v>696</v>
+      </c>
+      <c r="C412" s="7">
+        <v>3</v>
+      </c>
+      <c r="D412" s="9"/>
       <c r="E412" s="5" t="s">
-        <v>869</v>
-      </c>
-      <c r="F412" s="4"/>
-      <c r="G412" s="4"/>
-      <c r="H412" s="4"/>
+        <v>827</v>
+      </c>
+      <c r="F412" s="4">
+        <v>1</v>
+      </c>
+      <c r="G412" s="4">
+        <v>12</v>
+      </c>
+      <c r="H412" s="4" t="s">
+        <v>748</v>
+      </c>
       <c r="I412" s="4" t="s">
-        <v>870</v>
+        <v>828</v>
       </c>
       <c r="J412" s="4" t="s">
-        <v>430</v>
+        <v>769</v>
       </c>
       <c r="K412" s="4"/>
     </row>
-    <row r="413" spans="1:11">
-      <c r="A413" s="4" t="s">
+    <row r="413" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A413" s="8" t="s">
         <v>746</v>
       </c>
-      <c r="B413" s="4"/>
-      <c r="C413" s="4"/>
-      <c r="D413" s="4"/>
+      <c r="B413" s="7" t="s">
+        <v>696</v>
+      </c>
+      <c r="C413" s="7">
+        <v>4</v>
+      </c>
+      <c r="D413" s="9"/>
       <c r="E413" s="5" t="s">
-        <v>871</v>
-      </c>
-      <c r="F413" s="4"/>
-      <c r="G413" s="4"/>
-      <c r="H413" s="4"/>
+        <v>829</v>
+      </c>
+      <c r="F413" s="4">
+        <v>1</v>
+      </c>
+      <c r="G413" s="4">
+        <v>12</v>
+      </c>
+      <c r="H413" s="4" t="s">
+        <v>748</v>
+      </c>
       <c r="I413" s="4" t="s">
-        <v>872</v>
+        <v>830</v>
       </c>
       <c r="J413" s="4" t="s">
-        <v>784</v>
+        <v>769</v>
       </c>
       <c r="K413" s="4"/>
     </row>
-    <row r="414" spans="1:11">
-      <c r="A414" s="4" t="s">
+    <row r="414" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A414" s="8" t="s">
         <v>746</v>
       </c>
-      <c r="B414" s="4"/>
-      <c r="C414" s="4"/>
-      <c r="D414" s="4"/>
+      <c r="B414" s="7"/>
+      <c r="C414" s="7"/>
+      <c r="D414" s="9"/>
       <c r="E414" s="5" t="s">
-        <v>873</v>
-      </c>
-      <c r="F414" s="4"/>
-      <c r="G414" s="4"/>
-      <c r="H414" s="4"/>
+        <v>831</v>
+      </c>
+      <c r="F414" s="4">
+        <v>1</v>
+      </c>
+      <c r="G414" s="4">
+        <v>12</v>
+      </c>
+      <c r="H414" s="4" t="s">
+        <v>748</v>
+      </c>
       <c r="I414" s="4" t="s">
-        <v>874</v>
+        <v>832</v>
       </c>
       <c r="J414" s="4" t="s">
-        <v>784</v>
+        <v>769</v>
       </c>
       <c r="K414" s="4"/>
     </row>
-    <row r="415" spans="1:11">
-      <c r="A415" s="4" t="s">
+    <row r="415" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A415" s="8" t="s">
         <v>746</v>
       </c>
-      <c r="B415" s="4"/>
-      <c r="C415" s="4"/>
-      <c r="D415" s="4"/>
+      <c r="B415" s="7" t="s">
+        <v>696</v>
+      </c>
+      <c r="C415" s="7">
+        <v>1</v>
+      </c>
+      <c r="D415" s="9"/>
       <c r="E415" s="5" t="s">
         <v>875</v>
       </c>
@@ -12939,13 +13006,17 @@
       </c>
       <c r="K415" s="4"/>
     </row>
-    <row r="416" spans="1:11">
-      <c r="A416" s="4" t="s">
+    <row r="416" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A416" s="8" t="s">
         <v>746</v>
       </c>
-      <c r="B416" s="4"/>
-      <c r="C416" s="4"/>
-      <c r="D416" s="4"/>
+      <c r="B416" s="7" t="s">
+        <v>696</v>
+      </c>
+      <c r="C416" s="7">
+        <v>2</v>
+      </c>
+      <c r="D416" s="9"/>
       <c r="E416" s="5" t="s">
         <v>877</v>
       </c>
@@ -12960,13 +13031,17 @@
       </c>
       <c r="K416" s="4"/>
     </row>
-    <row r="417" spans="1:11">
-      <c r="A417" s="4" t="s">
+    <row r="417" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A417" s="8" t="s">
         <v>746</v>
       </c>
-      <c r="B417" s="4"/>
-      <c r="C417" s="4"/>
-      <c r="D417" s="4"/>
+      <c r="B417" s="7" t="s">
+        <v>696</v>
+      </c>
+      <c r="C417" s="7">
+        <v>3</v>
+      </c>
+      <c r="D417" s="9"/>
       <c r="E417" s="5" t="s">
         <v>879</v>
       </c>
@@ -12976,16 +13051,22 @@
       <c r="I417" s="4" t="s">
         <v>880</v>
       </c>
-      <c r="J417" s="4"/>
+      <c r="J417" s="4" t="s">
+        <v>883</v>
+      </c>
       <c r="K417" s="4"/>
     </row>
-    <row r="418" spans="1:11">
-      <c r="A418" s="4" t="s">
+    <row r="418" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A418" s="8" t="s">
         <v>746</v>
       </c>
-      <c r="B418" s="4"/>
-      <c r="C418" s="4"/>
-      <c r="D418" s="4"/>
+      <c r="B418" s="7" t="s">
+        <v>696</v>
+      </c>
+      <c r="C418" s="7">
+        <v>4</v>
+      </c>
+      <c r="D418" s="9"/>
       <c r="E418" s="5" t="s">
         <v>881</v>
       </c>
@@ -12995,24 +13076,31 @@
       <c r="I418" s="6" t="s">
         <v>882</v>
       </c>
-      <c r="J418" s="4"/>
+      <c r="J418" s="4" t="s">
+        <v>769</v>
+      </c>
       <c r="K418" s="4"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K418">
     <sortCondition ref="A2:A418"/>
   </sortState>
+  <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="I265" r:id="rId1" xr:uid="{746FEFF8-DBAD-2D43-AED4-35C1958425EC}"/>
-    <hyperlink ref="I418" r:id="rId2" xr:uid="{163FF38D-4BD6-9B45-808D-A5167E3089E5}"/>
-    <hyperlink ref="I24" r:id="rId3" xr:uid="{A4C4478F-F826-584E-A002-34684A8AA870}"/>
-    <hyperlink ref="I336" r:id="rId4" xr:uid="{DF09D0DA-7EC4-45E8-8B26-A125CB473DD9}"/>
-    <hyperlink ref="I286" r:id="rId5" xr:uid="{0A05FF91-FAC3-4B0F-A229-6A55F4FB56F0}"/>
-    <hyperlink ref="I267" r:id="rId6" xr:uid="{87AF5374-BAB0-4B99-88A6-C9883216C80D}"/>
-    <hyperlink ref="I240" r:id="rId7" xr:uid="{ED507F1C-1168-46E1-B298-662349A8D8E3}"/>
-    <hyperlink ref="I353" r:id="rId8" xr:uid="{7084FE31-8ABC-49C6-BA6F-C35E5D3B5F0B}"/>
-    <hyperlink ref="I219" r:id="rId9" xr:uid="{A5D7B03C-2CE6-406B-934D-C4C58BD2508B}"/>
-    <hyperlink ref="I210" r:id="rId10" xr:uid="{A0D9D98C-7CFB-4B41-83C9-DBF19B7699FF}"/>
+    <hyperlink ref="I24" r:id="rId1" xr:uid="{A4C4478F-F826-584E-A002-34684A8AA870}"/>
+    <hyperlink ref="I137" r:id="rId2" xr:uid="{6213AA7B-AAAF-6241-9552-D40959098F83}"/>
+    <hyperlink ref="I138" r:id="rId3" xr:uid="{CE92FD1B-1ED5-6441-8D82-42E32AA420C7}"/>
+    <hyperlink ref="I259" r:id="rId4" xr:uid="{A0D9D98C-7CFB-4B41-83C9-DBF19B7699FF}"/>
+    <hyperlink ref="I260" r:id="rId5" xr:uid="{A5D7B03C-2CE6-406B-934D-C4C58BD2508B}"/>
+    <hyperlink ref="I353" r:id="rId6" xr:uid="{7084FE31-8ABC-49C6-BA6F-C35E5D3B5F0B}"/>
+    <hyperlink ref="I296" r:id="rId7" xr:uid="{ED507F1C-1168-46E1-B298-662349A8D8E3}"/>
+    <hyperlink ref="I300" r:id="rId8" xr:uid="{87AF5374-BAB0-4B99-88A6-C9883216C80D}"/>
+    <hyperlink ref="I217" r:id="rId9" xr:uid="{0A05FF91-FAC3-4B0F-A229-6A55F4FB56F0}"/>
+    <hyperlink ref="I336" r:id="rId10" xr:uid="{DF09D0DA-7EC4-45E8-8B26-A125CB473DD9}"/>
+    <hyperlink ref="I418" r:id="rId11" xr:uid="{163FF38D-4BD6-9B45-808D-A5167E3089E5}"/>
+    <hyperlink ref="I273" r:id="rId12" xr:uid="{746FEFF8-DBAD-2D43-AED4-35C1958425EC}"/>
+    <hyperlink ref="I139" r:id="rId13" xr:uid="{A8072672-5657-8F45-AB32-EC3D48D213D0}"/>
+    <hyperlink ref="I143" r:id="rId14" xr:uid="{7D62D190-EF93-C448-A85E-982A8FF14026}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
